--- a/EcoFin/capm.xlsx
+++ b/EcoFin/capm.xlsx
@@ -11,35 +11,6 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>GSPC</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>PG</t>
-  </si>
-  <si>
-    <t>IRX</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -86,10 +57,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,66 +355,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>GSPC</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
         <v>37226</v>
       </c>
       <c r="B2">
         <v>1148.079956054688</v>
       </c>
       <c r="C2">
-        <v>6.592257022857666</v>
+        <v>6.592257499694824</v>
       </c>
       <c r="D2">
-        <v>20.14488410949707</v>
+        <v>20.10705375671387</v>
       </c>
       <c r="E2">
-        <v>10.96506309509277</v>
+        <v>10.96506118774414</v>
       </c>
       <c r="F2">
-        <v>40.02902603149414</v>
+        <v>39.97174835205078</v>
       </c>
       <c r="G2">
-        <v>20.31270980834961</v>
+        <v>20.31270790100098</v>
       </c>
       <c r="H2">
         <v>1.669999957084656</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" s="2">
         <v>37257</v>
       </c>
       <c r="B3">
@@ -453,13 +440,13 @@
         <v>6.460348606109619</v>
       </c>
       <c r="D3">
-        <v>19.37254524230957</v>
+        <v>19.33614730834961</v>
       </c>
       <c r="E3">
-        <v>13.70433521270752</v>
+        <v>13.704345703125</v>
       </c>
       <c r="F3">
-        <v>38.27579116821289</v>
+        <v>38.22099685668945</v>
       </c>
       <c r="G3">
         <v>21.06780624389648</v>
@@ -468,164 +455,164 @@
         <v>1.720000028610229</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" s="2">
         <v>37288</v>
       </c>
       <c r="B4">
         <v>1106.72998046875</v>
       </c>
       <c r="C4">
-        <v>6.283005237579346</v>
+        <v>6.28300666809082</v>
       </c>
       <c r="D4">
-        <v>17.73967361450195</v>
+        <v>17.70633316040039</v>
       </c>
       <c r="E4">
-        <v>13.19618988037109</v>
+        <v>13.19619083404541</v>
       </c>
       <c r="F4">
-        <v>38.75546264648438</v>
+        <v>38.70002746582031</v>
       </c>
       <c r="G4">
-        <v>21.86997032165527</v>
+        <v>21.86996269226074</v>
       </c>
       <c r="H4">
         <v>1.720000028610229</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" s="2">
         <v>37316</v>
       </c>
       <c r="B5">
         <v>1147.390014648438</v>
       </c>
       <c r="C5">
-        <v>6.962820053100586</v>
+        <v>6.962818145751953</v>
       </c>
       <c r="D5">
-        <v>18.33869552612305</v>
+        <v>18.30423164367676</v>
       </c>
       <c r="E5">
-        <v>10.16312503814697</v>
+        <v>10.16312980651855</v>
       </c>
       <c r="F5">
-        <v>38.99601364135742</v>
+        <v>38.94020843505859</v>
       </c>
       <c r="G5">
-        <v>23.23699569702148</v>
+        <v>23.23699378967285</v>
       </c>
       <c r="H5">
         <v>1.740000009536743</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" s="2">
         <v>37347</v>
       </c>
       <c r="B6">
         <v>1076.920043945312</v>
       </c>
       <c r="C6">
-        <v>6.755917549133301</v>
+        <v>6.755918979644775</v>
       </c>
       <c r="D6">
-        <v>15.89090156555176</v>
+        <v>15.86104583740234</v>
       </c>
       <c r="E6">
-        <v>7.971706867218018</v>
+        <v>7.971701145172119</v>
       </c>
       <c r="F6">
-        <v>33.80167007446289</v>
+        <v>33.7532844543457</v>
       </c>
       <c r="G6">
-        <v>23.37826538085938</v>
+        <v>23.37825393676758</v>
       </c>
       <c r="H6">
         <v>1.730000019073486</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" s="2">
         <v>37377</v>
       </c>
       <c r="B7">
         <v>1067.140014648438</v>
       </c>
       <c r="C7">
-        <v>7.499495983123779</v>
+        <v>7.499494552612305</v>
       </c>
       <c r="D7">
-        <v>15.48040390014648</v>
+        <v>15.4513111114502</v>
       </c>
       <c r="E7">
-        <v>6.28843355178833</v>
+        <v>6.288434982299805</v>
       </c>
       <c r="F7">
-        <v>33.27016448974609</v>
+        <v>33.22256851196289</v>
       </c>
       <c r="G7">
-        <v>23.19437599182129</v>
+        <v>23.19437026977539</v>
       </c>
       <c r="H7">
         <v>1.705000042915344</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" s="2">
         <v>37408</v>
       </c>
       <c r="B8">
         <v>989.8200073242188</v>
       </c>
       <c r="C8">
-        <v>6.798408508300781</v>
+        <v>6.798409461975098</v>
       </c>
       <c r="D8">
-        <v>16.63284301757812</v>
+        <v>16.60159873962402</v>
       </c>
       <c r="E8">
-        <v>7.519130229949951</v>
+        <v>7.519128799438477</v>
       </c>
       <c r="F8">
-        <v>29.00212097167969</v>
+        <v>28.96063041687012</v>
       </c>
       <c r="G8">
-        <v>23.30921363830566</v>
+        <v>23.30921173095703</v>
       </c>
       <c r="H8">
         <v>1.659000039100647</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" s="2">
         <v>37438</v>
       </c>
       <c r="B9">
         <v>911.6199951171875</v>
       </c>
       <c r="C9">
-        <v>5.767101764678955</v>
+        <v>5.767099857330322</v>
       </c>
       <c r="D9">
-        <v>14.58946132659912</v>
+        <v>14.56205558776855</v>
       </c>
       <c r="E9">
         <v>7.947884082794189</v>
       </c>
       <c r="F9">
-        <v>30.04083061218262</v>
+        <v>29.99785232543945</v>
       </c>
       <c r="G9">
-        <v>23.34610557556152</v>
+        <v>23.34610366821289</v>
       </c>
       <c r="H9">
         <v>1.664999961853027</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1">
+    <row r="10">
+      <c r="A10" s="2">
         <v>37469</v>
       </c>
       <c r="B10">
@@ -635,127 +622,127 @@
         <v>5.039257049560547</v>
       </c>
       <c r="D10">
-        <v>14.92394638061523</v>
+        <v>14.89590358734131</v>
       </c>
       <c r="E10">
         <v>7.614405155181885</v>
       </c>
       <c r="F10">
-        <v>30.01098823547363</v>
+        <v>29.96804237365723</v>
       </c>
       <c r="G10">
-        <v>23.25691413879395</v>
+        <v>23.25690650939941</v>
       </c>
       <c r="H10">
         <v>1.644999980926514</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1">
+    <row r="11">
+      <c r="A11" s="2">
         <v>37500</v>
       </c>
       <c r="B11">
         <v>815.280029296875</v>
       </c>
       <c r="C11">
-        <v>4.195812702178955</v>
+        <v>4.195813655853271</v>
       </c>
       <c r="D11">
-        <v>13.30018997192383</v>
+        <v>13.27520084381104</v>
       </c>
       <c r="E11">
-        <v>6.240795135498047</v>
+        <v>6.240796566009521</v>
       </c>
       <c r="F11">
-        <v>28.60994720458984</v>
+        <v>28.56902313232422</v>
       </c>
       <c r="G11">
-        <v>23.44841766357422</v>
+        <v>23.44842910766602</v>
       </c>
       <c r="H11">
         <v>1.526999950408936</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1">
+    <row r="12">
+      <c r="A12" s="2">
         <v>37530</v>
       </c>
       <c r="B12">
         <v>885.760009765625</v>
       </c>
       <c r="C12">
-        <v>3.666003227233887</v>
+        <v>3.666002750396729</v>
       </c>
       <c r="D12">
-        <v>16.25882911682129</v>
+        <v>16.22828102111816</v>
       </c>
       <c r="E12">
-        <v>8.090805053710938</v>
+        <v>8.090800285339355</v>
       </c>
       <c r="F12">
-        <v>28.69268798828125</v>
+        <v>28.6516227722168</v>
       </c>
       <c r="G12">
-        <v>23.31012535095215</v>
+        <v>23.31012725830078</v>
       </c>
       <c r="H12">
         <v>1.41700005531311</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1">
+    <row r="13">
+      <c r="A13" s="2">
         <v>37561</v>
       </c>
       <c r="B13">
         <v>936.3099975585938</v>
       </c>
       <c r="C13">
-        <v>4.931338787078857</v>
+        <v>4.931339263916016</v>
       </c>
       <c r="D13">
-        <v>17.53897666931152</v>
+        <v>17.50603103637695</v>
       </c>
       <c r="E13">
-        <v>9.647031784057617</v>
+        <v>9.647032737731934</v>
       </c>
       <c r="F13">
-        <v>35.48930358886719</v>
+        <v>35.43852615356445</v>
       </c>
       <c r="G13">
-        <v>22.27705574035645</v>
+        <v>22.27706718444824</v>
       </c>
       <c r="H13">
         <v>1.202000021934509</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1">
+    <row r="14">
+      <c r="A14" s="2">
         <v>37591</v>
       </c>
       <c r="B14">
         <v>879.8200073242188</v>
       </c>
       <c r="C14">
-        <v>4.030003070831299</v>
+        <v>4.030004024505615</v>
       </c>
       <c r="D14">
-        <v>15.72061061859131</v>
+        <v>15.69107913970947</v>
       </c>
       <c r="E14">
-        <v>8.575140953063965</v>
+        <v>8.575139045715332</v>
       </c>
       <c r="F14">
-        <v>32.99518585205078</v>
+        <v>32.94796752929688</v>
       </c>
       <c r="G14">
-        <v>22.64864349365234</v>
+        <v>22.64864921569824</v>
       </c>
       <c r="H14">
         <v>1.182000041007996</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1">
+    <row r="15">
+      <c r="A15" s="2">
         <v>37622</v>
       </c>
       <c r="B15">
@@ -765,65 +752,65 @@
         <v>3.989355802536011</v>
       </c>
       <c r="D15">
-        <v>14.43135261535645</v>
+        <v>14.40422534942627</v>
       </c>
       <c r="E15">
-        <v>9.551752090454102</v>
+        <v>9.551749229431152</v>
       </c>
       <c r="F15">
-        <v>31.30124855041504</v>
+        <v>31.25647163391113</v>
       </c>
       <c r="G15">
-        <v>22.65914916992188</v>
+        <v>22.65915489196777</v>
       </c>
       <c r="H15">
         <v>1.148000001907349</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1">
+    <row r="16">
+      <c r="A16" s="2">
         <v>37653</v>
       </c>
       <c r="B16">
         <v>841.1500244140625</v>
       </c>
       <c r="C16">
-        <v>3.643407106399536</v>
+        <v>3.643405199050903</v>
       </c>
       <c r="D16">
-        <v>14.45944690704346</v>
+        <v>14.43227195739746</v>
       </c>
       <c r="E16">
-        <v>9.496172904968262</v>
+        <v>9.496173858642578</v>
       </c>
       <c r="F16">
-        <v>29.55398750305176</v>
+        <v>29.51170921325684</v>
       </c>
       <c r="G16">
-        <v>21.67673873901367</v>
+        <v>21.67673683166504</v>
       </c>
       <c r="H16">
         <v>1.174999952316284</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1">
+    <row r="17">
+      <c r="A17" s="2">
         <v>37681</v>
       </c>
       <c r="B17">
         <v>848.1799926757812</v>
       </c>
       <c r="C17">
-        <v>3.293081521987915</v>
+        <v>3.293079614639282</v>
       </c>
       <c r="D17">
-        <v>14.77059173583984</v>
+        <v>14.742844581604</v>
       </c>
       <c r="E17">
-        <v>8.614838600158691</v>
+        <v>8.614842414855957</v>
       </c>
       <c r="F17">
-        <v>29.86226844787598</v>
+        <v>29.81955146789551</v>
       </c>
       <c r="G17">
         <v>23.58066558837891</v>
@@ -832,76 +819,76 @@
         <v>1.090000033378601</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="1">
+    <row r="18">
+      <c r="A18" s="2">
         <v>37712</v>
       </c>
       <c r="B18">
         <v>916.9199829101562</v>
       </c>
       <c r="C18">
-        <v>4.554603576660156</v>
+        <v>4.55460262298584</v>
       </c>
       <c r="D18">
-        <v>15.6003360748291</v>
+        <v>15.57102203369141</v>
       </c>
       <c r="E18">
-        <v>9.432657241821289</v>
+        <v>9.432653427124023</v>
       </c>
       <c r="F18">
-        <v>33.34750747680664</v>
+        <v>33.2997932434082</v>
       </c>
       <c r="G18">
-        <v>23.90145492553711</v>
+        <v>23.90144920349121</v>
       </c>
       <c r="H18">
         <v>1.10099995136261</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1">
+    <row r="19">
+      <c r="A19" s="2">
         <v>37742</v>
       </c>
       <c r="B19">
         <v>963.5900268554688</v>
       </c>
       <c r="C19">
-        <v>4.64304256439209</v>
+        <v>4.643041133880615</v>
       </c>
       <c r="D19">
-        <v>15.01464748382568</v>
+        <v>14.98642349243164</v>
       </c>
       <c r="E19">
-        <v>10.32986927032471</v>
+        <v>10.32986640930176</v>
       </c>
       <c r="F19">
-        <v>31.3946704864502</v>
+        <v>31.34975624084473</v>
       </c>
       <c r="G19">
-        <v>24.42550468444824</v>
+        <v>24.42550086975098</v>
       </c>
       <c r="H19">
         <v>1.085000038146973</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="1">
+    <row r="20">
+      <c r="A20" s="2">
         <v>37773</v>
       </c>
       <c r="B20">
         <v>974.5</v>
       </c>
       <c r="C20">
-        <v>4.859717845916748</v>
+        <v>4.859715938568115</v>
       </c>
       <c r="D20">
-        <v>15.64304351806641</v>
+        <v>15.61365413665771</v>
       </c>
       <c r="E20">
-        <v>9.535872459411621</v>
+        <v>9.535871505737305</v>
       </c>
       <c r="F20">
-        <v>36.22704315185547</v>
+        <v>36.17521286010742</v>
       </c>
       <c r="G20">
         <v>23.72322273254395</v>
@@ -910,112 +897,112 @@
         <v>0.8379999995231628</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="1">
+    <row r="21">
+      <c r="A21" s="2">
         <v>37803</v>
       </c>
       <c r="B21">
         <v>990.3099975585938</v>
       </c>
       <c r="C21">
-        <v>4.936251640319824</v>
+        <v>4.936249732971191</v>
       </c>
       <c r="D21">
-        <v>16.11282730102539</v>
+        <v>16.08255195617676</v>
       </c>
       <c r="E21">
-        <v>9.51999568939209</v>
+        <v>9.519996643066406</v>
       </c>
       <c r="F21">
-        <v>34.58300018310547</v>
+        <v>34.53350448608398</v>
       </c>
       <c r="G21">
-        <v>23.49519348144531</v>
+        <v>23.49519920349121</v>
       </c>
       <c r="H21">
         <v>0.9269999861717224</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="1">
+    <row r="22">
+      <c r="A22" s="2">
         <v>37834</v>
       </c>
       <c r="B22">
         <v>1008.010009765625</v>
       </c>
       <c r="C22">
-        <v>5.159407138824463</v>
+        <v>5.159408092498779</v>
       </c>
       <c r="D22">
-        <v>16.1799430847168</v>
+        <v>16.14953422546387</v>
       </c>
       <c r="E22">
-        <v>10.18694877624512</v>
+        <v>10.18695068359375</v>
       </c>
       <c r="F22">
-        <v>35.13259506225586</v>
+        <v>35.08232498168945</v>
       </c>
       <c r="G22">
-        <v>23.34011650085449</v>
+        <v>23.34011077880859</v>
       </c>
       <c r="H22">
         <v>0.9599999785423279</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="1">
+    <row r="23">
+      <c r="A23" s="2">
         <v>37865</v>
       </c>
       <c r="B23">
         <v>995.969970703125</v>
       </c>
       <c r="C23">
-        <v>4.806817531585693</v>
+        <v>4.806818962097168</v>
       </c>
       <c r="D23">
-        <v>16.96087074279785</v>
+        <v>16.92900276184082</v>
       </c>
       <c r="E23">
-        <v>8.932435035705566</v>
+        <v>8.93243408203125</v>
       </c>
       <c r="F23">
-        <v>31.36745643615723</v>
+        <v>31.32254791259766</v>
       </c>
       <c r="G23">
-        <v>24.81876373291016</v>
+        <v>24.81875991821289</v>
       </c>
       <c r="H23">
         <v>0.9259999990463257</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="1">
+    <row r="24">
+      <c r="A24" s="2">
         <v>37895</v>
       </c>
       <c r="B24">
         <v>1050.7099609375</v>
       </c>
       <c r="C24">
-        <v>5.457821846008301</v>
+        <v>5.457823276519775</v>
       </c>
       <c r="D24">
-        <v>16.03756904602051</v>
+        <v>16.00742721557617</v>
       </c>
       <c r="E24">
         <v>9.504116058349609</v>
       </c>
       <c r="F24">
-        <v>35.18011093139648</v>
+        <v>35.12978744506836</v>
       </c>
       <c r="G24">
-        <v>26.40688896179199</v>
+        <v>26.40688323974609</v>
       </c>
       <c r="H24">
         <v>0.9319999814033508</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1">
+    <row r="25">
+      <c r="A25" s="2">
         <v>37926</v>
       </c>
       <c r="B25">
@@ -1025,143 +1012,143 @@
         <v>5.939262390136719</v>
       </c>
       <c r="D25">
-        <v>15.77374744415283</v>
+        <v>15.74410820007324</v>
       </c>
       <c r="E25">
-        <v>9.543810844421387</v>
+        <v>9.54381275177002</v>
       </c>
       <c r="F25">
-        <v>36.51945877075195</v>
+        <v>36.46720123291016</v>
       </c>
       <c r="G25">
-        <v>25.85611724853516</v>
+        <v>25.85612678527832</v>
       </c>
       <c r="H25">
         <v>0.9079999923706055</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="1">
+    <row r="26">
+      <c r="A26" s="2">
         <v>37956</v>
       </c>
       <c r="B26">
         <v>1111.920043945312</v>
       </c>
       <c r="C26">
-        <v>7.199107646942139</v>
+        <v>7.199105262756348</v>
       </c>
       <c r="D26">
-        <v>16.79220008850098</v>
+        <v>16.76065635681152</v>
       </c>
       <c r="E26">
-        <v>10.50454235076904</v>
+        <v>10.50454807281494</v>
       </c>
       <c r="F26">
-        <v>37.33158874511719</v>
+        <v>37.27816390991211</v>
       </c>
       <c r="G26">
-        <v>26.83406829833984</v>
+        <v>26.83405494689941</v>
       </c>
       <c r="H26">
         <v>0.9070000052452087</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="1">
+    <row r="27">
+      <c r="A27" s="2">
         <v>37987</v>
       </c>
       <c r="B27">
         <v>1131.130004882812</v>
       </c>
       <c r="C27">
-        <v>6.583490371704102</v>
+        <v>6.583489418029785</v>
       </c>
       <c r="D27">
-        <v>16.96399879455566</v>
+        <v>16.9321231842041</v>
       </c>
       <c r="E27">
-        <v>11.00475883483887</v>
+        <v>11.00476264953613</v>
       </c>
       <c r="F27">
-        <v>36.11604690551758</v>
+        <v>36.06435775756836</v>
       </c>
       <c r="G27">
-        <v>27.28226661682129</v>
+        <v>27.28225898742676</v>
       </c>
       <c r="H27">
         <v>0.8970000147819519</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="1">
+    <row r="28">
+      <c r="A28" s="2">
         <v>38018</v>
       </c>
       <c r="B28">
         <v>1144.93994140625</v>
       </c>
       <c r="C28">
-        <v>6.225789546966553</v>
+        <v>6.225789070129395</v>
       </c>
       <c r="D28">
-        <v>16.27684593200684</v>
+        <v>16.24626541137695</v>
       </c>
       <c r="E28">
-        <v>10.21870994567871</v>
+        <v>10.21870708465576</v>
       </c>
       <c r="F28">
-        <v>39.43560028076172</v>
+        <v>39.37916946411133</v>
       </c>
       <c r="G28">
-        <v>27.6682186126709</v>
+        <v>27.6682300567627</v>
       </c>
       <c r="H28">
         <v>0.9269999861717224</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="1">
+    <row r="29">
+      <c r="A29" s="2">
         <v>38047</v>
       </c>
       <c r="B29">
         <v>1126.2099609375</v>
       </c>
       <c r="C29">
-        <v>6.144287109375</v>
+        <v>6.144286155700684</v>
       </c>
       <c r="D29">
-        <v>15.29520416259766</v>
+        <v>15.26646137237549</v>
       </c>
       <c r="E29">
-        <v>9.527931213378906</v>
+        <v>9.527933120727539</v>
       </c>
       <c r="F29">
-        <v>35.68085098266602</v>
+        <v>35.62979888916016</v>
       </c>
       <c r="G29">
-        <v>28.30791091918945</v>
+        <v>28.30790519714355</v>
       </c>
       <c r="H29">
         <v>0.9229999780654907</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="1">
+    <row r="30">
+      <c r="A30" s="2">
         <v>38078</v>
       </c>
       <c r="B30">
         <v>1107.300048828125</v>
       </c>
       <c r="C30">
-        <v>6.998429298400879</v>
+        <v>6.998431205749512</v>
       </c>
       <c r="D30">
-        <v>16.03143501281738</v>
+        <v>16.00130653381348</v>
       </c>
       <c r="E30">
-        <v>8.932435035705566</v>
+        <v>8.93243408203125</v>
       </c>
       <c r="F30">
-        <v>39.36627960205078</v>
+        <v>39.30992889404297</v>
       </c>
       <c r="G30">
         <v>28.6906566619873</v>
@@ -1170,128 +1157,128 @@
         <v>0.9520000219345093</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="1">
+    <row r="31">
+      <c r="A31" s="2">
         <v>38108</v>
       </c>
       <c r="B31">
         <v>1120.680053710938</v>
       </c>
       <c r="C31">
-        <v>6.76606273651123</v>
+        <v>6.766060352325439</v>
       </c>
       <c r="D31">
-        <v>16.09278869628906</v>
+        <v>16.06254386901855</v>
       </c>
       <c r="E31">
-        <v>9.051535606384277</v>
+        <v>9.051539421081543</v>
       </c>
       <c r="F31">
-        <v>39.48138427734375</v>
+        <v>39.42488861083984</v>
       </c>
       <c r="G31">
-        <v>29.2411994934082</v>
+        <v>29.2411937713623</v>
       </c>
       <c r="H31">
         <v>1.052000045776367</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="1">
+    <row r="32">
+      <c r="A32" s="2">
         <v>38139</v>
       </c>
       <c r="B32">
         <v>1140.839965820312</v>
       </c>
       <c r="C32">
-        <v>7.130561828613281</v>
+        <v>7.130565166473389</v>
       </c>
       <c r="D32">
-        <v>17.52230644226074</v>
+        <v>17.48937797546387</v>
       </c>
       <c r="E32">
-        <v>9.472352027893066</v>
+        <v>9.472357749938965</v>
       </c>
       <c r="F32">
-        <v>37.46630477905273</v>
+        <v>37.41272735595703</v>
       </c>
       <c r="G32">
-        <v>29.52869033813477</v>
+        <v>29.5286808013916</v>
       </c>
       <c r="H32">
         <v>1.302999973297119</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="1">
+    <row r="33">
+      <c r="A33" s="2">
         <v>38169</v>
       </c>
       <c r="B33">
         <v>1101.719970703125</v>
       </c>
       <c r="C33">
-        <v>6.752206325531006</v>
+        <v>6.752205848693848</v>
       </c>
       <c r="D33">
-        <v>17.4793529510498</v>
+        <v>17.44650650024414</v>
       </c>
       <c r="E33">
-        <v>8.344877243041992</v>
+        <v>8.344880104064941</v>
       </c>
       <c r="F33">
-        <v>34.14894485473633</v>
+        <v>34.10009384155273</v>
       </c>
       <c r="G33">
-        <v>28.41692543029785</v>
+        <v>28.41691207885742</v>
       </c>
       <c r="H33">
         <v>1.411999940872192</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="1">
+    <row r="34">
+      <c r="A34" s="2">
         <v>38200</v>
       </c>
       <c r="B34">
         <v>1104.239990234375</v>
       </c>
       <c r="C34">
-        <v>6.47239351272583</v>
+        <v>6.472393989562988</v>
       </c>
       <c r="D34">
-        <v>16.79866409301758</v>
+        <v>16.76711082458496</v>
       </c>
       <c r="E34">
-        <v>7.916122913360596</v>
+        <v>7.916123867034912</v>
       </c>
       <c r="F34">
-        <v>34.20310211181641</v>
+        <v>34.15416717529297</v>
       </c>
       <c r="G34">
-        <v>30.49845695495605</v>
+        <v>30.49845886230469</v>
       </c>
       <c r="H34">
         <v>1.567999958992004</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="1">
+    <row r="35">
+      <c r="A35" s="2">
         <v>38231</v>
       </c>
       <c r="B35">
         <v>1114.579956054688</v>
       </c>
       <c r="C35">
-        <v>6.444869995117188</v>
+        <v>6.44487190246582</v>
       </c>
       <c r="D35">
-        <v>17.01403617858887</v>
+        <v>16.98206329345703</v>
       </c>
       <c r="E35">
-        <v>8.956254959106445</v>
+        <v>8.956254005432129</v>
       </c>
       <c r="F35">
-        <v>32.37033081054688</v>
+        <v>32.32402038574219</v>
       </c>
       <c r="G35">
         <v>29.49037551879883</v>
@@ -1300,8 +1287,8 @@
         <v>1.674000024795532</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="1">
+    <row r="36">
+      <c r="A36" s="2">
         <v>38261</v>
       </c>
       <c r="B36">
@@ -1311,351 +1298,351 @@
         <v>6.022823333740234</v>
       </c>
       <c r="D36">
-        <v>17.21093940734863</v>
+        <v>17.17860412597656</v>
       </c>
       <c r="E36">
         <v>10.05196762084961</v>
       </c>
       <c r="F36">
-        <v>29.59958457946777</v>
+        <v>29.55721092224121</v>
       </c>
       <c r="G36">
-        <v>28.02054405212402</v>
+        <v>28.0205135345459</v>
       </c>
       <c r="H36">
         <v>1.866999983787537</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="1">
+    <row r="37">
+      <c r="A37" s="2">
         <v>38292</v>
       </c>
       <c r="B37">
         <v>1173.819946289062</v>
       </c>
       <c r="C37">
-        <v>6.554384231567383</v>
+        <v>6.554383754730225</v>
       </c>
       <c r="D37">
-        <v>18.38674545288086</v>
+        <v>18.35220146179199</v>
       </c>
       <c r="E37">
-        <v>10.11548709869385</v>
+        <v>10.11549186706543</v>
       </c>
       <c r="F37">
-        <v>28.92953491210938</v>
+        <v>28.88814353942871</v>
       </c>
       <c r="G37">
-        <v>29.27974891662598</v>
+        <v>29.27974700927734</v>
       </c>
       <c r="H37">
         <v>2.181999921798706</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="1">
+    <row r="38">
+      <c r="A38" s="2">
         <v>38322</v>
       </c>
       <c r="B38">
         <v>1211.920043945312</v>
       </c>
       <c r="C38">
-        <v>6.767008781433105</v>
+        <v>6.767008304595947</v>
       </c>
       <c r="D38">
-        <v>18.32502746582031</v>
+        <v>18.29058647155762</v>
       </c>
       <c r="E38">
-        <v>10.89360523223877</v>
+        <v>10.89360809326172</v>
       </c>
       <c r="F38">
-        <v>30.7847728729248</v>
+        <v>30.74070739746094</v>
       </c>
       <c r="G38">
-        <v>30.15574264526367</v>
+        <v>30.15573120117188</v>
       </c>
       <c r="H38">
         <v>2.181999921798706</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="1">
+    <row r="39">
+      <c r="A39" s="2">
         <v>38353</v>
       </c>
       <c r="B39">
         <v>1181.27001953125</v>
       </c>
       <c r="C39">
-        <v>6.13389778137207</v>
+        <v>6.133896350860596</v>
       </c>
       <c r="D39">
-        <v>18.02326202392578</v>
+        <v>17.98940086364746</v>
       </c>
       <c r="E39">
-        <v>10.93330001831055</v>
+        <v>10.9333028793335</v>
       </c>
       <c r="F39">
-        <v>29.42317390441895</v>
+        <v>29.38108062744141</v>
       </c>
       <c r="G39">
-        <v>29.27359390258789</v>
+        <v>29.27358436584473</v>
       </c>
       <c r="H39">
         <v>2.421999931335449</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="1">
+    <row r="40">
+      <c r="A40" s="2">
         <v>38384</v>
       </c>
       <c r="B40">
         <v>1203.599975585938</v>
       </c>
       <c r="C40">
-        <v>5.891711711883545</v>
+        <v>5.891707897186279</v>
       </c>
       <c r="D40">
-        <v>17.30838966369629</v>
+        <v>17.27585983276367</v>
       </c>
       <c r="E40">
-        <v>10.28222560882568</v>
+        <v>10.28222942352295</v>
       </c>
       <c r="F40">
-        <v>30.59003639221191</v>
+        <v>30.5462646484375</v>
       </c>
       <c r="G40">
-        <v>29.19660377502441</v>
+        <v>29.19659233093262</v>
       </c>
       <c r="H40">
         <v>2.690000057220459</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="1">
+    <row r="41">
+      <c r="A41" s="2">
         <v>38412</v>
       </c>
       <c r="B41">
         <v>1180.589965820312</v>
       </c>
       <c r="C41">
-        <v>5.276921272277832</v>
+        <v>5.276924133300781</v>
       </c>
       <c r="D41">
-        <v>16.62733268737793</v>
+        <v>16.59609413146973</v>
       </c>
       <c r="E41">
-        <v>9.90904712677002</v>
+        <v>9.909048080444336</v>
       </c>
       <c r="F41">
-        <v>28.45966720581055</v>
+        <v>28.4189338684082</v>
       </c>
       <c r="G41">
-        <v>29.1471004486084</v>
+        <v>29.14710807800293</v>
       </c>
       <c r="H41">
         <v>2.721999883651733</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="1">
+    <row r="42">
+      <c r="A42" s="2">
         <v>38443</v>
       </c>
       <c r="B42">
         <v>1156.849975585938</v>
       </c>
       <c r="C42">
-        <v>4.288390159606934</v>
+        <v>4.288389682769775</v>
       </c>
       <c r="D42">
-        <v>17.40469551086426</v>
+        <v>17.37199592590332</v>
       </c>
       <c r="E42">
-        <v>9.17857837677002</v>
+        <v>9.178574562072754</v>
       </c>
       <c r="F42">
-        <v>31.93927574157715</v>
+        <v>31.8935661315918</v>
       </c>
       <c r="G42">
-        <v>29.93379974365234</v>
+        <v>29.93381500244141</v>
       </c>
       <c r="H42">
         <v>2.836999893188477</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="1">
+    <row r="43">
+      <c r="A43" s="2">
         <v>38473</v>
       </c>
       <c r="B43">
         <v>1191.5</v>
       </c>
       <c r="C43">
-        <v>4.697928905487061</v>
+        <v>4.697929382324219</v>
       </c>
       <c r="D43">
-        <v>17.80496215820312</v>
+        <v>17.77150535583496</v>
       </c>
       <c r="E43">
-        <v>10.16312503814697</v>
+        <v>10.16312980651855</v>
       </c>
       <c r="F43">
-        <v>32.05239105224609</v>
+        <v>32.00651931762695</v>
       </c>
       <c r="G43">
-        <v>30.48660850524902</v>
+        <v>30.48661231994629</v>
       </c>
       <c r="H43">
         <v>2.881999969482422</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="1">
+    <row r="44">
+      <c r="A44" s="2">
         <v>38504</v>
       </c>
       <c r="B44">
         <v>1191.329956054688</v>
       </c>
       <c r="C44">
-        <v>4.820321559906006</v>
+        <v>4.820320129394531</v>
       </c>
       <c r="D44">
-        <v>17.1424503326416</v>
+        <v>17.1102409362793</v>
       </c>
       <c r="E44">
-        <v>10.48072624206543</v>
+        <v>10.48072338104248</v>
       </c>
       <c r="F44">
-        <v>30.62845611572266</v>
+        <v>30.58464050292969</v>
       </c>
       <c r="G44">
-        <v>29.1599006652832</v>
+        <v>29.1599063873291</v>
       </c>
       <c r="H44">
         <v>3.059999942779541</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="1">
+    <row r="45">
+      <c r="A45" s="2">
         <v>38534</v>
       </c>
       <c r="B45">
         <v>1234.180053710938</v>
       </c>
       <c r="C45">
-        <v>5.102497577667236</v>
+        <v>5.102499485015869</v>
       </c>
       <c r="D45">
-        <v>17.67384147644043</v>
+        <v>17.64063453674316</v>
       </c>
       <c r="E45">
-        <v>10.77450180053711</v>
+        <v>10.77450466156006</v>
       </c>
       <c r="F45">
-        <v>30.96383285522461</v>
+        <v>30.91951560974121</v>
       </c>
       <c r="G45">
-        <v>30.90964508056641</v>
+        <v>30.90966033935547</v>
       </c>
       <c r="H45">
         <v>3.332000017166138</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="1">
+    <row r="46">
+      <c r="A46" s="2">
         <v>38565</v>
       </c>
       <c r="B46">
         <v>1220.329956054688</v>
       </c>
       <c r="C46">
-        <v>4.736678123474121</v>
+        <v>4.736678600311279</v>
       </c>
       <c r="D46">
-        <v>18.95138740539551</v>
+        <v>18.91578102111816</v>
       </c>
       <c r="E46">
-        <v>10.31398677825928</v>
+        <v>10.31398963928223</v>
       </c>
       <c r="F46">
-        <v>30.46388053894043</v>
+        <v>30.42028999328613</v>
       </c>
       <c r="G46">
-        <v>30.82631874084473</v>
+        <v>30.82631492614746</v>
       </c>
       <c r="H46">
         <v>3.430000066757202</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="1">
+    <row r="47">
+      <c r="A47" s="2">
         <v>38596</v>
       </c>
       <c r="B47">
         <v>1228.81005859375</v>
       </c>
       <c r="C47">
-        <v>4.6844162940979</v>
+        <v>4.684418201446533</v>
       </c>
       <c r="D47">
-        <v>17.8093204498291</v>
+        <v>17.77586555480957</v>
       </c>
       <c r="E47">
-        <v>9.84553050994873</v>
+        <v>9.845528602600098</v>
       </c>
       <c r="F47">
-        <v>29.63333320617676</v>
+        <v>29.5909481048584</v>
       </c>
       <c r="G47">
-        <v>33.03771209716797</v>
+        <v>33.03770065307617</v>
       </c>
       <c r="H47">
         <v>3.470000028610229</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="1">
+    <row r="48">
+      <c r="A48" s="2">
         <v>38626</v>
       </c>
       <c r="B48">
         <v>1207.010009765625</v>
       </c>
       <c r="C48">
-        <v>4.001936912536621</v>
+        <v>4.001935958862305</v>
       </c>
       <c r="D48">
-        <v>17.78856086730957</v>
+        <v>17.7551326751709</v>
       </c>
       <c r="E48">
-        <v>10.06785202026367</v>
+        <v>10.06784629821777</v>
       </c>
       <c r="F48">
-        <v>27.56810188293457</v>
+        <v>27.52865219116211</v>
       </c>
       <c r="G48">
-        <v>31.26785659790039</v>
+        <v>31.26784706115723</v>
       </c>
       <c r="H48">
         <v>3.805000066757202</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="1">
+    <row r="49">
+      <c r="A49" s="2">
         <v>38657</v>
       </c>
       <c r="B49">
         <v>1249.47998046875</v>
       </c>
       <c r="C49">
-        <v>3.910547733306885</v>
+        <v>3.910547971725464</v>
       </c>
       <c r="D49">
-        <v>19.21520233154297</v>
+        <v>19.17910194396973</v>
       </c>
       <c r="E49">
         <v>10.00432872772217</v>
       </c>
       <c r="F49">
-        <v>28.16692352294922</v>
+        <v>28.12662124633789</v>
       </c>
       <c r="G49">
         <v>31.93800163269043</v>
@@ -1664,294 +1651,294 @@
         <v>3.857000112533569</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="1">
+    <row r="50">
+      <c r="A50" s="2">
         <v>38687</v>
       </c>
       <c r="B50">
         <v>1248.2900390625</v>
       </c>
       <c r="C50">
-        <v>3.713336706161499</v>
+        <v>3.713337182998657</v>
       </c>
       <c r="D50">
-        <v>18.15309524536133</v>
+        <v>18.11897850036621</v>
       </c>
       <c r="E50">
         <v>9.694667816162109</v>
       </c>
       <c r="F50">
-        <v>31.56368064880371</v>
+        <v>31.51853179931641</v>
       </c>
       <c r="G50">
-        <v>32.32332992553711</v>
+        <v>32.32333755493164</v>
       </c>
       <c r="H50">
         <v>3.984999895095825</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="1">
+    <row r="51">
+      <c r="A51" s="2">
         <v>38718</v>
       </c>
       <c r="B51">
         <v>1280.079956054688</v>
       </c>
       <c r="C51">
-        <v>4.175437450408936</v>
+        <v>4.175439834594727</v>
       </c>
       <c r="D51">
-        <v>19.54147720336914</v>
+        <v>19.50475692749023</v>
       </c>
       <c r="E51">
-        <v>9.980508804321289</v>
+        <v>9.980511665344238</v>
       </c>
       <c r="F51">
-        <v>31.58042907714844</v>
+        <v>31.53524971008301</v>
       </c>
       <c r="G51">
-        <v>33.23591232299805</v>
+        <v>33.23591995239258</v>
       </c>
       <c r="H51">
         <v>4.369999885559082</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="1">
+    <row r="52">
+      <c r="A52" s="2">
         <v>38749</v>
       </c>
       <c r="B52">
         <v>1280.660034179688</v>
       </c>
       <c r="C52">
-        <v>3.878581285476685</v>
+        <v>3.878582000732422</v>
       </c>
       <c r="D52">
-        <v>18.71612358093262</v>
+        <v>18.68095016479492</v>
       </c>
       <c r="E52">
-        <v>9.861413955688477</v>
+        <v>9.861409187316895</v>
       </c>
       <c r="F52">
-        <v>31.24513816833496</v>
+        <v>31.20041275024414</v>
       </c>
       <c r="G52">
-        <v>33.62871170043945</v>
+        <v>33.62872314453125</v>
       </c>
       <c r="H52">
         <v>4.506999969482422</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="1">
+    <row r="53">
+      <c r="A53" s="2">
         <v>38777</v>
       </c>
       <c r="B53">
         <v>1294.869995117188</v>
       </c>
       <c r="C53">
-        <v>3.873716115951538</v>
+        <v>3.873717308044434</v>
       </c>
       <c r="D53">
-        <v>18.95293807983398</v>
+        <v>18.91732788085938</v>
       </c>
       <c r="E53">
-        <v>10.86978054046631</v>
+        <v>10.86978340148926</v>
       </c>
       <c r="F53">
-        <v>31.06536102294922</v>
+        <v>31.02093124389648</v>
       </c>
       <c r="G53">
-        <v>32.33810424804688</v>
+        <v>32.33810806274414</v>
       </c>
       <c r="H53">
         <v>4.514999866485596</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="1">
+    <row r="54">
+      <c r="A54" s="2">
         <v>38808</v>
       </c>
       <c r="B54">
         <v>1310.609985351562</v>
       </c>
       <c r="C54">
-        <v>3.429837465286255</v>
+        <v>3.429838180541992</v>
       </c>
       <c r="D54">
-        <v>16.82151794433594</v>
+        <v>16.78990745544434</v>
       </c>
       <c r="E54">
-        <v>11.58437442779541</v>
+        <v>11.58437919616699</v>
       </c>
       <c r="F54">
-        <v>29.72837829589844</v>
+        <v>29.68582344055176</v>
       </c>
       <c r="G54">
-        <v>32.84485626220703</v>
+        <v>32.8448600769043</v>
       </c>
       <c r="H54">
         <v>4.650000095367432</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="1">
+    <row r="55">
+      <c r="A55" s="2">
         <v>38838</v>
       </c>
       <c r="B55">
         <v>1270.089965820312</v>
       </c>
       <c r="C55">
-        <v>3.53347373008728</v>
+        <v>3.533473014831543</v>
       </c>
       <c r="D55">
-        <v>15.83822154998779</v>
+        <v>15.80846309661865</v>
       </c>
       <c r="E55">
-        <v>11.29060077667236</v>
+        <v>11.29059982299805</v>
       </c>
       <c r="F55">
-        <v>29.23393821716309</v>
+        <v>29.19210815429688</v>
       </c>
       <c r="G55">
-        <v>30.61044311523438</v>
+        <v>30.61043930053711</v>
       </c>
       <c r="H55">
         <v>4.715000152587891</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="1">
+    <row r="56">
+      <c r="A56" s="2">
         <v>38869</v>
       </c>
       <c r="B56">
         <v>1270.199951171875</v>
       </c>
       <c r="C56">
-        <v>3.419968605041504</v>
+        <v>3.419968843460083</v>
       </c>
       <c r="D56">
-        <v>16.29274559020996</v>
+        <v>16.26213264465332</v>
       </c>
       <c r="E56">
-        <v>11.50498008728027</v>
+        <v>11.50498199462891</v>
       </c>
       <c r="F56">
-        <v>31.28892135620117</v>
+        <v>31.24414825439453</v>
       </c>
       <c r="G56">
-        <v>31.37216758728027</v>
+        <v>31.37216949462891</v>
       </c>
       <c r="H56">
         <v>4.860000133514404</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="1">
+    <row r="57">
+      <c r="A57" s="2">
         <v>38899</v>
       </c>
       <c r="B57">
         <v>1276.660034179688</v>
       </c>
       <c r="C57">
-        <v>3.31571888923645</v>
+        <v>3.315720081329346</v>
       </c>
       <c r="D57">
-        <v>16.82418632507324</v>
+        <v>16.79256820678711</v>
       </c>
       <c r="E57">
-        <v>11.88609790802002</v>
+        <v>11.8860969543457</v>
       </c>
       <c r="F57">
-        <v>32.13808441162109</v>
+        <v>32.09209442138672</v>
       </c>
       <c r="G57">
-        <v>31.88784217834473</v>
+        <v>31.88785743713379</v>
       </c>
       <c r="H57">
         <v>4.934999942779541</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="1">
+    <row r="58">
+      <c r="A58" s="2">
         <v>38930</v>
       </c>
       <c r="B58">
         <v>1303.819946289062</v>
       </c>
       <c r="C58">
-        <v>4.160804271697998</v>
+        <v>4.16080379486084</v>
       </c>
       <c r="D58">
-        <v>18.03714370727539</v>
+        <v>18.00324821472168</v>
       </c>
       <c r="E58">
         <v>12.4339542388916</v>
       </c>
       <c r="F58">
-        <v>31.8932991027832</v>
+        <v>31.8476505279541</v>
       </c>
       <c r="G58">
-        <v>35.12202072143555</v>
+        <v>35.12203598022461</v>
       </c>
       <c r="H58">
         <v>4.90500020980835</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="1">
+    <row r="59">
+      <c r="A59" s="2">
         <v>38961</v>
       </c>
       <c r="B59">
         <v>1335.849975585938</v>
       </c>
       <c r="C59">
-        <v>4.021614551544189</v>
+        <v>4.021615028381348</v>
       </c>
       <c r="D59">
-        <v>19.19516563415527</v>
+        <v>19.15910148620605</v>
       </c>
       <c r="E59">
-        <v>14.08545970916748</v>
+        <v>14.0854549407959</v>
       </c>
       <c r="F59">
-        <v>32.50344467163086</v>
+        <v>32.45692825317383</v>
       </c>
       <c r="G59">
-        <v>35.16742324829102</v>
+        <v>35.16742706298828</v>
       </c>
       <c r="H59">
         <v>4.760000228881836</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="1">
+    <row r="60">
+      <c r="A60" s="2">
         <v>38991</v>
       </c>
       <c r="B60">
         <v>1377.93994140625</v>
       </c>
       <c r="C60">
-        <v>4.11606502532959</v>
+        <v>4.116064071655273</v>
       </c>
       <c r="D60">
-        <v>20.14965629577637</v>
+        <v>20.11180305480957</v>
       </c>
       <c r="E60">
-        <v>14.66507530212402</v>
+        <v>14.66508197784424</v>
       </c>
       <c r="F60">
-        <v>31.93891906738281</v>
+        <v>31.89320373535156</v>
       </c>
       <c r="G60">
-        <v>36.14745330810547</v>
+        <v>36.1474609375</v>
       </c>
       <c r="H60">
         <v>4.940000057220459</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="1">
+    <row r="61">
+      <c r="A61" s="2">
         <v>39022</v>
       </c>
       <c r="B61">
@@ -1961,49 +1948,49 @@
         <v>4.041499137878418</v>
       </c>
       <c r="D61">
-        <v>20.67630195617676</v>
+        <v>20.637451171875</v>
       </c>
       <c r="E61">
-        <v>15.1255931854248</v>
+        <v>15.12558460235596</v>
       </c>
       <c r="F61">
-        <v>30.78639602661133</v>
+        <v>30.74233436584473</v>
       </c>
       <c r="G61">
-        <v>35.80532073974609</v>
+        <v>35.80532455444336</v>
       </c>
       <c r="H61">
         <v>4.889999866485596</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="1">
+    <row r="62">
+      <c r="A62" s="2">
         <v>39052</v>
       </c>
       <c r="B62">
         <v>1418.300048828125</v>
       </c>
       <c r="C62">
-        <v>3.7332923412323</v>
+        <v>3.733290672302246</v>
       </c>
       <c r="D62">
-        <v>21.0284252166748</v>
+        <v>20.9889087677002</v>
       </c>
       <c r="E62">
-        <v>13.60905742645264</v>
+        <v>13.6090612411499</v>
       </c>
       <c r="F62">
-        <v>29.93041610717773</v>
+        <v>29.8875789642334</v>
       </c>
       <c r="G62">
-        <v>36.64926910400391</v>
+        <v>36.64925765991211</v>
       </c>
       <c r="H62">
         <v>4.885000228881836</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="1">
+    <row r="63">
+      <c r="A63" s="2">
         <v>39083</v>
       </c>
       <c r="B63">
@@ -2013,65 +2000,65 @@
         <v>4.041499137878418</v>
       </c>
       <c r="D63">
-        <v>21.73266220092773</v>
+        <v>21.69182395935059</v>
       </c>
       <c r="E63">
-        <v>13.62494373321533</v>
+        <v>13.62494277954102</v>
       </c>
       <c r="F63">
-        <v>31.09087181091309</v>
+        <v>31.04637908935547</v>
       </c>
       <c r="G63">
-        <v>37.16868209838867</v>
+        <v>37.16867065429688</v>
       </c>
       <c r="H63">
         <v>4.974999904632568</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="1">
+    <row r="64">
+      <c r="A64" s="2">
         <v>39114</v>
       </c>
       <c r="B64">
         <v>1406.819946289062</v>
       </c>
       <c r="C64">
-        <v>3.932134628295898</v>
+        <v>3.932135105133057</v>
       </c>
       <c r="D64">
-        <v>19.90704917907715</v>
+        <v>19.86965370178223</v>
       </c>
       <c r="E64">
-        <v>13.04533100128174</v>
+        <v>13.04532432556152</v>
       </c>
       <c r="F64">
-        <v>30.44976615905762</v>
+        <v>30.40618324279785</v>
       </c>
       <c r="G64">
-        <v>36.37797164916992</v>
+        <v>36.37798309326172</v>
       </c>
       <c r="H64">
         <v>4.994999885559082</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="1">
+    <row r="65">
+      <c r="A65" s="2">
         <v>39142</v>
       </c>
       <c r="B65">
         <v>1420.859985351562</v>
       </c>
       <c r="C65">
-        <v>3.922192811965942</v>
+        <v>3.922192096710205</v>
       </c>
       <c r="D65">
-        <v>19.69505310058594</v>
+        <v>19.65804481506348</v>
       </c>
       <c r="E65">
-        <v>14.39511966705322</v>
+        <v>14.39511489868164</v>
       </c>
       <c r="F65">
-        <v>31.09824562072754</v>
+        <v>31.05373573303223</v>
       </c>
       <c r="G65">
         <v>36.18889617919922</v>
@@ -2080,76 +2067,76 @@
         <v>4.894999980926514</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="1">
+    <row r="66">
+      <c r="A66" s="2">
         <v>39173</v>
       </c>
       <c r="B66">
         <v>1482.369995117188</v>
       </c>
       <c r="C66">
-        <v>3.996760606765747</v>
+        <v>3.996758937835693</v>
       </c>
       <c r="D66">
-        <v>21.15787696838379</v>
+        <v>21.11812019348145</v>
       </c>
       <c r="E66">
-        <v>14.92709350585938</v>
+        <v>14.92709636688232</v>
       </c>
       <c r="F66">
-        <v>34.23643493652344</v>
+        <v>34.18747329711914</v>
       </c>
       <c r="G66">
-        <v>37.10314559936523</v>
+        <v>37.10315322875977</v>
       </c>
       <c r="H66">
         <v>4.724999904632568</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="1">
+    <row r="67">
+      <c r="A67" s="2">
         <v>39203</v>
       </c>
       <c r="B67">
         <v>1530.619995117188</v>
       </c>
       <c r="C67">
-        <v>4.14589262008667</v>
+        <v>4.145893573760986</v>
       </c>
       <c r="D67">
-        <v>21.75813484191895</v>
+        <v>21.71725463867188</v>
       </c>
       <c r="E67">
-        <v>15.38761520385742</v>
+        <v>15.38761043548584</v>
       </c>
       <c r="F67">
-        <v>34.18864059448242</v>
+        <v>34.13971328735352</v>
       </c>
       <c r="G67">
-        <v>36.61343383789062</v>
+        <v>36.61343002319336</v>
       </c>
       <c r="H67">
         <v>4.590000152587891</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="1">
+    <row r="68">
+      <c r="A68" s="2">
         <v>39234</v>
       </c>
       <c r="B68">
         <v>1503.349975585938</v>
       </c>
       <c r="C68">
-        <v>4.682771682739258</v>
+        <v>4.682770252227783</v>
       </c>
       <c r="D68">
-        <v>20.8931941986084</v>
+        <v>20.85394287109375</v>
       </c>
       <c r="E68">
-        <v>15.64963150024414</v>
+        <v>15.64962863922119</v>
       </c>
       <c r="F68">
-        <v>32.59060287475586</v>
+        <v>32.54396057128906</v>
       </c>
       <c r="G68">
         <v>35.25373840332031</v>
@@ -2158,190 +2145,190 @@
         <v>4.670000076293945</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="1">
+    <row r="69">
+      <c r="A69" s="2">
         <v>39264</v>
       </c>
       <c r="B69">
         <v>1455.27001953125</v>
       </c>
       <c r="C69">
-        <v>4.230400562286377</v>
+        <v>4.230399608612061</v>
       </c>
       <c r="D69">
-        <v>20.55288887023926</v>
+        <v>20.51426887512207</v>
       </c>
       <c r="E69">
-        <v>15.18118095397949</v>
+        <v>15.18117332458496</v>
       </c>
       <c r="F69">
-        <v>31.54662132263184</v>
+        <v>31.50149154663086</v>
       </c>
       <c r="G69">
-        <v>35.83988189697266</v>
+        <v>35.83989715576172</v>
       </c>
       <c r="H69">
         <v>4.809999942779541</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="1">
+    <row r="70">
+      <c r="A70" s="2">
         <v>39295</v>
       </c>
       <c r="B70">
         <v>1473.989990234375</v>
       </c>
       <c r="C70">
-        <v>3.882423639297485</v>
+        <v>3.882423400878906</v>
       </c>
       <c r="D70">
-        <v>20.43995094299316</v>
+        <v>20.40154457092285</v>
       </c>
       <c r="E70">
-        <v>16.10220527648926</v>
+        <v>16.10220718383789</v>
       </c>
       <c r="F70">
-        <v>33.69850540161133</v>
+        <v>33.6502799987793</v>
       </c>
       <c r="G70">
-        <v>37.83872222900391</v>
+        <v>37.83871078491211</v>
       </c>
       <c r="H70">
         <v>3.990000009536743</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="1">
+    <row r="71">
+      <c r="A71" s="2">
         <v>39326</v>
       </c>
       <c r="B71">
         <v>1526.75</v>
       </c>
       <c r="C71">
-        <v>4.220458030700684</v>
+        <v>4.220457553863525</v>
       </c>
       <c r="D71">
-        <v>20.95931625366211</v>
+        <v>20.9199275970459</v>
       </c>
       <c r="E71">
-        <v>17.18997573852539</v>
+        <v>17.18998718261719</v>
       </c>
       <c r="F71">
-        <v>33.45169448852539</v>
+        <v>33.40385437011719</v>
       </c>
       <c r="G71">
-        <v>40.75295257568359</v>
+        <v>40.75297164916992</v>
       </c>
       <c r="H71">
         <v>3.700000047683716</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="1">
+    <row r="72">
+      <c r="A72" s="2">
         <v>39356</v>
       </c>
       <c r="B72">
         <v>1549.380004882812</v>
       </c>
       <c r="C72">
-        <v>4.409360885620117</v>
+        <v>4.409359931945801</v>
       </c>
       <c r="D72">
-        <v>26.1884651184082</v>
+        <v>26.13925361633301</v>
       </c>
       <c r="E72">
-        <v>17.60285568237305</v>
+        <v>17.60284805297852</v>
       </c>
       <c r="F72">
-        <v>31.81820297241211</v>
+        <v>31.77266883850098</v>
       </c>
       <c r="G72">
-        <v>40.4779167175293</v>
+        <v>40.47792816162109</v>
       </c>
       <c r="H72">
         <v>3.819999933242798</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="1">
+    <row r="73">
+      <c r="A73" s="2">
         <v>39387</v>
       </c>
       <c r="B73">
         <v>1481.140014648438</v>
       </c>
       <c r="C73">
-        <v>3.7332923412323</v>
+        <v>3.733290672302246</v>
       </c>
       <c r="D73">
-        <v>23.98373603820801</v>
+        <v>23.93868255615234</v>
       </c>
       <c r="E73">
-        <v>16.0228099822998</v>
+        <v>16.02281188964844</v>
       </c>
       <c r="F73">
-        <v>31.36700439453125</v>
+        <v>31.32212066650391</v>
       </c>
       <c r="G73">
-        <v>43.08640289306641</v>
+        <v>43.08639526367188</v>
       </c>
       <c r="H73">
         <v>3.069999933242798</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="1">
+    <row r="74">
+      <c r="A74" s="2">
         <v>39417</v>
       </c>
       <c r="B74">
         <v>1468.359985351562</v>
       </c>
       <c r="C74">
-        <v>3.34554648399353</v>
+        <v>3.345547199249268</v>
       </c>
       <c r="D74">
-        <v>25.41134643554688</v>
+        <v>25.36360740661621</v>
       </c>
       <c r="E74">
         <v>17.92839431762695</v>
       </c>
       <c r="F74">
-        <v>31.62763786315918</v>
+        <v>31.5824031829834</v>
       </c>
       <c r="G74">
-        <v>42.74868774414062</v>
+        <v>42.74867248535156</v>
       </c>
       <c r="H74">
         <v>3.140000104904175</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="1">
+    <row r="75">
+      <c r="A75" s="2">
         <v>39448</v>
       </c>
       <c r="B75">
         <v>1378.550048828125</v>
       </c>
       <c r="C75">
-        <v>3.300805807113647</v>
+        <v>3.300806283950806</v>
       </c>
       <c r="D75">
-        <v>23.26994514465332</v>
+        <v>23.22622299194336</v>
       </c>
       <c r="E75">
-        <v>16.31658554077148</v>
+        <v>16.31657791137695</v>
       </c>
       <c r="F75">
-        <v>30.44288444519043</v>
+        <v>30.39931297302246</v>
       </c>
       <c r="G75">
-        <v>38.28293609619141</v>
+        <v>38.28294372558594</v>
       </c>
       <c r="H75">
         <v>1.870000004768372</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="1">
+    <row r="76">
+      <c r="A76" s="2">
         <v>39479</v>
       </c>
       <c r="B76">
@@ -2351,23 +2338,23 @@
         <v>3.246124029159546</v>
       </c>
       <c r="D76">
-        <v>19.4908504486084</v>
+        <v>19.45424270629883</v>
       </c>
       <c r="E76">
-        <v>14.92709350585938</v>
+        <v>14.92709636688232</v>
       </c>
       <c r="F76">
-        <v>29.90682029724121</v>
+        <v>29.86401557922363</v>
       </c>
       <c r="G76">
-        <v>38.7276725769043</v>
+        <v>38.72768783569336</v>
       </c>
       <c r="H76">
         <v>1.784999966621399</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="1">
+    <row r="77">
+      <c r="A77" s="2">
         <v>39508</v>
       </c>
       <c r="B77">
@@ -2377,13 +2364,13 @@
         <v>2.843465566635132</v>
       </c>
       <c r="D77">
-        <v>20.33640670776367</v>
+        <v>20.29820251464844</v>
       </c>
       <c r="E77">
-        <v>15.53052997589111</v>
+        <v>15.5305290222168</v>
       </c>
       <c r="F77">
-        <v>30.84551811218262</v>
+        <v>30.80138397216797</v>
       </c>
       <c r="G77">
         <v>41.00405120849609</v>
@@ -2392,50 +2379,50 @@
         <v>1.274999976158142</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="1">
+    <row r="78">
+      <c r="A78" s="2">
         <v>39539</v>
       </c>
       <c r="B78">
         <v>1385.589965820312</v>
       </c>
       <c r="C78">
-        <v>4.106122493743896</v>
+        <v>4.106122970581055</v>
       </c>
       <c r="D78">
-        <v>20.43673515319824</v>
+        <v>20.39833831787109</v>
       </c>
       <c r="E78">
-        <v>16.55478096008301</v>
+        <v>16.55478668212891</v>
       </c>
       <c r="F78">
-        <v>28.78277015686035</v>
+        <v>28.74158096313477</v>
       </c>
       <c r="G78">
-        <v>39.4615478515625</v>
+        <v>39.46155166625977</v>
       </c>
       <c r="H78">
         <v>1.340000033378601</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="1">
+    <row r="79">
+      <c r="A79" s="2">
         <v>39569</v>
       </c>
       <c r="B79">
         <v>1400.380004882812</v>
       </c>
       <c r="C79">
-        <v>3.380343914031982</v>
+        <v>3.380343198776245</v>
       </c>
       <c r="D79">
-        <v>20.36812782287598</v>
+        <v>20.32985877990723</v>
       </c>
       <c r="E79">
-        <v>18.13483619689941</v>
+        <v>18.13483047485352</v>
       </c>
       <c r="F79">
-        <v>29.06290817260742</v>
+        <v>29.02131843566895</v>
       </c>
       <c r="G79">
         <v>38.87300872802734</v>
@@ -2444,102 +2431,102 @@
         <v>1.850000023841858</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="1">
+    <row r="80">
+      <c r="A80" s="2">
         <v>39600</v>
       </c>
       <c r="B80">
         <v>1280</v>
       </c>
       <c r="C80">
-        <v>2.391095876693726</v>
+        <v>2.391095399856567</v>
       </c>
       <c r="D80">
-        <v>19.78556632995605</v>
+        <v>19.74838829040527</v>
       </c>
       <c r="E80">
-        <v>16.67387580871582</v>
+        <v>16.67387199401855</v>
       </c>
       <c r="F80">
-        <v>27.86753845214844</v>
+        <v>27.82767677307129</v>
       </c>
       <c r="G80">
-        <v>35.78906631469727</v>
+        <v>35.7890625</v>
       </c>
       <c r="H80">
         <v>1.705000042915344</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="1">
+    <row r="81">
+      <c r="A81" s="2">
         <v>39630</v>
       </c>
       <c r="B81">
         <v>1267.380004882812</v>
       </c>
       <c r="C81">
-        <v>2.386124610900879</v>
+        <v>2.386125087738037</v>
       </c>
       <c r="D81">
-        <v>18.49817085266113</v>
+        <v>18.46341896057129</v>
       </c>
       <c r="E81">
-        <v>17.09469604492188</v>
+        <v>17.09469795227051</v>
       </c>
       <c r="F81">
-        <v>28.44107437133789</v>
+        <v>28.40038299560547</v>
       </c>
       <c r="G81">
-        <v>38.77858734130859</v>
+        <v>38.77859497070312</v>
       </c>
       <c r="H81">
         <v>1.634999990463257</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="1">
+    <row r="82">
+      <c r="A82" s="2">
         <v>39661</v>
       </c>
       <c r="B82">
         <v>1282.829956054688</v>
       </c>
       <c r="C82">
-        <v>2.217108249664307</v>
+        <v>2.217107772827148</v>
       </c>
       <c r="D82">
-        <v>19.70562171936035</v>
+        <v>19.6685962677002</v>
       </c>
       <c r="E82">
         <v>17.41229820251465</v>
       </c>
       <c r="F82">
-        <v>28.43471717834473</v>
+        <v>28.39403533935547</v>
       </c>
       <c r="G82">
-        <v>41.31921768188477</v>
+        <v>41.3192024230957</v>
       </c>
       <c r="H82">
         <v>1.690000057220459</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="1">
+    <row r="83">
+      <c r="A83" s="2">
         <v>39692</v>
       </c>
       <c r="B83">
         <v>1166.359985351562</v>
       </c>
       <c r="C83">
-        <v>2.584968566894531</v>
+        <v>2.584969520568848</v>
       </c>
       <c r="D83">
-        <v>19.27236938476562</v>
+        <v>19.23616027832031</v>
       </c>
       <c r="E83">
-        <v>16.12602806091309</v>
+        <v>16.12602424621582</v>
       </c>
       <c r="F83">
-        <v>26.83774948120117</v>
+        <v>26.79934883117676</v>
       </c>
       <c r="G83">
         <v>41.27182769775391</v>
@@ -2548,336 +2535,336 @@
         <v>0.8999999761581421</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="1">
+    <row r="84">
+      <c r="A84" s="2">
         <v>39722</v>
       </c>
       <c r="B84">
         <v>968.75</v>
       </c>
       <c r="C84">
-        <v>1.088670134544373</v>
+        <v>1.088669300079346</v>
       </c>
       <c r="D84">
-        <v>16.12408828735352</v>
+        <v>16.09378814697266</v>
       </c>
       <c r="E84">
-        <v>14.52215766906738</v>
+        <v>14.52215194702148</v>
       </c>
       <c r="F84">
-        <v>20.61441421508789</v>
+        <v>20.58491325378418</v>
       </c>
       <c r="G84">
-        <v>38.46628952026367</v>
+        <v>38.46628570556641</v>
       </c>
       <c r="H84">
         <v>0.4350000023841858</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="1">
+    <row r="85">
+      <c r="A85" s="2">
         <v>39753</v>
       </c>
       <c r="B85">
         <v>896.239990234375</v>
       </c>
       <c r="C85">
-        <v>1.33722460269928</v>
+        <v>1.337224125862122</v>
       </c>
       <c r="D85">
-        <v>14.69940090179443</v>
+        <v>14.67179203033447</v>
       </c>
       <c r="E85">
-        <v>12.77537155151367</v>
+        <v>12.77536773681641</v>
       </c>
       <c r="F85">
-        <v>21.10759544372559</v>
+        <v>21.07739639282227</v>
       </c>
       <c r="G85">
-        <v>38.35305786132812</v>
+        <v>38.35304260253906</v>
       </c>
       <c r="H85">
         <v>0.01999999955296516</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="1">
+    <row r="86">
+      <c r="A86" s="2">
         <v>39783</v>
       </c>
       <c r="B86">
         <v>903.25</v>
       </c>
       <c r="C86">
-        <v>1.138380646705627</v>
+        <v>1.138380527496338</v>
       </c>
       <c r="D86">
-        <v>14.1323709487915</v>
+        <v>14.10581398010254</v>
       </c>
       <c r="E86">
-        <v>14.07751941680908</v>
+        <v>14.07752132415771</v>
       </c>
       <c r="F86">
-        <v>24.8902702331543</v>
+        <v>24.85466384887695</v>
       </c>
       <c r="G86">
-        <v>36.84514236450195</v>
+        <v>36.84515380859375</v>
       </c>
       <c r="H86">
         <v>0.1150000020861626</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="1">
+    <row r="87">
+      <c r="A87" s="2">
         <v>39814</v>
       </c>
       <c r="B87">
         <v>825.8800048828125</v>
       </c>
       <c r="C87">
-        <v>0.9295943379402161</v>
+        <v>0.9295942187309265</v>
       </c>
       <c r="D87">
-        <v>12.43124771118164</v>
+        <v>12.40789222717285</v>
       </c>
       <c r="E87">
-        <v>13.36292171478271</v>
+        <v>13.36292362213135</v>
       </c>
       <c r="F87">
-        <v>22.75787544250488</v>
+        <v>22.72531700134277</v>
       </c>
       <c r="G87">
-        <v>32.71020126342773</v>
+        <v>32.71020889282227</v>
       </c>
       <c r="H87">
         <v>0.2199999988079071</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="1">
+    <row r="88">
+      <c r="A88" s="2">
         <v>39845</v>
       </c>
       <c r="B88">
         <v>735.0900268554688</v>
       </c>
       <c r="C88">
-        <v>0.9942187666893005</v>
+        <v>0.9942187070846558</v>
       </c>
       <c r="D88">
-        <v>11.82112598419189</v>
+        <v>11.79891300201416</v>
       </c>
       <c r="E88">
-        <v>12.33867073059082</v>
+        <v>12.33867263793945</v>
       </c>
       <c r="F88">
-        <v>18.40345001220703</v>
+        <v>18.37711715698242</v>
       </c>
       <c r="G88">
-        <v>28.91101455688477</v>
+        <v>28.91102027893066</v>
       </c>
       <c r="H88">
         <v>0.25</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="1">
+    <row r="89">
+      <c r="A89" s="2">
         <v>39873</v>
       </c>
       <c r="B89">
         <v>797.8699951171875</v>
       </c>
       <c r="C89">
-        <v>1.307397365570068</v>
+        <v>1.307397484779358</v>
       </c>
       <c r="D89">
-        <v>13.44607067108154</v>
+        <v>13.42080402374268</v>
       </c>
       <c r="E89">
-        <v>14.34747791290283</v>
+        <v>14.34747886657715</v>
       </c>
       <c r="F89">
-        <v>20.92782402038574</v>
+        <v>20.89787483215332</v>
       </c>
       <c r="G89">
-        <v>28.2628116607666</v>
+        <v>28.2628288269043</v>
       </c>
       <c r="H89">
         <v>0.2000000029802322</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="1">
+    <row r="90">
+      <c r="A90" s="2">
         <v>39904</v>
       </c>
       <c r="B90">
         <v>872.8099975585938</v>
       </c>
       <c r="C90">
-        <v>2.972713232040405</v>
+        <v>2.972713947296143</v>
       </c>
       <c r="D90">
-        <v>14.82947731018066</v>
+        <v>14.80160999298096</v>
       </c>
       <c r="E90">
-        <v>15.3957576751709</v>
+        <v>15.39575576782227</v>
       </c>
       <c r="F90">
-        <v>20.62087631225586</v>
+        <v>20.59137344360352</v>
       </c>
       <c r="G90">
-        <v>29.92960357666016</v>
+        <v>29.92961502075195</v>
       </c>
       <c r="H90">
         <v>0.125</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="1">
+    <row r="91">
+      <c r="A91" s="2">
         <v>39934</v>
       </c>
       <c r="B91">
         <v>919.1400146484375</v>
       </c>
       <c r="C91">
-        <v>2.858377933502197</v>
+        <v>2.858379125595093</v>
       </c>
       <c r="D91">
-        <v>15.38772010803223</v>
+        <v>15.35879898071289</v>
       </c>
       <c r="E91">
-        <v>15.59477519989014</v>
+        <v>15.59476184844971</v>
       </c>
       <c r="F91">
-        <v>21.95408821105957</v>
+        <v>21.92267036437988</v>
       </c>
       <c r="G91">
-        <v>31.44305419921875</v>
+        <v>31.44304656982422</v>
       </c>
       <c r="H91">
         <v>0.1299999952316284</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="1">
+    <row r="92">
+      <c r="A92" s="2">
         <v>39965</v>
       </c>
       <c r="B92">
         <v>919.3200073242188</v>
       </c>
       <c r="C92">
-        <v>3.017453670501709</v>
+        <v>3.017455101013184</v>
       </c>
       <c r="D92">
-        <v>17.50914764404297</v>
+        <v>17.47623443603516</v>
       </c>
       <c r="E92">
-        <v>17.05156326293945</v>
+        <v>17.05155372619629</v>
       </c>
       <c r="F92">
-        <v>21.9985408782959</v>
+        <v>21.96706390380859</v>
       </c>
       <c r="G92">
-        <v>30.93454360961914</v>
+        <v>30.93453216552734</v>
       </c>
       <c r="H92">
         <v>0.1800000071525574</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="1">
+    <row r="93">
+      <c r="A93" s="2">
         <v>39995</v>
       </c>
       <c r="B93">
         <v>987.47998046875</v>
       </c>
       <c r="C93">
-        <v>3.976875066757202</v>
+        <v>3.976874828338623</v>
       </c>
       <c r="D93">
-        <v>17.32499122619629</v>
+        <v>17.29243850708008</v>
       </c>
       <c r="E93">
-        <v>17.65984916687012</v>
+        <v>17.65984725952148</v>
       </c>
       <c r="F93">
-        <v>22.15730857849121</v>
+        <v>22.1255989074707</v>
       </c>
       <c r="G93">
-        <v>33.87280654907227</v>
+        <v>33.87282180786133</v>
       </c>
       <c r="H93">
         <v>0.1749999970197678</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="1">
+    <row r="94">
+      <c r="A94" s="2">
         <v>40026</v>
       </c>
       <c r="B94">
         <v>1020.619995117188</v>
       </c>
       <c r="C94">
-        <v>3.77803111076355</v>
+        <v>3.778032302856445</v>
       </c>
       <c r="D94">
-        <v>18.25945091247559</v>
+        <v>18.22513961791992</v>
       </c>
       <c r="E94">
-        <v>17.46035385131836</v>
+        <v>17.46035575866699</v>
       </c>
       <c r="F94">
-        <v>21.56298065185547</v>
+        <v>21.5321159362793</v>
       </c>
       <c r="G94">
-        <v>33.01852035522461</v>
+        <v>33.01852798461914</v>
       </c>
       <c r="H94">
         <v>0.1299999952316284</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="1">
+    <row r="95">
+      <c r="A95" s="2">
         <v>40057</v>
       </c>
       <c r="B95">
         <v>1057.079956054688</v>
       </c>
       <c r="C95">
-        <v>3.584158897399902</v>
+        <v>3.584159135818481</v>
       </c>
       <c r="D95">
-        <v>19.05204772949219</v>
+        <v>19.01624870300293</v>
       </c>
       <c r="E95">
-        <v>16.63042831420898</v>
+        <v>16.63042259216309</v>
       </c>
       <c r="F95">
-        <v>21.28586006164551</v>
+        <v>21.25540924072266</v>
       </c>
       <c r="G95">
-        <v>35.34341812133789</v>
+        <v>35.34342193603516</v>
       </c>
       <c r="H95">
         <v>0.1150000020861626</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="1">
+    <row r="96">
+      <c r="A96" s="2">
         <v>40087</v>
       </c>
       <c r="B96">
         <v>1036.18994140625</v>
       </c>
       <c r="C96">
-        <v>3.47976541519165</v>
+        <v>3.479764223098755</v>
       </c>
       <c r="D96">
-        <v>20.54095840454102</v>
+        <v>20.50236129760742</v>
       </c>
       <c r="E96">
-        <v>16.87848091125488</v>
+        <v>16.87848472595215</v>
       </c>
       <c r="F96">
-        <v>21.91742324829102</v>
+        <v>21.88605308532715</v>
       </c>
       <c r="G96">
         <v>35.66217041015625</v>
@@ -2886,190 +2873,190 @@
         <v>0.04500000178813934</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="1">
+    <row r="97">
+      <c r="A97" s="2">
         <v>40118</v>
       </c>
       <c r="B97">
         <v>1095.630004882812</v>
       </c>
       <c r="C97">
-        <v>4.419302940368652</v>
+        <v>4.419301509857178</v>
       </c>
       <c r="D97">
-        <v>21.8817081451416</v>
+        <v>21.8405933380127</v>
       </c>
       <c r="E97">
-        <v>17.66240882873535</v>
+        <v>17.66241264343262</v>
       </c>
       <c r="F97">
-        <v>24.00329780578613</v>
+        <v>23.96893882751465</v>
       </c>
       <c r="G97">
-        <v>38.33684158325195</v>
+        <v>38.33683395385742</v>
       </c>
       <c r="H97">
         <v>0.05000000074505806</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="1">
+    <row r="98">
+      <c r="A98" s="2">
         <v>40148</v>
       </c>
       <c r="B98">
         <v>1115.099975585938</v>
       </c>
       <c r="C98">
-        <v>4.97109317779541</v>
+        <v>4.971093654632568</v>
       </c>
       <c r="D98">
-        <v>22.67782211303711</v>
+        <v>22.63520812988281</v>
       </c>
       <c r="E98">
-        <v>19.62223434448242</v>
+        <v>19.62223815917969</v>
       </c>
       <c r="F98">
-        <v>23.33672142028809</v>
+        <v>23.30332565307617</v>
       </c>
       <c r="G98">
-        <v>37.27927017211914</v>
+        <v>37.27927398681641</v>
       </c>
       <c r="H98">
         <v>0.05000000074505806</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="1">
+    <row r="99">
+      <c r="A99" s="2">
         <v>40179</v>
       </c>
       <c r="B99">
         <v>1073.869995117188</v>
       </c>
       <c r="C99">
-        <v>5.388666152954102</v>
+        <v>5.388665199279785</v>
       </c>
       <c r="D99">
-        <v>20.96656227111816</v>
+        <v>20.92716598510742</v>
       </c>
       <c r="E99">
-        <v>18.48360824584961</v>
+        <v>18.48360252380371</v>
       </c>
       <c r="F99">
-        <v>23.00343132019043</v>
+        <v>22.97051811218262</v>
       </c>
       <c r="G99">
-        <v>38.11666488647461</v>
+        <v>38.11668014526367</v>
       </c>
       <c r="H99">
         <v>0.07000000029802322</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="1">
+    <row r="100">
+      <c r="A100" s="2">
         <v>40210</v>
       </c>
       <c r="B100">
         <v>1104.489990234375</v>
       </c>
       <c r="C100">
-        <v>5.836063385009766</v>
+        <v>5.836064338684082</v>
       </c>
       <c r="D100">
-        <v>21.43087577819824</v>
+        <v>21.3906135559082</v>
       </c>
       <c r="E100">
-        <v>19.7580623626709</v>
+        <v>19.7580680847168</v>
       </c>
       <c r="F100">
-        <v>22.75822257995605</v>
+        <v>22.72564506530762</v>
       </c>
       <c r="G100">
-        <v>39.18804168701172</v>
+        <v>39.18802642822266</v>
       </c>
       <c r="H100">
         <v>0.1150000020861626</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="1">
+    <row r="101">
+      <c r="A101" s="2">
         <v>40238</v>
       </c>
       <c r="B101">
         <v>1169.430053710938</v>
       </c>
       <c r="C101">
-        <v>6.248664379119873</v>
+        <v>6.248663902282715</v>
       </c>
       <c r="D101">
-        <v>21.89433479309082</v>
+        <v>21.85319519042969</v>
       </c>
       <c r="E101">
-        <v>20.60769271850586</v>
+        <v>20.60769653320312</v>
       </c>
       <c r="F101">
-        <v>24.00415229797363</v>
+        <v>23.96980094909668</v>
       </c>
       <c r="G101">
-        <v>39.18185043334961</v>
+        <v>39.18184280395508</v>
       </c>
       <c r="H101">
         <v>0.1500000059604645</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="1">
+    <row r="102">
+      <c r="A102" s="2">
         <v>40269</v>
       </c>
       <c r="B102">
         <v>1186.68994140625</v>
       </c>
       <c r="C102">
-        <v>6.472364902496338</v>
+        <v>6.472363471984863</v>
       </c>
       <c r="D102">
-        <v>22.82871627807617</v>
+        <v>22.78581809997559</v>
       </c>
       <c r="E102">
-        <v>20.77570152282715</v>
+        <v>20.77570533752441</v>
       </c>
       <c r="F102">
-        <v>23.17574501037598</v>
+        <v>23.142578125</v>
       </c>
       <c r="G102">
-        <v>38.79070663452148</v>
+        <v>38.79070281982422</v>
       </c>
       <c r="H102">
         <v>0.1550000011920929</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="1">
+    <row r="103">
+      <c r="A103" s="2">
         <v>40299</v>
       </c>
       <c r="B103">
         <v>1089.410034179688</v>
       </c>
       <c r="C103">
-        <v>5.83109188079834</v>
+        <v>5.831092357635498</v>
       </c>
       <c r="D103">
-        <v>19.3725757598877</v>
+        <v>19.33616828918457</v>
       </c>
       <c r="E103">
-        <v>18.12553405761719</v>
+        <v>18.12552261352539</v>
       </c>
       <c r="F103">
-        <v>22.03705406188965</v>
+        <v>22.00552177429199</v>
       </c>
       <c r="G103">
-        <v>38.12296295166016</v>
+        <v>38.12296676635742</v>
       </c>
       <c r="H103">
         <v>0.1500000059604645</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="1">
+    <row r="104">
+      <c r="A104" s="2">
         <v>40330</v>
       </c>
       <c r="B104">
@@ -3079,39 +3066,39 @@
         <v>5.010862350463867</v>
       </c>
       <c r="D104">
-        <v>17.27762985229492</v>
+        <v>17.24516487121582</v>
       </c>
       <c r="E104">
-        <v>17.23410987854004</v>
+        <v>17.23411560058594</v>
       </c>
       <c r="F104">
-        <v>22.51422500610352</v>
+        <v>22.48200798034668</v>
       </c>
       <c r="G104">
-        <v>37.43028259277344</v>
+        <v>37.4302864074707</v>
       </c>
       <c r="H104">
         <v>0.1700000017881393</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="1">
+    <row r="105">
+      <c r="A105" s="2">
         <v>40360</v>
       </c>
       <c r="B105">
         <v>1101.599975585938</v>
       </c>
       <c r="C105">
-        <v>6.348086833953857</v>
+        <v>6.348089694976807</v>
       </c>
       <c r="D105">
-        <v>19.38007736206055</v>
+        <v>19.34366607666016</v>
       </c>
       <c r="E105">
-        <v>19.02553558349609</v>
+        <v>19.02553176879883</v>
       </c>
       <c r="F105">
-        <v>23.92556190490723</v>
+        <v>23.89132499694824</v>
       </c>
       <c r="G105">
         <v>38.46535873413086</v>
@@ -3120,34 +3107,34 @@
         <v>0.1400000005960464</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="1">
+    <row r="106">
+      <c r="A106" s="2">
         <v>40391</v>
       </c>
       <c r="B106">
         <v>1049.329956054688</v>
       </c>
       <c r="C106">
-        <v>5.612364292144775</v>
+        <v>5.612366199493408</v>
       </c>
       <c r="D106">
-        <v>17.717041015625</v>
+        <v>17.68375396728516</v>
       </c>
       <c r="E106">
         <v>17.57688522338867</v>
       </c>
       <c r="F106">
-        <v>22.87141990661621</v>
+        <v>22.83869934082031</v>
       </c>
       <c r="G106">
-        <v>37.52823638916016</v>
+        <v>37.52825927734375</v>
       </c>
       <c r="H106">
         <v>0.135000005364418</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="1">
+    <row r="107">
+      <c r="A107" s="2">
         <v>40422</v>
       </c>
       <c r="B107">
@@ -3157,257 +3144,257 @@
         <v>6.084617614746094</v>
       </c>
       <c r="D107">
-        <v>18.48702430725098</v>
+        <v>18.45228385925293</v>
       </c>
       <c r="E107">
         <v>21.60894393920898</v>
       </c>
       <c r="F107">
-        <v>24.87326812744141</v>
+        <v>24.83767700195312</v>
       </c>
       <c r="G107">
-        <v>37.71692657470703</v>
+        <v>37.71693420410156</v>
       </c>
       <c r="H107">
         <v>0.1550000011920929</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="1">
+    <row r="108">
+      <c r="A108" s="2">
         <v>40452</v>
       </c>
       <c r="B108">
         <v>1183.260009765625</v>
       </c>
       <c r="C108">
-        <v>7.024158000946045</v>
+        <v>7.024153709411621</v>
       </c>
       <c r="D108">
-        <v>20.13266181945801</v>
+        <v>20.09483337402344</v>
       </c>
       <c r="E108">
-        <v>23.6885814666748</v>
+        <v>23.68857574462891</v>
       </c>
       <c r="F108">
-        <v>23.96767616271973</v>
+        <v>23.93338775634766</v>
       </c>
       <c r="G108">
-        <v>40.28844451904297</v>
+        <v>40.28843688964844</v>
       </c>
       <c r="H108">
         <v>0.1099999994039536</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="1">
+    <row r="109">
+      <c r="A109" s="2">
         <v>40483</v>
       </c>
       <c r="B109">
         <v>1180.550048828125</v>
       </c>
       <c r="C109">
-        <v>7.923922061920166</v>
+        <v>7.923922538757324</v>
       </c>
       <c r="D109">
-        <v>19.18544769287109</v>
+        <v>19.14939498901367</v>
       </c>
       <c r="E109">
-        <v>21.8099365234375</v>
+        <v>21.8099479675293</v>
       </c>
       <c r="F109">
-        <v>23.23740005493164</v>
+        <v>23.20415306091309</v>
       </c>
       <c r="G109">
-        <v>38.70402908325195</v>
+        <v>38.70402145385742</v>
       </c>
       <c r="H109">
         <v>0.1599999964237213</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="1">
+    <row r="110">
+      <c r="A110" s="2">
         <v>40513</v>
       </c>
       <c r="B110">
         <v>1257.640014648438</v>
       </c>
       <c r="C110">
-        <v>8.346467018127441</v>
+        <v>8.346470832824707</v>
       </c>
       <c r="D110">
-        <v>21.19817352294922</v>
+        <v>21.1583366394043</v>
       </c>
       <c r="E110">
-        <v>25.23665237426758</v>
+        <v>25.23663711547852</v>
       </c>
       <c r="F110">
-        <v>24.19009780883789</v>
+        <v>24.15549278259277</v>
       </c>
       <c r="G110">
-        <v>40.77009201049805</v>
+        <v>40.77009963989258</v>
       </c>
       <c r="H110">
         <v>0.1150000020861626</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="1">
+    <row r="111">
+      <c r="A111" s="2">
         <v>40544</v>
       </c>
       <c r="B111">
         <v>1286.119995117188</v>
       </c>
       <c r="C111">
-        <v>7.928894519805908</v>
+        <v>7.928892135620117</v>
       </c>
       <c r="D111">
-        <v>21.06145477294922</v>
+        <v>21.02187728881836</v>
       </c>
       <c r="E111">
-        <v>25.86671447753906</v>
+        <v>25.86670875549316</v>
       </c>
       <c r="F111">
-        <v>24.00370025634766</v>
+        <v>23.96936798095703</v>
       </c>
       <c r="G111">
-        <v>40.30617904663086</v>
+        <v>40.30620193481445</v>
       </c>
       <c r="H111">
         <v>0.1449999958276749</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="1">
+    <row r="112">
+      <c r="A112" s="2">
         <v>40575</v>
       </c>
       <c r="B112">
         <v>1327.219970703125</v>
       </c>
       <c r="C112">
-        <v>7.481497287750244</v>
+        <v>7.481494426727295</v>
       </c>
       <c r="D112">
-        <v>20.30733489990234</v>
+        <v>20.26918029785156</v>
       </c>
       <c r="E112">
-        <v>26.56930160522461</v>
+        <v>26.56929588317871</v>
       </c>
       <c r="F112">
-        <v>24.1915168762207</v>
+        <v>24.15690422058105</v>
       </c>
       <c r="G112">
-        <v>40.25510406494141</v>
+        <v>40.25509262084961</v>
       </c>
       <c r="H112">
         <v>0.135000005364418</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="1">
+    <row r="113">
+      <c r="A113" s="2">
         <v>40603</v>
       </c>
       <c r="B113">
         <v>1325.829956054688</v>
       </c>
       <c r="C113">
-        <v>7.411901473999023</v>
+        <v>7.411898136138916</v>
       </c>
       <c r="D113">
-        <v>19.39816474914551</v>
+        <v>19.36170959472656</v>
       </c>
       <c r="E113">
-        <v>26.99731636047363</v>
+        <v>26.99732398986816</v>
       </c>
       <c r="F113">
-        <v>24.61850357055664</v>
+        <v>24.58327293395996</v>
       </c>
       <c r="G113">
-        <v>39.32932662963867</v>
+        <v>39.32934188842773</v>
       </c>
       <c r="H113">
         <v>0.09000000357627869</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="1">
+    <row r="114">
+      <c r="A114" s="2">
         <v>40634</v>
       </c>
       <c r="B114">
         <v>1363.609985351562</v>
       </c>
       <c r="C114">
-        <v>7.690282344818115</v>
+        <v>7.690285205841064</v>
       </c>
       <c r="D114">
-        <v>19.80307960510254</v>
+        <v>19.7658805847168</v>
       </c>
       <c r="E114">
-        <v>29.092529296875</v>
+        <v>29.0925407409668</v>
       </c>
       <c r="F114">
-        <v>25.90648651123047</v>
+        <v>25.86940383911133</v>
       </c>
       <c r="G114">
-        <v>41.77989196777344</v>
+        <v>41.77990341186523</v>
       </c>
       <c r="H114">
         <v>0.03999999910593033</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="1">
+    <row r="115">
+      <c r="A115" s="2">
         <v>40664</v>
       </c>
       <c r="B115">
         <v>1345.199951171875</v>
       </c>
       <c r="C115">
-        <v>7.416872501373291</v>
+        <v>7.416870594024658</v>
       </c>
       <c r="D115">
-        <v>19.23308563232422</v>
+        <v>19.19695472717285</v>
       </c>
       <c r="E115">
-        <v>27.68481826782227</v>
+        <v>27.6848316192627</v>
       </c>
       <c r="F115">
-        <v>27.28069496154785</v>
+        <v>27.24166107177734</v>
       </c>
       <c r="G115">
-        <v>43.13178634643555</v>
+        <v>43.13180160522461</v>
       </c>
       <c r="H115">
         <v>0.03999999910593033</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="1">
+    <row r="116">
+      <c r="A116" s="2">
         <v>40695</v>
       </c>
       <c r="B116">
         <v>1320.640014648438</v>
       </c>
       <c r="C116">
-        <v>6.855136871337891</v>
+        <v>6.855140209197998</v>
       </c>
       <c r="D116">
-        <v>19.99440765380859</v>
+        <v>19.95684051513672</v>
       </c>
       <c r="E116">
-        <v>26.62500190734863</v>
+        <v>26.62499809265137</v>
       </c>
       <c r="F116">
-        <v>26.60718154907227</v>
+        <v>26.56911659240723</v>
       </c>
       <c r="G116">
-        <v>40.92370986938477</v>
+        <v>40.92369842529297</v>
       </c>
       <c r="H116">
         <v>0.01499999966472387</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="1">
+    <row r="117">
+      <c r="A117" s="2">
         <v>40725</v>
       </c>
       <c r="B117">
@@ -3417,143 +3404,143 @@
         <v>6.069705486297607</v>
       </c>
       <c r="D117">
-        <v>21.07103157043457</v>
+        <v>21.03144645690918</v>
       </c>
       <c r="E117">
         <v>24.78379058837891</v>
       </c>
       <c r="F117">
-        <v>27.15310096740723</v>
+        <v>27.11423301696777</v>
       </c>
       <c r="G117">
-        <v>39.90896606445312</v>
+        <v>39.90898132324219</v>
       </c>
       <c r="H117">
         <v>0.09000000357627869</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="1">
+    <row r="118">
+      <c r="A118" s="2">
         <v>40756</v>
       </c>
       <c r="B118">
         <v>1218.890014648438</v>
       </c>
       <c r="C118">
-        <v>5.527855396270752</v>
+        <v>5.527854442596436</v>
       </c>
       <c r="D118">
-        <v>20.58493232727051</v>
+        <v>20.54625129699707</v>
       </c>
       <c r="E118">
-        <v>22.74954223632812</v>
+        <v>22.74954795837402</v>
       </c>
       <c r="F118">
-        <v>26.97626686096191</v>
+        <v>26.93765830993652</v>
       </c>
       <c r="G118">
-        <v>41.33035278320312</v>
+        <v>41.33034515380859</v>
       </c>
       <c r="H118">
         <v>0.01499999966472387</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="1">
+    <row r="119">
+      <c r="A119" s="2">
         <v>40787</v>
       </c>
       <c r="B119">
         <v>1131.420043945312</v>
       </c>
       <c r="C119">
-        <v>4.807046413421631</v>
+        <v>4.807047367095947</v>
       </c>
       <c r="D119">
-        <v>19.26161003112793</v>
+        <v>19.22542953491211</v>
       </c>
       <c r="E119">
         <v>23.29254913330078</v>
       </c>
       <c r="F119">
-        <v>26.5878963470459</v>
+        <v>26.54985809326172</v>
       </c>
       <c r="G119">
-        <v>41.00583648681641</v>
+        <v>41.00583267211914</v>
       </c>
       <c r="H119">
         <v>0.009999999776482582</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
-      <c r="A120" s="1">
+    <row r="120">
+      <c r="A120" s="2">
         <v>40817</v>
       </c>
       <c r="B120">
         <v>1253.300048828125</v>
       </c>
       <c r="C120">
-        <v>5.806235790252686</v>
+        <v>5.80623722076416</v>
       </c>
       <c r="D120">
-        <v>20.60814476013184</v>
+        <v>20.56941986083984</v>
       </c>
       <c r="E120">
-        <v>26.6117992401123</v>
+        <v>26.61179542541504</v>
       </c>
       <c r="F120">
-        <v>26.72455215454102</v>
+        <v>26.68631553649902</v>
       </c>
       <c r="G120">
-        <v>41.87015914916992</v>
+        <v>41.87015151977539</v>
       </c>
       <c r="H120">
         <v>0.004999999888241291</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="1">
+    <row r="121">
+      <c r="A121" s="2">
         <v>40848</v>
       </c>
       <c r="B121">
         <v>1246.9599609375</v>
       </c>
       <c r="C121">
-        <v>5.269359111785889</v>
+        <v>5.269357681274414</v>
       </c>
       <c r="D121">
-        <v>19.94465065002441</v>
+        <v>19.90716934204102</v>
       </c>
       <c r="E121">
-        <v>25.45864105224609</v>
+        <v>25.45864868164062</v>
       </c>
       <c r="F121">
-        <v>27.57779693603516</v>
+        <v>27.5383358001709</v>
       </c>
       <c r="G121">
-        <v>42.24966049194336</v>
+        <v>42.24966812133789</v>
       </c>
       <c r="H121">
         <v>0.01499999966472387</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
-      <c r="A122" s="1">
+    <row r="122">
+      <c r="A122" s="2">
         <v>40878</v>
       </c>
       <c r="B122">
         <v>1257.599975585938</v>
       </c>
       <c r="C122">
-        <v>5.348898410797119</v>
+        <v>5.348896503448486</v>
       </c>
       <c r="D122">
-        <v>20.24093246459961</v>
+        <v>20.20289993286133</v>
       </c>
       <c r="E122">
-        <v>20.82980537414551</v>
+        <v>20.82979583740234</v>
       </c>
       <c r="F122">
-        <v>30.28092765808105</v>
+        <v>30.23760223388672</v>
       </c>
       <c r="G122">
         <v>43.6499137878418</v>
@@ -3562,24 +3549,24 @@
         <v>0.004999999888241291</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
-      <c r="A123" s="1">
+    <row r="123">
+      <c r="A123" s="2">
         <v>40909</v>
       </c>
       <c r="B123">
         <v>1312.410034179688</v>
       </c>
       <c r="C123">
-        <v>6.198330879211426</v>
+        <v>6.198329448699951</v>
       </c>
       <c r="D123">
-        <v>23.02444458007812</v>
+        <v>22.98119163513184</v>
       </c>
       <c r="E123">
-        <v>22.95987129211426</v>
+        <v>22.95986938476562</v>
       </c>
       <c r="F123">
-        <v>28.95487976074219</v>
+        <v>28.9134407043457</v>
       </c>
       <c r="G123">
         <v>41.57798004150391</v>
@@ -3588,50 +3575,50 @@
         <v>0.05499999970197678</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="1">
+    <row r="124">
+      <c r="A124" s="2">
         <v>40940</v>
       </c>
       <c r="B124">
         <v>1365.680053710938</v>
       </c>
       <c r="C124">
-        <v>6.178367614746094</v>
+        <v>6.178366661071777</v>
       </c>
       <c r="D124">
-        <v>24.91050720214844</v>
+        <v>24.86369705200195</v>
       </c>
       <c r="E124">
-        <v>23.80631446838379</v>
+        <v>23.80632400512695</v>
       </c>
       <c r="F124">
-        <v>28.95144271850586</v>
+        <v>28.91001892089844</v>
       </c>
       <c r="G124">
-        <v>44.59871673583984</v>
+        <v>44.59872055053711</v>
       </c>
       <c r="H124">
         <v>0.07500000298023224</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="1">
+    <row r="125">
+      <c r="A125" s="2">
         <v>40969</v>
       </c>
       <c r="B125">
         <v>1408.469970703125</v>
       </c>
       <c r="C125">
-        <v>6.228273391723633</v>
+        <v>6.228272438049316</v>
       </c>
       <c r="D125">
-        <v>25.3186092376709</v>
+        <v>25.27103233337402</v>
       </c>
       <c r="E125">
-        <v>23.73307037353516</v>
+        <v>23.73306655883789</v>
       </c>
       <c r="F125">
-        <v>29.71138000488281</v>
+        <v>29.66887855529785</v>
       </c>
       <c r="G125">
         <v>44.32829666137695</v>
@@ -3640,102 +3627,102 @@
         <v>0.06499999761581421</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="1">
+    <row r="126">
+      <c r="A126" s="2">
         <v>41000</v>
       </c>
       <c r="B126">
         <v>1397.910034179688</v>
       </c>
       <c r="C126">
-        <v>5.653770923614502</v>
+        <v>5.653769493103027</v>
       </c>
       <c r="D126">
-        <v>25.13025856018066</v>
+        <v>25.08303833007812</v>
       </c>
       <c r="E126">
         <v>23.97707176208496</v>
       </c>
       <c r="F126">
-        <v>30.53772926330566</v>
+        <v>30.4940185546875</v>
       </c>
       <c r="G126">
-        <v>42.32876968383789</v>
+        <v>42.32875823974609</v>
       </c>
       <c r="H126">
         <v>0.09000000357627869</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="1">
+    <row r="127">
+      <c r="A127" s="2">
         <v>41030</v>
       </c>
       <c r="B127">
         <v>1310.329956054688</v>
       </c>
       <c r="C127">
-        <v>5.292891025543213</v>
+        <v>5.292891979217529</v>
       </c>
       <c r="D127">
-        <v>23.05950927734375</v>
+        <v>23.01617431640625</v>
       </c>
       <c r="E127">
-        <v>21.58752250671387</v>
+        <v>21.5875186920166</v>
       </c>
       <c r="F127">
-        <v>30.57188606262207</v>
+        <v>30.52814865112305</v>
       </c>
       <c r="G127">
-        <v>41.43083953857422</v>
+        <v>41.43084716796875</v>
       </c>
       <c r="H127">
         <v>0.05999999865889549</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="1">
+    <row r="128">
+      <c r="A128" s="2">
         <v>41061</v>
       </c>
       <c r="B128">
         <v>1362.160034179688</v>
       </c>
       <c r="C128">
-        <v>4.806707859039307</v>
+        <v>4.806708335876465</v>
       </c>
       <c r="D128">
-        <v>24.16548156738281</v>
+        <v>24.12007713317871</v>
       </c>
       <c r="E128">
-        <v>24.22173500061035</v>
+        <v>24.22173881530762</v>
       </c>
       <c r="F128">
-        <v>32.03515625</v>
+        <v>31.98933410644531</v>
       </c>
       <c r="G128">
-        <v>40.73910522460938</v>
+        <v>40.73912811279297</v>
       </c>
       <c r="H128">
         <v>0.07999999821186066</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
-      <c r="A129" s="1">
+    <row r="129">
+      <c r="A129" s="2">
         <v>41091</v>
       </c>
       <c r="B129">
         <v>1379.319946289062</v>
       </c>
       <c r="C129">
-        <v>4.631280899047852</v>
+        <v>4.631279945373535</v>
       </c>
       <c r="D129">
-        <v>23.28070259094238</v>
+        <v>23.23694801330566</v>
       </c>
       <c r="E129">
-        <v>24.68048286437988</v>
+        <v>24.68048858642578</v>
       </c>
       <c r="F129">
-        <v>32.87130737304688</v>
+        <v>32.82428741455078</v>
       </c>
       <c r="G129">
         <v>43.29975509643555</v>
@@ -3744,24 +3731,24 @@
         <v>0.1000000014901161</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
-      <c r="A130" s="1">
+    <row r="130">
+      <c r="A130" s="2">
         <v>41122</v>
       </c>
       <c r="B130">
         <v>1406.579956054688</v>
       </c>
       <c r="C130">
-        <v>4.706872463226318</v>
+        <v>4.706871509552002</v>
       </c>
       <c r="D130">
-        <v>24.50847053527832</v>
+        <v>24.4624137878418</v>
       </c>
       <c r="E130">
-        <v>25.865478515625</v>
+        <v>25.86546897888184</v>
       </c>
       <c r="F130">
-        <v>33.90938949584961</v>
+        <v>33.86086654663086</v>
       </c>
       <c r="G130">
         <v>45.07762145996094</v>
@@ -3770,476 +3757,476 @@
         <v>0.08500000089406967</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
-      <c r="A131" s="1">
+    <row r="131">
+      <c r="A131" s="2">
         <v>41153</v>
       </c>
       <c r="B131">
         <v>1440.670043945312</v>
       </c>
       <c r="C131">
-        <v>4.968924522399902</v>
+        <v>4.968924999237061</v>
       </c>
       <c r="D131">
-        <v>23.66554260253906</v>
+        <v>23.62107849121094</v>
       </c>
       <c r="E131">
-        <v>25.7101993560791</v>
+        <v>25.7101936340332</v>
       </c>
       <c r="F131">
-        <v>35.79701995849609</v>
+        <v>35.74580001831055</v>
       </c>
       <c r="G131">
-        <v>46.53347778320312</v>
+        <v>46.53346633911133</v>
       </c>
       <c r="H131">
         <v>0.09000000357627869</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
-      <c r="A132" s="1">
+    <row r="132">
+      <c r="A132" s="2">
         <v>41183</v>
       </c>
       <c r="B132">
         <v>1412.160034179688</v>
       </c>
       <c r="C132">
-        <v>5.651331424713135</v>
+        <v>5.651330471038818</v>
       </c>
       <c r="D132">
-        <v>22.69537734985352</v>
+        <v>22.65273284912109</v>
       </c>
       <c r="E132">
-        <v>25.4494800567627</v>
+        <v>25.4494743347168</v>
       </c>
       <c r="F132">
-        <v>36.71819305419922</v>
+        <v>36.66564559936523</v>
       </c>
       <c r="G132">
-        <v>46.83444595336914</v>
+        <v>46.83443450927734</v>
       </c>
       <c r="H132">
         <v>0.1049999967217445</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
-      <c r="A133" s="1">
+    <row r="133">
+      <c r="A133" s="2">
         <v>41214</v>
       </c>
       <c r="B133">
         <v>1416.180053710938</v>
       </c>
       <c r="C133">
-        <v>5.798184871673584</v>
+        <v>5.798186302185059</v>
       </c>
       <c r="D133">
-        <v>21.34252166748047</v>
+        <v>21.30241966247559</v>
       </c>
       <c r="E133">
-        <v>26.35019683837891</v>
+        <v>26.35019874572754</v>
       </c>
       <c r="F133">
-        <v>37.40724182128906</v>
+        <v>37.35373687744141</v>
       </c>
       <c r="G133">
-        <v>47.23351287841797</v>
+        <v>47.23351669311523</v>
       </c>
       <c r="H133">
         <v>0.07500000298023224</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
-      <c r="A134" s="1">
+    <row r="134">
+      <c r="A134" s="2">
         <v>41244</v>
       </c>
       <c r="B134">
         <v>1426.18994140625</v>
       </c>
       <c r="C134">
-        <v>6.557772159576416</v>
+        <v>6.557774066925049</v>
       </c>
       <c r="D134">
-        <v>21.4146728515625</v>
+        <v>21.37443542480469</v>
       </c>
       <c r="E134">
-        <v>27.43636703491211</v>
+        <v>27.43638038635254</v>
       </c>
       <c r="F134">
-        <v>37.62083435058594</v>
+        <v>37.5670051574707</v>
       </c>
       <c r="G134">
-        <v>45.92127990722656</v>
+        <v>45.92128753662109</v>
       </c>
       <c r="H134">
         <v>0.03500000014901161</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
-      <c r="A135" s="1">
+    <row r="135">
+      <c r="A135" s="2">
         <v>41275</v>
       </c>
       <c r="B135">
         <v>1498.109985351562</v>
       </c>
       <c r="C135">
-        <v>6.606062889099121</v>
+        <v>6.606063365936279</v>
       </c>
       <c r="D135">
-        <v>22.00796890258789</v>
+        <v>21.96661758422852</v>
       </c>
       <c r="E135">
-        <v>29.23966407775879</v>
+        <v>29.23965263366699</v>
       </c>
       <c r="F135">
-        <v>40.9542236328125</v>
+        <v>40.89562606811523</v>
       </c>
       <c r="G135">
-        <v>51.25094223022461</v>
+        <v>51.25092315673828</v>
       </c>
       <c r="H135">
         <v>0.06499999761581421</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
-      <c r="A136" s="1">
+    <row r="136">
+      <c r="A136" s="2">
         <v>41306</v>
       </c>
       <c r="B136">
         <v>1514.680053710938</v>
       </c>
       <c r="C136">
-        <v>6.432622909545898</v>
+        <v>6.432621955871582</v>
       </c>
       <c r="D136">
-        <v>22.47311592102051</v>
+        <v>22.43088912963867</v>
       </c>
       <c r="E136">
-        <v>28.19392585754395</v>
+        <v>28.19391632080078</v>
       </c>
       <c r="F136">
-        <v>42.07736206054688</v>
+        <v>42.01715469360352</v>
       </c>
       <c r="G136">
-        <v>51.94647598266602</v>
+        <v>51.94646072387695</v>
       </c>
       <c r="H136">
         <v>0.1000000014901161</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
-      <c r="A137" s="1">
+    <row r="137">
+      <c r="A137" s="2">
         <v>41334</v>
       </c>
       <c r="B137">
         <v>1569.18994140625</v>
       </c>
       <c r="C137">
-        <v>6.708084583282471</v>
+        <v>6.708089351654053</v>
       </c>
       <c r="D137">
-        <v>23.12790870666504</v>
+        <v>23.08444404602051</v>
       </c>
       <c r="E137">
-        <v>26.62118911743164</v>
+        <v>26.62118530273438</v>
       </c>
       <c r="F137">
-        <v>43.7170524597168</v>
+        <v>43.65448760986328</v>
       </c>
       <c r="G137">
-        <v>52.54651641845703</v>
+        <v>52.54655075073242</v>
       </c>
       <c r="H137">
         <v>0.06499999761581421</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
-      <c r="A138" s="1">
+    <row r="138">
+      <c r="A138" s="2">
         <v>41365</v>
       </c>
       <c r="B138">
         <v>1597.569946289062</v>
       </c>
       <c r="C138">
-        <v>6.993752956390381</v>
+        <v>6.993753433227539</v>
       </c>
       <c r="D138">
-        <v>26.75755500793457</v>
+        <v>26.70727729797363</v>
       </c>
       <c r="E138">
-        <v>26.99172782897949</v>
+        <v>26.99172592163086</v>
       </c>
       <c r="F138">
-        <v>42.63161849975586</v>
+        <v>42.57062149047852</v>
       </c>
       <c r="G138">
-        <v>52.73338317871094</v>
+        <v>52.7333984375</v>
       </c>
       <c r="H138">
         <v>0.04500000178813934</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
-      <c r="A139" s="1">
+    <row r="139">
+      <c r="A139" s="2">
         <v>41395</v>
       </c>
       <c r="B139">
         <v>1630.739990234375</v>
       </c>
       <c r="C139">
-        <v>8.057464599609375</v>
+        <v>8.057463645935059</v>
       </c>
       <c r="D139">
-        <v>28.41048812866211</v>
+        <v>28.35711097717285</v>
       </c>
       <c r="E139">
         <v>27.81514930725098</v>
       </c>
       <c r="F139">
-        <v>41.28207015991211</v>
+        <v>41.22300720214844</v>
       </c>
       <c r="G139">
-        <v>52.72652053833008</v>
+        <v>52.72651290893555</v>
       </c>
       <c r="H139">
         <v>0.02999999932944775</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
-      <c r="A140" s="1">
+    <row r="140">
+      <c r="A140" s="2">
         <v>41426</v>
       </c>
       <c r="B140">
         <v>1606.280029296875</v>
       </c>
       <c r="C140">
-        <v>7.949552059173584</v>
+        <v>7.949551105499268</v>
       </c>
       <c r="D140">
-        <v>28.117431640625</v>
+        <v>28.06459426879883</v>
       </c>
       <c r="E140">
-        <v>25.28724479675293</v>
+        <v>25.28725051879883</v>
       </c>
       <c r="F140">
-        <v>38.14477157592773</v>
+        <v>38.09019470214844</v>
       </c>
       <c r="G140">
-        <v>52.88451766967773</v>
+        <v>52.884521484375</v>
       </c>
       <c r="H140">
         <v>0.02999999932944775</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="1">
+    <row r="141">
+      <c r="A141" s="2">
         <v>41456</v>
       </c>
       <c r="B141">
         <v>1685.72998046875</v>
       </c>
       <c r="C141">
-        <v>8.725191116333008</v>
+        <v>8.725188255310059</v>
       </c>
       <c r="D141">
-        <v>25.91948318481445</v>
+        <v>25.87077713012695</v>
       </c>
       <c r="E141">
-        <v>26.73945617675781</v>
+        <v>26.73945808410645</v>
       </c>
       <c r="F141">
-        <v>41.24325942993164</v>
+        <v>41.18423461914062</v>
       </c>
       <c r="G141">
-        <v>55.57132720947266</v>
+        <v>55.57131195068359</v>
       </c>
       <c r="H141">
         <v>0.02999999932944775</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
-      <c r="A142" s="1">
+    <row r="142">
+      <c r="A142" s="2">
         <v>41487</v>
       </c>
       <c r="B142">
         <v>1632.969970703125</v>
       </c>
       <c r="C142">
-        <v>8.368533134460449</v>
+        <v>8.368532180786133</v>
       </c>
       <c r="D142">
-        <v>27.3809986114502</v>
+        <v>27.32955169677734</v>
       </c>
       <c r="E142">
         <v>26.33444023132324</v>
       </c>
       <c r="F142">
-        <v>40.28049468994141</v>
+        <v>40.22286224365234</v>
       </c>
       <c r="G142">
-        <v>53.90348434448242</v>
+        <v>53.90347671508789</v>
       </c>
       <c r="H142">
         <v>0.01999999955296516</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
-      <c r="A143" s="1">
+    <row r="143">
+      <c r="A143" s="2">
         <v>41518</v>
       </c>
       <c r="B143">
         <v>1681.550048828125</v>
       </c>
       <c r="C143">
-        <v>8.72002124786377</v>
+        <v>8.720022201538086</v>
       </c>
       <c r="D143">
-        <v>27.28261947631836</v>
+        <v>27.23134994506836</v>
       </c>
       <c r="E143">
-        <v>27.41724014282227</v>
+        <v>27.41723442077637</v>
       </c>
       <c r="F143">
-        <v>39.44197845458984</v>
+        <v>39.38554382324219</v>
       </c>
       <c r="G143">
-        <v>52.31177520751953</v>
+        <v>52.31178283691406</v>
       </c>
       <c r="H143">
         <v>0.004999999888241291</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
-      <c r="A144" s="1">
+    <row r="144">
+      <c r="A144" s="2">
         <v>41548</v>
       </c>
       <c r="B144">
         <v>1756.5400390625</v>
       </c>
       <c r="C144">
-        <v>8.894583702087402</v>
+        <v>8.894587516784668</v>
       </c>
       <c r="D144">
-        <v>29.02877998352051</v>
+        <v>28.9742431640625</v>
       </c>
       <c r="E144">
-        <v>27.79034042358398</v>
+        <v>27.79033088684082</v>
       </c>
       <c r="F144">
-        <v>39.04229354858398</v>
+        <v>38.98644256591797</v>
       </c>
       <c r="G144">
-        <v>56.31964111328125</v>
+        <v>56.31965637207031</v>
       </c>
       <c r="H144">
         <v>0.03299999982118607</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="1">
+    <row r="145">
+      <c r="A145" s="2">
         <v>41579</v>
       </c>
       <c r="B145">
         <v>1805.81005859375</v>
       </c>
       <c r="C145">
-        <v>8.878989219665527</v>
+        <v>8.878990173339844</v>
       </c>
       <c r="D145">
-        <v>31.49567222595215</v>
+        <v>31.43648910522461</v>
       </c>
       <c r="E145">
-        <v>29.2752571105957</v>
+        <v>29.27525520324707</v>
       </c>
       <c r="F145">
-        <v>39.74480056762695</v>
+        <v>39.68793869018555</v>
       </c>
       <c r="G145">
-        <v>58.73981475830078</v>
+        <v>58.73983001708984</v>
       </c>
       <c r="H145">
         <v>0.05499999970197678</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
-      <c r="A146" s="1">
+    <row r="146">
+      <c r="A146" s="2">
         <v>41609</v>
       </c>
       <c r="B146">
         <v>1848.359985351562</v>
       </c>
       <c r="C146">
-        <v>8.021240234375</v>
+        <v>8.021243095397949</v>
       </c>
       <c r="D146">
-        <v>30.90093421936035</v>
+        <v>30.84287261962891</v>
       </c>
       <c r="E146">
-        <v>31.73904037475586</v>
+        <v>31.73905754089355</v>
       </c>
       <c r="F146">
-        <v>40.36209487915039</v>
+        <v>40.30435562133789</v>
       </c>
       <c r="G146">
-        <v>56.77998352050781</v>
+        <v>56.77997589111328</v>
       </c>
       <c r="H146">
         <v>0.06300000101327896</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
-      <c r="A147" s="1">
+    <row r="147">
+      <c r="A147" s="2">
         <v>41640</v>
       </c>
       <c r="B147">
         <v>1782.589965820312</v>
       </c>
       <c r="C147">
-        <v>7.83924674987793</v>
+        <v>7.839248657226562</v>
       </c>
       <c r="D147">
-        <v>31.25613594055176</v>
+        <v>31.19739723205566</v>
       </c>
       <c r="E147">
-        <v>30.70823860168457</v>
+        <v>30.70822334289551</v>
       </c>
       <c r="F147">
-        <v>42.74427032470703</v>
+        <v>42.68310928344727</v>
       </c>
       <c r="G147">
-        <v>53.84343338012695</v>
+        <v>53.84341812133789</v>
       </c>
       <c r="H147">
         <v>0.009999999776482582</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
-      <c r="A148" s="1">
+    <row r="148">
+      <c r="A148" s="2">
         <v>41671</v>
       </c>
       <c r="B148">
         <v>1859.449951171875</v>
       </c>
       <c r="C148">
-        <v>8.064576148986816</v>
+        <v>8.064574241638184</v>
       </c>
       <c r="D148">
-        <v>31.88162803649902</v>
+        <v>31.82174110412598</v>
       </c>
       <c r="E148">
-        <v>32.54740142822266</v>
+        <v>32.54739761352539</v>
       </c>
       <c r="F148">
-        <v>47.60412216186523</v>
+        <v>47.53598785400391</v>
       </c>
       <c r="G148">
-        <v>55.27699279785156</v>
+        <v>55.27700042724609</v>
       </c>
       <c r="H148">
         <v>0.0430000014603138</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
-      <c r="A149" s="1">
+    <row r="149">
+      <c r="A149" s="2">
         <v>41699</v>
       </c>
       <c r="B149">
@@ -4249,39 +4236,39 @@
         <v>8.174617767333984</v>
       </c>
       <c r="D149">
-        <v>34.1119384765625</v>
+        <v>34.04784393310547</v>
       </c>
       <c r="E149">
         <v>34.04536056518555</v>
       </c>
       <c r="F149">
-        <v>47.00516128540039</v>
+        <v>46.93790435791016</v>
       </c>
       <c r="G149">
-        <v>56.64028167724609</v>
+        <v>56.64030075073242</v>
       </c>
       <c r="H149">
         <v>0.02800000086426735</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="1">
+    <row r="150">
+      <c r="A150" s="2">
         <v>41730</v>
       </c>
       <c r="B150">
         <v>1883.949951171875</v>
       </c>
       <c r="C150">
-        <v>8.528960227966309</v>
+        <v>8.528962135314941</v>
       </c>
       <c r="D150">
-        <v>33.62094497680664</v>
+        <v>33.55777740478516</v>
       </c>
       <c r="E150">
-        <v>34.121826171875</v>
+        <v>34.12182235717773</v>
       </c>
       <c r="F150">
-        <v>47.19681549072266</v>
+        <v>47.12930297851562</v>
       </c>
       <c r="G150">
         <v>58.47410202026367</v>
@@ -4290,8 +4277,8 @@
         <v>0.01999999955296516</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
-      <c r="A151" s="1">
+    <row r="151">
+      <c r="A151" s="2">
         <v>41760</v>
       </c>
       <c r="B151">
@@ -4301,257 +4288,257 @@
         <v>8.682113647460938</v>
       </c>
       <c r="D151">
-        <v>34.31068801879883</v>
+        <v>34.2462043762207</v>
       </c>
       <c r="E151">
-        <v>35.07337188720703</v>
+        <v>35.07336807250977</v>
       </c>
       <c r="F151">
-        <v>48.20124053955078</v>
+        <v>48.13226318359375</v>
       </c>
       <c r="G151">
-        <v>57.2274055480957</v>
+        <v>57.22739791870117</v>
       </c>
       <c r="H151">
         <v>0.02999999932944775</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
-      <c r="A152" s="1">
+    <row r="152">
+      <c r="A152" s="2">
         <v>41791</v>
       </c>
       <c r="B152">
         <v>1960.22998046875</v>
       </c>
       <c r="C152">
-        <v>9.104598045349121</v>
+        <v>9.104597091674805</v>
       </c>
       <c r="D152">
-        <v>34.9476203918457</v>
+        <v>34.8819465637207</v>
       </c>
       <c r="E152">
-        <v>33.82968521118164</v>
+        <v>33.82967758178711</v>
       </c>
       <c r="F152">
-        <v>50.06133651733398</v>
+        <v>49.98968887329102</v>
       </c>
       <c r="G152">
-        <v>55.66905212402344</v>
+        <v>55.66905975341797</v>
       </c>
       <c r="H152">
         <v>0.01999999955296516</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
-      <c r="A153" s="1">
+    <row r="153">
+      <c r="A153" s="2">
         <v>41821</v>
       </c>
       <c r="B153">
         <v>1930.670043945312</v>
       </c>
       <c r="C153">
-        <v>9.052821159362793</v>
+        <v>9.052822113037109</v>
       </c>
       <c r="D153">
-        <v>36.17121887207031</v>
+        <v>36.10324478149414</v>
       </c>
       <c r="E153">
-        <v>33.81096649169922</v>
+        <v>33.81096267700195</v>
       </c>
       <c r="F153">
-        <v>49.16751098632812</v>
+        <v>49.09716796875</v>
       </c>
       <c r="G153">
-        <v>55.20694732666016</v>
+        <v>55.20697784423828</v>
       </c>
       <c r="H153">
         <v>0.01799999922513962</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
-      <c r="A154" s="1">
+    <row r="154">
+      <c r="A154" s="2">
         <v>41852</v>
       </c>
       <c r="B154">
         <v>2003.369995117188</v>
       </c>
       <c r="C154">
-        <v>9.260257720947266</v>
+        <v>9.260258674621582</v>
       </c>
       <c r="D154">
-        <v>38.31143569946289</v>
+        <v>38.23944854736328</v>
       </c>
       <c r="E154">
-        <v>34.7652702331543</v>
+        <v>34.76528167724609</v>
       </c>
       <c r="F154">
-        <v>51.59252548217773</v>
+        <v>51.51870346069336</v>
       </c>
       <c r="G154">
-        <v>59.34106063842773</v>
+        <v>59.34107208251953</v>
       </c>
       <c r="H154">
         <v>0.01799999922513962</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
-      <c r="A155" s="1">
+    <row r="155">
+      <c r="A155" s="2">
         <v>41883</v>
       </c>
       <c r="B155">
         <v>1972.2900390625</v>
       </c>
       <c r="C155">
-        <v>7.866700649261475</v>
+        <v>7.866701602935791</v>
       </c>
       <c r="D155">
-        <v>39.09570693969727</v>
+        <v>39.02225494384766</v>
       </c>
       <c r="E155">
-        <v>32.04466247558594</v>
+        <v>32.04465866088867</v>
       </c>
       <c r="F155">
-        <v>52.63964080810547</v>
+        <v>52.56431198120117</v>
       </c>
       <c r="G155">
-        <v>59.7908935546875</v>
+        <v>59.79088592529297</v>
       </c>
       <c r="H155">
         <v>0.0130000002682209</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
-      <c r="A156" s="1">
+    <row r="156">
+      <c r="A156" s="2">
         <v>41913</v>
       </c>
       <c r="B156">
         <v>2018.050048828125</v>
       </c>
       <c r="C156">
-        <v>7.561120510101318</v>
+        <v>7.561120986938477</v>
       </c>
       <c r="D156">
-        <v>39.59326553344727</v>
+        <v>39.51886367797852</v>
       </c>
       <c r="E156">
-        <v>32.79043579101562</v>
+        <v>32.79041290283203</v>
       </c>
       <c r="F156">
-        <v>53.84098815917969</v>
+        <v>53.76393127441406</v>
       </c>
       <c r="G156">
-        <v>62.78924560546875</v>
+        <v>62.78922653198242</v>
       </c>
       <c r="H156">
         <v>0.003000000026077032</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
-      <c r="A157" s="1">
+    <row r="157">
+      <c r="A157" s="2">
         <v>41944</v>
       </c>
       <c r="B157">
         <v>2067.56005859375</v>
       </c>
       <c r="C157">
-        <v>8.441193580627441</v>
+        <v>8.441196441650391</v>
       </c>
       <c r="D157">
-        <v>40.57280349731445</v>
+        <v>40.49656295776367</v>
       </c>
       <c r="E157">
-        <v>35.61182403564453</v>
+        <v>35.61182022094727</v>
       </c>
       <c r="F157">
-        <v>55.69618225097656</v>
+        <v>55.61647796630859</v>
       </c>
       <c r="G157">
-        <v>65.06279754638672</v>
+        <v>65.06281280517578</v>
       </c>
       <c r="H157">
         <v>0.004999999888241291</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
-      <c r="A158" s="1">
+    <row r="158">
+      <c r="A158" s="2">
         <v>41974</v>
       </c>
       <c r="B158">
         <v>2058.89990234375</v>
       </c>
       <c r="C158">
-        <v>8.317770957946777</v>
+        <v>8.31777286529541</v>
       </c>
       <c r="D158">
-        <v>39.41867065429688</v>
+        <v>39.34460067749023</v>
       </c>
       <c r="E158">
-        <v>37.76147842407227</v>
+        <v>37.76145553588867</v>
       </c>
       <c r="F158">
-        <v>56.40751266479492</v>
+        <v>56.32678604125977</v>
       </c>
       <c r="G158">
-        <v>65.53766632080078</v>
+        <v>65.53765869140625</v>
       </c>
       <c r="H158">
         <v>0.03700000047683716</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
-      <c r="A159" s="1">
+    <row r="159">
+      <c r="A159" s="2">
         <v>42005</v>
       </c>
       <c r="B159">
         <v>1994.989990234375</v>
       </c>
       <c r="C159">
-        <v>7.97438383102417</v>
+        <v>7.974380970001221</v>
       </c>
       <c r="D159">
-        <v>34.28449249267578</v>
+        <v>34.22005462646484</v>
       </c>
       <c r="E159">
         <v>35.27064895629883</v>
       </c>
       <c r="F159">
-        <v>58.86853408813477</v>
+        <v>58.78427886962891</v>
       </c>
       <c r="G159">
-        <v>61.07650756835938</v>
+        <v>61.07653045654297</v>
       </c>
       <c r="H159">
         <v>0.004999999888241291</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
-      <c r="A160" s="1">
+    <row r="160">
+      <c r="A160" s="2">
         <v>42036</v>
       </c>
       <c r="B160">
         <v>2104.5</v>
       </c>
       <c r="C160">
-        <v>8.858016967773438</v>
+        <v>8.858016014099121</v>
       </c>
       <c r="D160">
-        <v>37.47707366943359</v>
+        <v>37.40665817260742</v>
       </c>
       <c r="E160">
-        <v>36.89566802978516</v>
+        <v>36.89568328857422</v>
       </c>
       <c r="F160">
-        <v>57.78210067749023</v>
+        <v>57.69940185546875</v>
       </c>
       <c r="G160">
-        <v>61.68516159057617</v>
+        <v>61.68517303466797</v>
       </c>
       <c r="H160">
         <v>0.00800000037997961</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
-      <c r="A161" s="1">
+    <row r="161">
+      <c r="A161" s="2">
         <v>42064</v>
       </c>
       <c r="B161">
@@ -4561,75 +4548,75 @@
         <v>8.749593734741211</v>
       </c>
       <c r="D161">
-        <v>34.75068664550781</v>
+        <v>34.68538665771484</v>
       </c>
       <c r="E161">
-        <v>36.33154296875</v>
+        <v>36.33155059814453</v>
       </c>
       <c r="F161">
-        <v>59.82426834106445</v>
+        <v>59.73867034912109</v>
       </c>
       <c r="G161">
-        <v>59.37368392944336</v>
+        <v>59.37370300292969</v>
       </c>
       <c r="H161">
         <v>0.02500000037252903</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
-      <c r="A162" s="1">
+    <row r="162">
+      <c r="A162" s="2">
         <v>42095</v>
       </c>
       <c r="B162">
         <v>2085.510009765625</v>
       </c>
       <c r="C162">
-        <v>8.646029472351074</v>
+        <v>8.646032333374023</v>
       </c>
       <c r="D162">
-        <v>41.57091903686523</v>
+        <v>41.49280548095703</v>
       </c>
       <c r="E162">
-        <v>36.85602951049805</v>
+        <v>36.85602188110352</v>
       </c>
       <c r="F162">
-        <v>59.18198013305664</v>
+        <v>59.0972785949707</v>
       </c>
       <c r="G162">
-        <v>58.07634353637695</v>
+        <v>58.07632827758789</v>
       </c>
       <c r="H162">
         <v>0.004999999888241291</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
-      <c r="A163" s="1">
+    <row r="163">
+      <c r="A163" s="2">
         <v>42125</v>
       </c>
       <c r="B163">
         <v>2107.389892578125</v>
       </c>
       <c r="C163">
-        <v>8.301283836364746</v>
+        <v>8.30128288269043</v>
       </c>
       <c r="D163">
-        <v>40.30990219116211</v>
+        <v>40.23415374755859</v>
       </c>
       <c r="E163">
-        <v>36.74618530273438</v>
+        <v>36.74619674682617</v>
       </c>
       <c r="F163">
-        <v>65.42020416259766</v>
+        <v>65.32657623291016</v>
       </c>
       <c r="G163">
-        <v>57.25826644897461</v>
+        <v>57.25823974609375</v>
       </c>
       <c r="H163">
         <v>0.003000000026077032</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
-      <c r="A164" s="1">
+    <row r="164">
+      <c r="A164" s="2">
         <v>42156</v>
       </c>
       <c r="B164">
@@ -4639,195 +4626,195 @@
         <v>8.213728904724121</v>
       </c>
       <c r="D164">
-        <v>37.97869110107422</v>
+        <v>37.90732955932617</v>
       </c>
       <c r="E164">
-        <v>34.05084991455078</v>
+        <v>34.05085754394531</v>
       </c>
       <c r="F164">
-        <v>69.22600555419922</v>
+        <v>69.12696075439453</v>
       </c>
       <c r="G164">
-        <v>57.1486930847168</v>
+        <v>57.14870071411133</v>
       </c>
       <c r="H164">
         <v>0.009999999776482582</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
-      <c r="A165" s="1">
+    <row r="165">
+      <c r="A165" s="2">
         <v>42186</v>
       </c>
       <c r="B165">
         <v>2103.840087890625</v>
       </c>
       <c r="C165">
-        <v>8.198152542114258</v>
+        <v>8.198150634765625</v>
       </c>
       <c r="D165">
-        <v>40.17224884033203</v>
+        <v>40.09677505493164</v>
       </c>
       <c r="E165">
-        <v>33.87255859375</v>
+        <v>33.87256240844727</v>
       </c>
       <c r="F165">
-        <v>70.07176971435547</v>
+        <v>69.97146606445312</v>
       </c>
       <c r="G165">
-        <v>56.48260116577148</v>
+        <v>56.48257827758789</v>
       </c>
       <c r="H165">
         <v>0.05799999833106995</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
-      <c r="A166" s="1">
+    <row r="166">
+      <c r="A166" s="2">
         <v>42217</v>
       </c>
       <c r="B166">
         <v>1972.180053710938</v>
       </c>
       <c r="C166">
-        <v>7.66745662689209</v>
+        <v>7.667455196380615</v>
       </c>
       <c r="D166">
-        <v>37.68362426757812</v>
+        <v>37.61282348632812</v>
       </c>
       <c r="E166">
-        <v>31.45551872253418</v>
+        <v>31.45550155639648</v>
       </c>
       <c r="F166">
-        <v>68.69190979003906</v>
+        <v>68.59360504150391</v>
       </c>
       <c r="G166">
-        <v>52.04203796386719</v>
+        <v>52.04204940795898</v>
       </c>
       <c r="H166">
         <v>0.003000000026077032</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
-      <c r="A167" s="1">
+    <row r="167">
+      <c r="A167" s="2">
         <v>42248</v>
       </c>
       <c r="B167">
         <v>1920.030029296875</v>
       </c>
       <c r="C167">
-        <v>7.501612663269043</v>
+        <v>7.501614570617676</v>
       </c>
       <c r="D167">
-        <v>38.32438659667969</v>
+        <v>38.25236892700195</v>
       </c>
       <c r="E167">
-        <v>30.63287162780762</v>
+        <v>30.63286209106445</v>
       </c>
       <c r="F167">
-        <v>69.80966186523438</v>
+        <v>69.70977020263672</v>
       </c>
       <c r="G167">
-        <v>52.97727966308594</v>
+        <v>52.9772834777832</v>
       </c>
       <c r="H167">
         <v>0.004999999888241291</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="1">
+    <row r="168">
+      <c r="A168" s="2">
         <v>42278</v>
       </c>
       <c r="B168">
         <v>2079.360107421875</v>
       </c>
       <c r="C168">
-        <v>8.270414352416992</v>
+        <v>8.270410537719727</v>
       </c>
       <c r="D168">
-        <v>45.58056640625</v>
+        <v>45.49491500854492</v>
       </c>
       <c r="E168">
-        <v>33.07059478759766</v>
+        <v>33.07058715820312</v>
       </c>
       <c r="F168">
-        <v>68.04129028320312</v>
+        <v>67.94390106201172</v>
       </c>
       <c r="G168">
-        <v>56.7524528503418</v>
+        <v>56.75246429443359</v>
       </c>
       <c r="H168">
         <v>0.06800000369548798</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
-      <c r="A169" s="1">
+    <row r="169">
+      <c r="A169" s="2">
         <v>42309</v>
       </c>
       <c r="B169">
         <v>2080.409912109375</v>
       </c>
       <c r="C169">
-        <v>8.002365112304688</v>
+        <v>8.002361297607422</v>
       </c>
       <c r="D169">
-        <v>47.37844085693359</v>
+        <v>47.28941345214844</v>
       </c>
       <c r="E169">
-        <v>33.1812858581543</v>
+        <v>33.18128204345703</v>
       </c>
       <c r="F169">
-        <v>68.86722564697266</v>
+        <v>68.76864624023438</v>
       </c>
       <c r="G169">
-        <v>55.60820388793945</v>
+        <v>55.60821533203125</v>
       </c>
       <c r="H169">
         <v>0.1700000017881393</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
-      <c r="A170" s="1">
+    <row r="170">
+      <c r="A170" s="2">
         <v>42339</v>
       </c>
       <c r="B170">
         <v>2043.93994140625</v>
       </c>
       <c r="C170">
-        <v>7.868338584899902</v>
+        <v>7.868341445922852</v>
       </c>
       <c r="D170">
-        <v>48.36349487304688</v>
+        <v>48.27263259887695</v>
       </c>
       <c r="E170">
-        <v>31.10372161865234</v>
+        <v>31.10371589660645</v>
       </c>
       <c r="F170">
-        <v>70.73074340820312</v>
+        <v>70.62955474853516</v>
       </c>
       <c r="G170">
-        <v>59.00384140014648</v>
+        <v>59.00381851196289</v>
       </c>
       <c r="H170">
         <v>0.1480000019073486</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
-      <c r="A171" s="1">
+    <row r="171">
+      <c r="A171" s="2">
         <v>42370</v>
       </c>
       <c r="B171">
         <v>1940.239990234375</v>
       </c>
       <c r="C171">
-        <v>6.892583847045898</v>
+        <v>6.892585754394531</v>
       </c>
       <c r="D171">
-        <v>48.02351760864258</v>
+        <v>47.93328094482422</v>
       </c>
       <c r="E171">
-        <v>31.04387664794922</v>
+        <v>31.04388046264648</v>
       </c>
       <c r="F171">
-        <v>66.39925384521484</v>
+        <v>66.30427551269531</v>
       </c>
       <c r="G171">
         <v>61.22700881958008</v>
@@ -4836,102 +4823,102 @@
         <v>0.300000011920929</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
-      <c r="A172" s="1">
+    <row r="172">
+      <c r="A172" s="2">
         <v>42401</v>
       </c>
       <c r="B172">
         <v>1932.22998046875</v>
       </c>
       <c r="C172">
-        <v>7.221628189086914</v>
+        <v>7.22162914276123</v>
       </c>
       <c r="D172">
-        <v>44.67200088500977</v>
+        <v>44.58805465698242</v>
       </c>
       <c r="E172">
-        <v>31.4456958770752</v>
+        <v>31.44570350646973</v>
       </c>
       <c r="F172">
-        <v>60.86018371582031</v>
+        <v>60.77312469482422</v>
       </c>
       <c r="G172">
-        <v>60.17768859863281</v>
+        <v>60.17771148681641</v>
       </c>
       <c r="H172">
         <v>0.3079999983310699</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
-      <c r="A173" s="1">
+    <row r="173">
+      <c r="A173" s="2">
         <v>42430</v>
       </c>
       <c r="B173">
         <v>2059.739990234375</v>
       </c>
       <c r="C173">
-        <v>7.7931227684021</v>
+        <v>7.793124675750732</v>
       </c>
       <c r="D173">
-        <v>48.49125671386719</v>
+        <v>48.40013122558594</v>
       </c>
       <c r="E173">
-        <v>34.97673034667969</v>
+        <v>34.97671508789062</v>
       </c>
       <c r="F173">
-        <v>60.8686637878418</v>
+        <v>60.78156661987305</v>
       </c>
       <c r="G173">
-        <v>61.69167327880859</v>
+        <v>61.69168090820312</v>
       </c>
       <c r="H173">
         <v>0.193000003695488</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
-      <c r="A174" s="1">
+    <row r="174">
+      <c r="A174" s="2">
         <v>42461</v>
       </c>
       <c r="B174">
         <v>2065.300048828125</v>
       </c>
       <c r="C174">
-        <v>7.914097309112549</v>
+        <v>7.9140944480896</v>
       </c>
       <c r="D174">
-        <v>43.78522109985352</v>
+        <v>43.70295333862305</v>
       </c>
       <c r="E174">
-        <v>34.20603561401367</v>
+        <v>34.2060432434082</v>
       </c>
       <c r="F174">
-        <v>63.84404373168945</v>
+        <v>63.75268936157227</v>
       </c>
       <c r="G174">
-        <v>60.54217529296875</v>
+        <v>60.54218673706055</v>
       </c>
       <c r="H174">
         <v>0.193000003695488</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
-      <c r="A175" s="1">
+    <row r="175">
+      <c r="A175" s="2">
         <v>42491</v>
       </c>
       <c r="B175">
         <v>2096.949951171875</v>
       </c>
       <c r="C175">
-        <v>7.87324047088623</v>
+        <v>7.873241424560547</v>
       </c>
       <c r="D175">
-        <v>46.85879516601562</v>
+        <v>46.77075958251953</v>
       </c>
       <c r="E175">
-        <v>34.49781036376953</v>
+        <v>34.49781799316406</v>
       </c>
       <c r="F175">
-        <v>63.84494781494141</v>
+        <v>63.75357818603516</v>
       </c>
       <c r="G175">
         <v>61.23738479614258</v>
@@ -4940,112 +4927,112 @@
         <v>0.2829999923706055</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
-      <c r="A176" s="1">
+    <row r="176">
+      <c r="A176" s="2">
         <v>42522</v>
       </c>
       <c r="B176">
         <v>2098.860107421875</v>
       </c>
       <c r="C176">
-        <v>7.336297512054443</v>
+        <v>7.336295604705811</v>
       </c>
       <c r="D176">
-        <v>45.2408561706543</v>
+        <v>45.15584182739258</v>
       </c>
       <c r="E176">
         <v>35.12426376342773</v>
       </c>
       <c r="F176">
-        <v>67.01039123535156</v>
+        <v>66.91448974609375</v>
       </c>
       <c r="G176">
-        <v>63.98036956787109</v>
+        <v>63.98036193847656</v>
       </c>
       <c r="H176">
         <v>0.2479999959468842</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
-      <c r="A177" s="1">
+    <row r="177">
+      <c r="A177" s="2">
         <v>42552</v>
       </c>
       <c r="B177">
         <v>2173.60009765625</v>
       </c>
       <c r="C177">
-        <v>7.469842910766602</v>
+        <v>7.469841480255127</v>
       </c>
       <c r="D177">
-        <v>50.11240005493164</v>
+        <v>50.01823806762695</v>
       </c>
       <c r="E177">
-        <v>35.34821701049805</v>
+        <v>35.34821319580078</v>
       </c>
       <c r="F177">
-        <v>70.53321075439453</v>
+        <v>70.43229675292969</v>
       </c>
       <c r="G177">
-        <v>65.18235778808594</v>
+        <v>65.182373046875</v>
       </c>
       <c r="H177">
         <v>0.239999994635582</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
-      <c r="A178" s="1">
+    <row r="178">
+      <c r="A178" s="2">
         <v>42583</v>
       </c>
       <c r="B178">
         <v>2170.949951171875</v>
       </c>
       <c r="C178">
-        <v>7.434441566467285</v>
+        <v>7.434439659118652</v>
       </c>
       <c r="D178">
-        <v>51.11865615844727</v>
+        <v>51.02259826660156</v>
       </c>
       <c r="E178">
         <v>35.50324630737305</v>
       </c>
       <c r="F178">
-        <v>66.58101654052734</v>
+        <v>66.48574066162109</v>
       </c>
       <c r="G178">
-        <v>66.49225616455078</v>
+        <v>66.49226379394531</v>
       </c>
       <c r="H178">
         <v>0.3199999928474426</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
-      <c r="A179" s="1">
+    <row r="179">
+      <c r="A179" s="2">
         <v>42614</v>
       </c>
       <c r="B179">
         <v>2168.27001953125</v>
       </c>
       <c r="C179">
-        <v>7.121721744537354</v>
+        <v>7.121723175048828</v>
       </c>
       <c r="D179">
-        <v>51.24319458007812</v>
+        <v>51.14691925048828</v>
       </c>
       <c r="E179">
-        <v>33.83230209350586</v>
+        <v>33.83229446411133</v>
       </c>
       <c r="F179">
-        <v>68.73045349121094</v>
+        <v>68.63208770751953</v>
       </c>
       <c r="G179">
-        <v>68.35047912597656</v>
+        <v>68.35047149658203</v>
       </c>
       <c r="H179">
         <v>0.2599999904632568</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
-      <c r="A180" s="1">
+    <row r="180">
+      <c r="A180" s="2">
         <v>42644</v>
       </c>
       <c r="B180">
@@ -5055,65 +5042,65 @@
         <v>7.013309001922607</v>
       </c>
       <c r="D180">
-        <v>53.30715942382812</v>
+        <v>53.20699691772461</v>
       </c>
       <c r="E180">
-        <v>33.21976089477539</v>
+        <v>33.21977233886719</v>
       </c>
       <c r="F180">
-        <v>63.23269271850586</v>
+        <v>63.14222717285156</v>
       </c>
       <c r="G180">
-        <v>66.61420440673828</v>
+        <v>66.61425018310547</v>
       </c>
       <c r="H180">
         <v>0.2949999868869781</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
-      <c r="A181" s="1">
+    <row r="181">
+      <c r="A181" s="2">
         <v>42675</v>
       </c>
       <c r="B181">
         <v>2198.81005859375</v>
       </c>
       <c r="C181">
-        <v>7.14473295211792</v>
+        <v>7.144732475280762</v>
       </c>
       <c r="D181">
-        <v>53.97180557250977</v>
+        <v>53.87039184570312</v>
       </c>
       <c r="E181">
-        <v>34.75019836425781</v>
+        <v>34.75019454956055</v>
       </c>
       <c r="F181">
-        <v>57.85444641113281</v>
+        <v>57.77166366577148</v>
       </c>
       <c r="G181">
-        <v>63.28350067138672</v>
+        <v>63.28350448608398</v>
       </c>
       <c r="H181">
         <v>0.4679999947547913</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
-      <c r="A182" s="1">
+    <row r="182">
+      <c r="A182" s="2">
         <v>42705</v>
       </c>
       <c r="B182">
         <v>2238.830078125</v>
       </c>
       <c r="C182">
-        <v>7.246289253234863</v>
+        <v>7.24629020690918</v>
       </c>
       <c r="D182">
-        <v>55.6556282043457</v>
+        <v>55.55105590820312</v>
       </c>
       <c r="E182">
         <v>33.24571228027344</v>
       </c>
       <c r="F182">
-        <v>63.39681243896484</v>
+        <v>63.30608749389648</v>
       </c>
       <c r="G182">
         <v>64.52677917480469</v>
@@ -5122,476 +5109,476 @@
         <v>0.4799999892711639</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
-      <c r="A183" s="1">
+    <row r="183">
+      <c r="A183" s="2">
         <v>42736</v>
       </c>
       <c r="B183">
         <v>2278.8701171875</v>
       </c>
       <c r="C183">
-        <v>7.502684116363525</v>
+        <v>7.502686500549316</v>
       </c>
       <c r="D183">
-        <v>57.90370559692383</v>
+        <v>57.79489517211914</v>
       </c>
       <c r="E183">
-        <v>34.81685638427734</v>
+        <v>34.81685256958008</v>
       </c>
       <c r="F183">
-        <v>66.39644622802734</v>
+        <v>66.30140686035156</v>
       </c>
       <c r="G183">
-        <v>67.76100158691406</v>
+        <v>67.760986328125</v>
       </c>
       <c r="H183">
         <v>0.5</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
-      <c r="A184" s="1">
+    <row r="184">
+      <c r="A184" s="2">
         <v>42767</v>
       </c>
       <c r="B184">
         <v>2363.639892578125</v>
       </c>
       <c r="C184">
-        <v>7.605878829956055</v>
+        <v>7.605876922607422</v>
       </c>
       <c r="D184">
-        <v>57.65101623535156</v>
+        <v>57.54268264770508</v>
       </c>
       <c r="E184">
-        <v>36.96957397460938</v>
+        <v>36.96957015991211</v>
       </c>
       <c r="F184">
-        <v>71.85884857177734</v>
+        <v>71.75605773925781</v>
       </c>
       <c r="G184">
-        <v>70.44511413574219</v>
+        <v>70.44510650634766</v>
       </c>
       <c r="H184">
         <v>0.5230000019073486</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
-      <c r="A185" s="1">
+    <row r="185">
+      <c r="A185" s="2">
         <v>42795</v>
       </c>
       <c r="B185">
         <v>2362.719970703125</v>
       </c>
       <c r="C185">
-        <v>7.065633773803711</v>
+        <v>7.065635204315186</v>
       </c>
       <c r="D185">
-        <v>59.34504699707031</v>
+        <v>59.23353576660156</v>
       </c>
       <c r="E185">
-        <v>38.72300338745117</v>
+        <v>38.72300720214844</v>
       </c>
       <c r="F185">
-        <v>72.98695373535156</v>
+        <v>72.88250732421875</v>
       </c>
       <c r="G185">
-        <v>69.50143432617188</v>
+        <v>69.50144195556641</v>
       </c>
       <c r="H185">
         <v>0.7379999756813049</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
-      <c r="A186" s="1">
+    <row r="186">
+      <c r="A186" s="2">
         <v>42826</v>
       </c>
       <c r="B186">
         <v>2384.199951171875</v>
       </c>
       <c r="C186">
-        <v>7.056275844573975</v>
+        <v>7.056277751922607</v>
       </c>
       <c r="D186">
-        <v>61.68785858154297</v>
+        <v>61.57194900512695</v>
       </c>
       <c r="E186">
-        <v>39.19495391845703</v>
+        <v>39.19496154785156</v>
       </c>
       <c r="F186">
-        <v>71.20805358886719</v>
+        <v>71.10617065429688</v>
       </c>
       <c r="G186">
-        <v>68.06938171386719</v>
+        <v>68.06939697265625</v>
       </c>
       <c r="H186">
         <v>0.7799999713897705</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
-      <c r="A187" s="1">
+    <row r="187">
+      <c r="A187" s="2">
         <v>42856</v>
       </c>
       <c r="B187">
         <v>2411.800048828125</v>
       </c>
       <c r="C187">
-        <v>6.840958595275879</v>
+        <v>6.840959072113037</v>
       </c>
       <c r="D187">
-        <v>63.29204177856445</v>
+        <v>63.17313003540039</v>
       </c>
       <c r="E187">
         <v>39.56982421875</v>
       </c>
       <c r="F187">
-        <v>69.49318695068359</v>
+        <v>69.39374542236328</v>
       </c>
       <c r="G187">
-        <v>68.66175842285156</v>
+        <v>68.66176605224609</v>
       </c>
       <c r="H187">
         <v>0.949999988079071</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
-      <c r="A188" s="1">
+    <row r="188">
+      <c r="A188" s="2">
         <v>42887</v>
       </c>
       <c r="B188">
         <v>2423.409912109375</v>
       </c>
       <c r="C188">
-        <v>6.88402271270752</v>
+        <v>6.884020805358887</v>
       </c>
       <c r="D188">
-        <v>62.46737670898438</v>
+        <v>62.35002899169922</v>
       </c>
       <c r="E188">
-        <v>43.71075439453125</v>
+        <v>43.71075057983398</v>
       </c>
       <c r="F188">
-        <v>71.87745666503906</v>
+        <v>71.77460479736328</v>
       </c>
       <c r="G188">
-        <v>67.92908477783203</v>
+        <v>67.92910003662109</v>
       </c>
       <c r="H188">
         <v>0.9929999709129333</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
-      <c r="A189" s="1">
+    <row r="189">
+      <c r="A189" s="2">
         <v>42917</v>
       </c>
       <c r="B189">
         <v>2470.300048828125</v>
       </c>
       <c r="C189">
-        <v>6.991123676300049</v>
+        <v>6.991121292114258</v>
       </c>
       <c r="D189">
-        <v>65.88393402099609</v>
+        <v>65.76012420654297</v>
       </c>
       <c r="E189">
-        <v>43.69186019897461</v>
+        <v>43.69186401367188</v>
       </c>
       <c r="F189">
-        <v>72.19186401367188</v>
+        <v>72.08857727050781</v>
       </c>
       <c r="G189">
-        <v>71.34503173828125</v>
+        <v>71.34505462646484</v>
       </c>
       <c r="H189">
         <v>1.052999973297119</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
-      <c r="A190" s="1">
+    <row r="190">
+      <c r="A190" s="2">
         <v>42948</v>
       </c>
       <c r="B190">
         <v>2471.64990234375</v>
       </c>
       <c r="C190">
-        <v>6.872734546661377</v>
+        <v>6.872733592987061</v>
       </c>
       <c r="D190">
-        <v>68.120849609375</v>
+        <v>67.99284362792969</v>
       </c>
       <c r="E190">
-        <v>44.04190826416016</v>
+        <v>44.04190063476562</v>
       </c>
       <c r="F190">
-        <v>71.44816589355469</v>
+        <v>71.34595489501953</v>
       </c>
       <c r="G190">
-        <v>72.48412322998047</v>
+        <v>72.48414611816406</v>
       </c>
       <c r="H190">
         <v>0.9779999852180481</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
-      <c r="A191" s="1">
+    <row r="191">
+      <c r="A191" s="2">
         <v>42979</v>
       </c>
       <c r="B191">
         <v>2519.360107421875</v>
       </c>
       <c r="C191">
-        <v>7.458440780639648</v>
+        <v>7.458445072174072</v>
       </c>
       <c r="D191">
-        <v>67.86575317382812</v>
+        <v>67.73822784423828</v>
       </c>
       <c r="E191">
         <v>42.30926895141602</v>
       </c>
       <c r="F191">
-        <v>75.18361663818359</v>
+        <v>75.0760498046875</v>
       </c>
       <c r="G191">
-        <v>71.47074890136719</v>
+        <v>71.47074127197266</v>
       </c>
       <c r="H191">
         <v>1.027999997138977</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
-      <c r="A192" s="1">
+    <row r="192">
+      <c r="A192" s="2">
         <v>43009</v>
       </c>
       <c r="B192">
         <v>2575.260009765625</v>
       </c>
       <c r="C192">
-        <v>7.740306377410889</v>
+        <v>7.740303993225098</v>
       </c>
       <c r="D192">
-        <v>75.78297424316406</v>
+        <v>75.64057922363281</v>
       </c>
       <c r="E192">
-        <v>44.71636581420898</v>
+        <v>44.71636199951172</v>
       </c>
       <c r="F192">
-        <v>72.01947784423828</v>
+        <v>71.91642761230469</v>
       </c>
       <c r="G192">
-        <v>68.33396911621094</v>
+        <v>68.333984375</v>
       </c>
       <c r="H192">
         <v>1.123000025749207</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
-      <c r="A193" s="1">
+    <row r="193">
+      <c r="A193" s="2">
         <v>43040</v>
       </c>
       <c r="B193">
         <v>2647.580078125</v>
       </c>
       <c r="C193">
-        <v>7.898013114929199</v>
+        <v>7.898012161254883</v>
       </c>
       <c r="D193">
-        <v>77.07003021240234</v>
+        <v>76.92526245117188</v>
       </c>
       <c r="E193">
-        <v>43.09989929199219</v>
+        <v>43.09990310668945</v>
       </c>
       <c r="F193">
-        <v>74.86239624023438</v>
+        <v>74.75527954101562</v>
       </c>
       <c r="G193">
-        <v>71.22277069091797</v>
+        <v>71.22276306152344</v>
       </c>
       <c r="H193">
         <v>1.23800003528595</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
-      <c r="A194" s="1">
+    <row r="194">
+      <c r="A194" s="2">
         <v>43070</v>
       </c>
       <c r="B194">
         <v>2673.610107421875</v>
       </c>
       <c r="C194">
-        <v>7.879089832305908</v>
+        <v>7.879088401794434</v>
       </c>
       <c r="D194">
-        <v>78.32448577880859</v>
+        <v>78.17733001708984</v>
       </c>
       <c r="E194">
-        <v>41.53615188598633</v>
+        <v>41.53614044189453</v>
       </c>
       <c r="F194">
-        <v>74.70318603515625</v>
+        <v>74.59629821777344</v>
       </c>
       <c r="G194">
-        <v>72.71860504150391</v>
+        <v>72.71859741210938</v>
       </c>
       <c r="H194">
         <v>1.355000019073486</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
-      <c r="A195" s="1">
+    <row r="195">
+      <c r="A195" s="2">
         <v>43101</v>
       </c>
       <c r="B195">
         <v>2823.81005859375</v>
       </c>
       <c r="C195">
-        <v>7.090641975402832</v>
+        <v>7.090642929077148</v>
       </c>
       <c r="D195">
-        <v>86.99566650390625</v>
+        <v>86.83222198486328</v>
       </c>
       <c r="E195">
-        <v>45.49902725219727</v>
+        <v>45.49904251098633</v>
       </c>
       <c r="F195">
-        <v>72.0408935546875</v>
+        <v>71.93782806396484</v>
       </c>
       <c r="G195">
-        <v>68.85491180419922</v>
+        <v>68.85492706298828</v>
       </c>
       <c r="H195">
         <v>1.429999947547913</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
-      <c r="A196" s="1">
+    <row r="196">
+      <c r="A196" s="2">
         <v>43132</v>
       </c>
       <c r="B196">
         <v>2713.830078125</v>
       </c>
       <c r="C196">
-        <v>6.857950687408447</v>
+        <v>6.85795259475708</v>
       </c>
       <c r="D196">
-        <v>86.26361083984375</v>
+        <v>86.10149383544922</v>
       </c>
       <c r="E196">
-        <v>44.68763732910156</v>
+        <v>44.68764877319336</v>
       </c>
       <c r="F196">
-        <v>68.629638671875</v>
+        <v>68.53144836425781</v>
       </c>
       <c r="G196">
-        <v>62.61857223510742</v>
+        <v>62.61857986450195</v>
       </c>
       <c r="H196">
         <v>1.618000030517578</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
-      <c r="A197" s="1">
+    <row r="197">
+      <c r="A197" s="2">
         <v>43160</v>
       </c>
       <c r="B197">
         <v>2640.8701171875</v>
       </c>
       <c r="C197">
-        <v>7.161744117736816</v>
+        <v>7.161745548248291</v>
       </c>
       <c r="D197">
-        <v>83.9637451171875</v>
+        <v>83.80596160888672</v>
       </c>
       <c r="E197">
-        <v>40.34853363037109</v>
+        <v>40.3485221862793</v>
       </c>
       <c r="F197">
-        <v>68.94155120849609</v>
+        <v>68.84287261962891</v>
       </c>
       <c r="G197">
-        <v>63.22465133666992</v>
+        <v>63.22466659545898</v>
       </c>
       <c r="H197">
         <v>1.669999957084656</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
-      <c r="A198" s="1">
+    <row r="198">
+      <c r="A198" s="2">
         <v>43191</v>
       </c>
       <c r="B198">
         <v>2648.050048828125</v>
       </c>
       <c r="C198">
-        <v>7.3626389503479</v>
+        <v>7.362638473510742</v>
       </c>
       <c r="D198">
-        <v>86.03360748291016</v>
+        <v>85.87195587158203</v>
       </c>
       <c r="E198">
-        <v>40.44475173950195</v>
+        <v>40.44474029541016</v>
       </c>
       <c r="F198">
-        <v>72.23847198486328</v>
+        <v>72.13510894775391</v>
       </c>
       <c r="G198">
-        <v>58.22396087646484</v>
+        <v>58.22394180297852</v>
       </c>
       <c r="H198">
         <v>1.763000011444092</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
-      <c r="A199" s="1">
+    <row r="199">
+      <c r="A199" s="2">
         <v>43221</v>
       </c>
       <c r="B199">
         <v>2705.27001953125</v>
       </c>
       <c r="C199">
-        <v>7.565700054168701</v>
+        <v>7.565699100494385</v>
       </c>
       <c r="D199">
-        <v>91.32185363769531</v>
+        <v>91.15027618408203</v>
       </c>
       <c r="E199">
-        <v>41.37459945678711</v>
+        <v>41.37460708618164</v>
       </c>
       <c r="F199">
-        <v>76.29852294921875</v>
+        <v>76.1893310546875</v>
       </c>
       <c r="G199">
-        <v>58.89199829101562</v>
+        <v>58.89199066162109</v>
       </c>
       <c r="H199">
         <v>1.870000004768372</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
-      <c r="A200" s="1">
+    <row r="200">
+      <c r="A200" s="2">
         <v>43252</v>
       </c>
       <c r="B200">
         <v>2718.3701171875</v>
       </c>
       <c r="C200">
-        <v>7.251279830932617</v>
+        <v>7.251279354095459</v>
       </c>
       <c r="D200">
-        <v>91.10934448242188</v>
+        <v>90.93814849853516</v>
       </c>
       <c r="E200">
-        <v>39.01895141601562</v>
+        <v>39.01894760131836</v>
       </c>
       <c r="F200">
-        <v>76.55867767333984</v>
+        <v>76.44913482666016</v>
       </c>
       <c r="G200">
-        <v>62.82778549194336</v>
+        <v>62.82778167724609</v>
       </c>
       <c r="H200">
         <v>1.879999995231628</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
-      <c r="A201" s="1">
+    <row r="201">
+      <c r="A201" s="2">
         <v>43282</v>
       </c>
       <c r="B201">
@@ -5601,49 +5588,49 @@
         <v>6.669045925140381</v>
       </c>
       <c r="D201">
-        <v>98.01116180419922</v>
+        <v>97.82698822021484</v>
       </c>
       <c r="E201">
         <v>42.3903923034668</v>
       </c>
       <c r="F201">
-        <v>88.65303039550781</v>
+        <v>88.52618408203125</v>
       </c>
       <c r="G201">
-        <v>65.68828582763672</v>
+        <v>65.68830871582031</v>
       </c>
       <c r="H201">
         <v>1.985000014305115</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
-      <c r="A202" s="1">
+    <row r="202">
+      <c r="A202" s="2">
         <v>43313</v>
       </c>
       <c r="B202">
         <v>2901.52001953125</v>
       </c>
       <c r="C202">
-        <v>6.297065258026123</v>
+        <v>6.297066688537598</v>
       </c>
       <c r="D202">
-        <v>104.1851577758789</v>
+        <v>103.9893798828125</v>
       </c>
       <c r="E202">
-        <v>43.19055557250977</v>
+        <v>43.19055938720703</v>
       </c>
       <c r="F202">
-        <v>95.31377410888672</v>
+        <v>95.17739868164062</v>
       </c>
       <c r="G202">
-        <v>67.3695068359375</v>
+        <v>67.36949157714844</v>
       </c>
       <c r="H202">
         <v>2.055000066757202</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
-      <c r="A203" s="1">
+    <row r="203">
+      <c r="A203" s="2">
         <v>43344</v>
       </c>
       <c r="B203">
@@ -5653,205 +5640,205 @@
         <v>6.144289970397949</v>
       </c>
       <c r="D203">
-        <v>106.0772399902344</v>
+        <v>105.8778991699219</v>
       </c>
       <c r="E203">
-        <v>45.83995056152344</v>
+        <v>45.83993530273438</v>
       </c>
       <c r="F203">
-        <v>96.81136322021484</v>
+        <v>96.67284393310547</v>
       </c>
       <c r="G203">
-        <v>67.59691619873047</v>
+        <v>67.59690093994141</v>
       </c>
       <c r="H203">
         <v>2.150000095367432</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
-      <c r="A204" s="1">
+    <row r="204">
+      <c r="A204" s="2">
         <v>43374</v>
       </c>
       <c r="B204">
         <v>2711.739990234375</v>
       </c>
       <c r="C204">
-        <v>6.45751953125</v>
+        <v>6.457520484924316</v>
       </c>
       <c r="D204">
-        <v>99.06539916992188</v>
+        <v>98.87923431396484</v>
       </c>
       <c r="E204">
-        <v>43.59652328491211</v>
+        <v>43.59653091430664</v>
       </c>
       <c r="F204">
-        <v>97.83082580566406</v>
+        <v>97.69083404541016</v>
       </c>
       <c r="G204">
-        <v>72.65962982177734</v>
+        <v>72.65962219238281</v>
       </c>
       <c r="H204">
         <v>2.278000116348267</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
-      <c r="A205" s="1">
+    <row r="205">
+      <c r="A205" s="2">
         <v>43405</v>
       </c>
       <c r="B205">
         <v>2760.169921875</v>
       </c>
       <c r="C205">
-        <v>6.362853527069092</v>
+        <v>6.362854957580566</v>
       </c>
       <c r="D205">
-        <v>103.2938995361328</v>
+        <v>103.0998001098633</v>
       </c>
       <c r="E205">
         <v>43.52511596679688</v>
       </c>
       <c r="F205">
-        <v>107.5717697143555</v>
+        <v>107.4178695678711</v>
       </c>
       <c r="G205">
-        <v>77.43643951416016</v>
+        <v>77.43643188476562</v>
       </c>
       <c r="H205">
         <v>2.308000087738037</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
-      <c r="A206" s="1">
+    <row r="206">
+      <c r="A206" s="2">
         <v>43435</v>
       </c>
       <c r="B206">
         <v>2506.85009765625</v>
       </c>
       <c r="C206">
-        <v>5.172779560089111</v>
+        <v>5.172778129577637</v>
       </c>
       <c r="D206">
-        <v>94.61231994628906</v>
+        <v>94.43454742431641</v>
       </c>
       <c r="E206">
         <v>40.30268859863281</v>
       </c>
       <c r="F206">
-        <v>104.924186706543</v>
+        <v>104.7740478515625</v>
       </c>
       <c r="G206">
-        <v>75.3143310546875</v>
+        <v>75.31433868408203</v>
       </c>
       <c r="H206">
         <v>2.299999952316284</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
-      <c r="A207" s="1">
+    <row r="207">
+      <c r="A207" s="2">
         <v>43466</v>
       </c>
       <c r="B207">
         <v>2704.10009765625</v>
       </c>
       <c r="C207">
-        <v>6.054051876068115</v>
+        <v>6.054049968719482</v>
       </c>
       <c r="D207">
-        <v>97.27641296386719</v>
+        <v>97.09362030029297</v>
       </c>
       <c r="E207">
         <v>45.01481246948242</v>
       </c>
       <c r="F207">
-        <v>108.6779632568359</v>
+        <v>108.5224456787109</v>
       </c>
       <c r="G207">
-        <v>79.66754150390625</v>
+        <v>79.66753387451172</v>
       </c>
       <c r="H207">
         <v>2.339999914169312</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
-      <c r="A208" s="1">
+    <row r="208">
+      <c r="A208" s="2">
         <v>43497</v>
       </c>
       <c r="B208">
         <v>2784.489990234375</v>
       </c>
       <c r="C208">
-        <v>6.033412456512451</v>
+        <v>6.033412933349609</v>
       </c>
       <c r="D208">
-        <v>104.8014678955078</v>
+        <v>104.6045303344727</v>
       </c>
       <c r="E208">
-        <v>46.71754837036133</v>
+        <v>46.71755599975586</v>
       </c>
       <c r="F208">
-        <v>115.1287078857422</v>
+        <v>114.9639739990234</v>
       </c>
       <c r="G208">
-        <v>81.38524627685547</v>
+        <v>81.38523864746094</v>
       </c>
       <c r="H208">
         <v>2.382999897003174</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
-      <c r="A209" s="1">
+    <row r="209">
+      <c r="A209" s="2">
         <v>43525</v>
       </c>
       <c r="B209">
         <v>2834.39990234375</v>
       </c>
       <c r="C209">
-        <v>6.040290832519531</v>
+        <v>6.040289402008057</v>
       </c>
       <c r="D209">
-        <v>110.3301391601562</v>
+        <v>110.1228256225586</v>
       </c>
       <c r="E209">
-        <v>48.13350296020508</v>
+        <v>48.13349914550781</v>
       </c>
       <c r="F209">
-        <v>118.2920532226562</v>
+        <v>118.1227569580078</v>
       </c>
       <c r="G209">
-        <v>85.92730712890625</v>
+        <v>85.92732238769531</v>
       </c>
       <c r="H209">
         <v>2.328000068664551</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
-      <c r="A210" s="1">
+    <row r="210">
+      <c r="A210" s="2">
         <v>43556</v>
       </c>
       <c r="B210">
         <v>2945.830078125</v>
       </c>
       <c r="C210">
-        <v>7.304519176483154</v>
+        <v>7.304518699645996</v>
       </c>
       <c r="D210">
-        <v>122.1732482910156</v>
+        <v>121.9436950683594</v>
       </c>
       <c r="E210">
         <v>49.80736541748047</v>
       </c>
       <c r="F210">
-        <v>106.6962127685547</v>
+        <v>106.5435333251953</v>
       </c>
       <c r="G210">
-        <v>88.55481719970703</v>
+        <v>88.55483245849609</v>
       </c>
       <c r="H210">
         <v>2.368000030517578</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
-      <c r="A211" s="1">
+    <row r="211">
+      <c r="A211" s="2">
         <v>43586</v>
       </c>
       <c r="B211">
@@ -5861,65 +5848,65 @@
         <v>6.654451847076416</v>
       </c>
       <c r="D211">
-        <v>116.128044128418</v>
+        <v>115.9098434448242</v>
       </c>
       <c r="E211">
         <v>45.54948425292969</v>
       </c>
       <c r="F211">
-        <v>106.2863616943359</v>
+        <v>106.1342544555664</v>
       </c>
       <c r="G211">
-        <v>85.58580017089844</v>
+        <v>85.5858154296875</v>
       </c>
       <c r="H211">
         <v>2.292999982833862</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
-      <c r="A212" s="1">
+    <row r="212">
+      <c r="A212" s="2">
         <v>43617</v>
       </c>
       <c r="B212">
         <v>2941.760009765625</v>
       </c>
       <c r="C212">
-        <v>7.150737762451172</v>
+        <v>7.150740146636963</v>
       </c>
       <c r="D212">
-        <v>125.7803573608398</v>
+        <v>125.5439834594727</v>
       </c>
       <c r="E212">
         <v>51.28367614746094</v>
       </c>
       <c r="F212">
-        <v>101.5651397705078</v>
+        <v>101.4198303222656</v>
       </c>
       <c r="G212">
-        <v>91.19116973876953</v>
+        <v>91.19118499755859</v>
       </c>
       <c r="H212">
         <v>2.035000085830688</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
-      <c r="A213" s="1">
+    <row r="213">
+      <c r="A213" s="2">
         <v>43647</v>
       </c>
       <c r="B213">
         <v>2980.3798828125</v>
       </c>
       <c r="C213">
-        <v>6.760865688323975</v>
+        <v>6.760866165161133</v>
       </c>
       <c r="D213">
-        <v>127.9493026733398</v>
+        <v>127.7088470458984</v>
       </c>
       <c r="E213">
         <v>50.88570404052734</v>
       </c>
       <c r="F213">
-        <v>99.87836456298828</v>
+        <v>99.73543548583984</v>
       </c>
       <c r="G213">
         <v>98.80452728271484</v>
@@ -5928,164 +5915,164 @@
         <v>2.029999971389771</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
-      <c r="A214" s="1">
+    <row r="214">
+      <c r="A214" s="2">
         <v>43678</v>
       </c>
       <c r="B214">
         <v>2926.4599609375</v>
       </c>
       <c r="C214">
-        <v>6.505472660064697</v>
+        <v>6.505471229553223</v>
       </c>
       <c r="D214">
-        <v>129.8732452392578</v>
+        <v>129.6291961669922</v>
       </c>
       <c r="E214">
-        <v>47.0534553527832</v>
+        <v>47.05346298217773</v>
       </c>
       <c r="F214">
-        <v>104.1442184448242</v>
+        <v>103.9952011108398</v>
       </c>
       <c r="G214">
-        <v>100.6376266479492</v>
+        <v>100.6376342773438</v>
       </c>
       <c r="H214">
         <v>1.932999968528748</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
-      <c r="A215" s="1">
+    <row r="215">
+      <c r="A215" s="2">
         <v>43709</v>
       </c>
       <c r="B215">
         <v>2976.739990234375</v>
       </c>
       <c r="C215">
-        <v>6.498378276824951</v>
+        <v>6.498377799987793</v>
       </c>
       <c r="D215">
-        <v>130.9754486083984</v>
+        <v>130.7293548583984</v>
       </c>
       <c r="E215">
-        <v>49.73783874511719</v>
+        <v>49.73784255981445</v>
       </c>
       <c r="F215">
-        <v>103.0932922363281</v>
+        <v>102.9457855224609</v>
       </c>
       <c r="G215">
-        <v>104.1113586425781</v>
+        <v>104.1113739013672</v>
       </c>
       <c r="H215">
         <v>1.769999980926514</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
-      <c r="A216" s="1">
+    <row r="216">
+      <c r="A216" s="2">
         <v>43739</v>
       </c>
       <c r="B216">
         <v>3037.56005859375</v>
       </c>
       <c r="C216">
-        <v>6.194013118743896</v>
+        <v>6.194014549255371</v>
       </c>
       <c r="D216">
-        <v>135.0640106201172</v>
+        <v>134.8102722167969</v>
       </c>
       <c r="E216">
-        <v>49.46942520141602</v>
+        <v>49.46942901611328</v>
       </c>
       <c r="F216">
-        <v>105.0476531982422</v>
+        <v>104.897346496582</v>
       </c>
       <c r="G216">
-        <v>104.8859100341797</v>
+        <v>104.8859329223633</v>
       </c>
       <c r="H216">
         <v>1.498000025749207</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
-      <c r="A217" s="1">
+    <row r="217">
+      <c r="A217" s="2">
         <v>43770</v>
       </c>
       <c r="B217">
         <v>3140.97998046875</v>
       </c>
       <c r="C217">
-        <v>6.532917976379395</v>
+        <v>6.532918930053711</v>
       </c>
       <c r="D217">
-        <v>143.0952606201172</v>
+        <v>142.8263702392578</v>
       </c>
       <c r="E217">
-        <v>50.96739196777344</v>
+        <v>50.96740341186523</v>
       </c>
       <c r="F217">
-        <v>108.8042526245117</v>
+        <v>108.6485595703125</v>
       </c>
       <c r="G217">
-        <v>102.8220520019531</v>
+        <v>102.8220748901367</v>
       </c>
       <c r="H217">
         <v>1.539999961853027</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
-      <c r="A218" s="1">
+    <row r="218">
+      <c r="A218" s="2">
         <v>43800</v>
       </c>
       <c r="B218">
         <v>3230.780029296875</v>
       </c>
       <c r="C218">
-        <v>6.705975532531738</v>
+        <v>6.705974102020264</v>
       </c>
       <c r="D218">
-        <v>149.0693969726562</v>
+        <v>148.7892456054688</v>
       </c>
       <c r="E218">
-        <v>48.09854888916016</v>
+        <v>48.09855651855469</v>
       </c>
       <c r="F218">
-        <v>121.8589172363281</v>
+        <v>121.6845321655273</v>
       </c>
       <c r="G218">
-        <v>105.2144775390625</v>
+        <v>105.2144546508789</v>
       </c>
       <c r="H218">
         <v>1.504999995231628</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
-      <c r="A219" s="1">
+    <row r="219">
+      <c r="A219" s="2">
         <v>43831</v>
       </c>
       <c r="B219">
         <v>3225.52001953125</v>
       </c>
       <c r="C219">
-        <v>6.468020915985107</v>
+        <v>6.468020439147949</v>
       </c>
       <c r="D219">
-        <v>160.9135894775391</v>
+        <v>160.6112365722656</v>
       </c>
       <c r="E219">
-        <v>47.8293342590332</v>
+        <v>47.82933807373047</v>
       </c>
       <c r="F219">
-        <v>129.4710388183594</v>
+        <v>129.2857513427734</v>
       </c>
       <c r="G219">
-        <v>105.602294921875</v>
+        <v>105.6023101806641</v>
       </c>
       <c r="H219">
         <v>1.509999990463257</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
-      <c r="A220" s="1">
+    <row r="220">
+      <c r="A220" s="2">
         <v>43862</v>
       </c>
       <c r="B220">
@@ -6095,91 +6082,91 @@
         <v>5.104016780853271</v>
       </c>
       <c r="D220">
-        <v>153.5617828369141</v>
+        <v>153.2732391357422</v>
       </c>
       <c r="E220">
-        <v>45.10274124145508</v>
+        <v>45.10274505615234</v>
       </c>
       <c r="F220">
-        <v>117.5509948730469</v>
+        <v>117.3828201293945</v>
       </c>
       <c r="G220">
-        <v>95.95046997070312</v>
+        <v>95.95045471191406</v>
       </c>
       <c r="H220">
         <v>1.230000019073486</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
-      <c r="A221" s="1">
+    <row r="221">
+      <c r="A221" s="2">
         <v>43891</v>
       </c>
       <c r="B221">
         <v>2584.590087890625</v>
       </c>
       <c r="C221">
-        <v>3.542011499404907</v>
+        <v>3.542011737823486</v>
       </c>
       <c r="D221">
-        <v>149.4860076904297</v>
+        <v>149.2051696777344</v>
       </c>
       <c r="E221">
-        <v>44.07228851318359</v>
+        <v>44.07229232788086</v>
       </c>
       <c r="F221">
-        <v>129.2846984863281</v>
+        <v>129.0996704101562</v>
       </c>
       <c r="G221">
-        <v>93.21339416503906</v>
+        <v>93.21337890625</v>
       </c>
       <c r="H221">
         <v>0.02999999932944775</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
-      <c r="A222" s="1">
+    <row r="222">
+      <c r="A222" s="2">
         <v>43922</v>
       </c>
       <c r="B222">
         <v>2912.429931640625</v>
       </c>
       <c r="C222">
-        <v>3.732678890228271</v>
+        <v>3.732678651809692</v>
       </c>
       <c r="D222">
-        <v>169.8648529052734</v>
+        <v>169.5457000732422</v>
       </c>
       <c r="E222">
-        <v>48.53298950195312</v>
+        <v>48.53299713134766</v>
       </c>
       <c r="F222">
-        <v>144.1218414306641</v>
+        <v>143.9156036376953</v>
       </c>
       <c r="G222">
-        <v>100.5485000610352</v>
+        <v>100.5484924316406</v>
       </c>
       <c r="H222">
         <v>0.09000000357627869</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
-      <c r="A223" s="1">
+    <row r="223">
+      <c r="A223" s="2">
         <v>43952</v>
       </c>
       <c r="B223">
         <v>3044.31005859375</v>
       </c>
       <c r="C223">
-        <v>4.1873459815979</v>
+        <v>4.187346935272217</v>
       </c>
       <c r="D223">
-        <v>174.1779174804688</v>
+        <v>173.8506469726562</v>
       </c>
       <c r="E223">
-        <v>49.26598358154297</v>
+        <v>49.26598739624023</v>
       </c>
       <c r="F223">
-        <v>143.2178192138672</v>
+        <v>143.0129089355469</v>
       </c>
       <c r="G223">
         <v>98.88504028320312</v>
@@ -6188,8 +6175,8 @@
         <v>0.1280000060796738</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
-      <c r="A224" s="1">
+    <row r="224">
+      <c r="A224" s="2">
         <v>43983</v>
       </c>
       <c r="B224">
@@ -6199,23 +6186,23 @@
         <v>4.458681106567383</v>
       </c>
       <c r="D224">
-        <v>193.4349212646484</v>
+        <v>193.0714263916016</v>
       </c>
       <c r="E224">
-        <v>50.64032363891602</v>
+        <v>50.64032745361328</v>
       </c>
       <c r="F224">
-        <v>153.7333221435547</v>
+        <v>153.5133056640625</v>
       </c>
       <c r="G224">
-        <v>101.9986724853516</v>
+        <v>101.9986572265625</v>
       </c>
       <c r="H224">
         <v>0.135000005364418</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
-      <c r="A225" s="1">
+    <row r="225">
+      <c r="A225" s="2">
         <v>44013</v>
       </c>
       <c r="B225">
@@ -6225,39 +6212,39 @@
         <v>4.847349166870117</v>
       </c>
       <c r="D225">
-        <v>194.8606567382812</v>
+        <v>194.4945068359375</v>
       </c>
       <c r="E225">
-        <v>51.02004241943359</v>
+        <v>51.02005386352539</v>
       </c>
       <c r="F225">
-        <v>140.7271270751953</v>
+        <v>140.5257415771484</v>
       </c>
       <c r="G225">
-        <v>112.5571594238281</v>
+        <v>112.5571746826172</v>
       </c>
       <c r="H225">
         <v>0.08299999684095383</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
-      <c r="A226" s="1">
+    <row r="226">
+      <c r="A226" s="2">
         <v>44044</v>
       </c>
       <c r="B226">
         <v>3500.31005859375</v>
       </c>
       <c r="C226">
-        <v>5.001349925994873</v>
+        <v>5.001348972320557</v>
       </c>
       <c r="D226">
-        <v>214.8829803466797</v>
+        <v>214.479248046875</v>
       </c>
       <c r="E226">
-        <v>52.64864349365234</v>
+        <v>52.64864730834961</v>
       </c>
       <c r="F226">
-        <v>139.6253509521484</v>
+        <v>139.4255065917969</v>
       </c>
       <c r="G226">
         <v>118.7464370727539</v>
@@ -6266,180 +6253,180 @@
         <v>0.0949999988079071</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
-      <c r="A227" s="1">
+    <row r="227">
+      <c r="A227" s="2">
         <v>44075</v>
       </c>
       <c r="B227">
         <v>3363</v>
       </c>
       <c r="C227">
-        <v>4.884015560150146</v>
+        <v>4.884016036987305</v>
       </c>
       <c r="D227">
-        <v>200.4005889892578</v>
+        <v>200.0240020751953</v>
       </c>
       <c r="E227">
         <v>54.93051528930664</v>
       </c>
       <c r="F227">
-        <v>139.2771759033203</v>
+        <v>139.077880859375</v>
       </c>
       <c r="G227">
-        <v>119.3130264282227</v>
+        <v>119.3129959106445</v>
       </c>
       <c r="H227">
         <v>0.08500000089406967</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
-      <c r="A228" s="1">
+    <row r="228">
+      <c r="A228" s="2">
         <v>44105</v>
       </c>
       <c r="B228">
         <v>3269.9599609375</v>
       </c>
       <c r="C228">
-        <v>5.668685436248779</v>
+        <v>5.668684482574463</v>
       </c>
       <c r="D228">
-        <v>192.9116058349609</v>
+        <v>192.5491180419922</v>
       </c>
       <c r="E228">
-        <v>51.83637237548828</v>
+        <v>51.83636856079102</v>
       </c>
       <c r="F228">
-        <v>122.7543640136719</v>
+        <v>122.5787048339844</v>
       </c>
       <c r="G228">
-        <v>118.3440856933594</v>
+        <v>118.3440475463867</v>
       </c>
       <c r="H228">
         <v>0.08299999684095383</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
-      <c r="A229" s="1">
+    <row r="229">
+      <c r="A229" s="2">
         <v>44136</v>
       </c>
       <c r="B229">
         <v>3621.6298828125</v>
       </c>
       <c r="C229">
-        <v>6.658689022064209</v>
+        <v>6.658688545227051</v>
       </c>
       <c r="D229">
-        <v>204.4980163574219</v>
+        <v>204.1137390136719</v>
       </c>
       <c r="E229">
         <v>53.32374572753906</v>
       </c>
       <c r="F229">
-        <v>137.7513275146484</v>
+        <v>137.5542144775391</v>
       </c>
       <c r="G229">
-        <v>119.8719024658203</v>
+        <v>119.8719100952148</v>
       </c>
       <c r="H229">
         <v>0.07500000298023224</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
-      <c r="A230" s="1">
+    <row r="230">
+      <c r="A230" s="2">
         <v>44166</v>
       </c>
       <c r="B230">
         <v>3756.070068359375</v>
       </c>
       <c r="C230">
-        <v>6.44602108001709</v>
+        <v>6.446021556854248</v>
       </c>
       <c r="D230">
-        <v>212.4746704101562</v>
+        <v>212.0753936767578</v>
       </c>
       <c r="E230">
-        <v>59.76286315917969</v>
+        <v>59.76286697387695</v>
       </c>
       <c r="F230">
-        <v>159.6837615966797</v>
+        <v>159.4552307128906</v>
       </c>
       <c r="G230">
-        <v>120.1049728393555</v>
+        <v>120.10498046875</v>
       </c>
       <c r="H230">
         <v>0.06499999761581421</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
-      <c r="A231" s="1">
+    <row r="231">
+      <c r="A231" s="2">
         <v>44197</v>
       </c>
       <c r="B231">
         <v>3714.239990234375</v>
       </c>
       <c r="C231">
-        <v>7.722024917602539</v>
+        <v>7.722023963928223</v>
       </c>
       <c r="D231">
-        <v>221.5880432128906</v>
+        <v>221.1717071533203</v>
       </c>
       <c r="E231">
-        <v>56.04095840454102</v>
+        <v>56.04096221923828</v>
       </c>
       <c r="F231">
-        <v>196.6917114257812</v>
+        <v>196.4102325439453</v>
       </c>
       <c r="G231">
-        <v>111.337776184082</v>
+        <v>111.3377838134766</v>
       </c>
       <c r="H231">
         <v>0.04800000041723251</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
-      <c r="A232" s="1">
+    <row r="232">
+      <c r="A232" s="2">
         <v>44228</v>
       </c>
       <c r="B232">
         <v>3811.14990234375</v>
       </c>
       <c r="C232">
-        <v>8.58002758026123</v>
+        <v>8.580028533935547</v>
       </c>
       <c r="D232">
-        <v>222.5005798339844</v>
+        <v>222.0824432373047</v>
       </c>
       <c r="E232">
-        <v>59.82463073730469</v>
+        <v>59.82463836669922</v>
       </c>
       <c r="F232">
-        <v>194.5879821777344</v>
+        <v>194.3095092773438</v>
       </c>
       <c r="G232">
-        <v>107.2736587524414</v>
+        <v>107.273681640625</v>
       </c>
       <c r="H232">
         <v>0.03500000014901161</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
-      <c r="A233" s="1">
+    <row r="233">
+      <c r="A233" s="2">
         <v>44256</v>
       </c>
       <c r="B233">
         <v>3972.889892578125</v>
       </c>
       <c r="C233">
-        <v>8.983362197875977</v>
+        <v>8.983364105224609</v>
       </c>
       <c r="D233">
-        <v>225.7464447021484</v>
+        <v>225.3222503662109</v>
       </c>
       <c r="E233">
-        <v>65.07353973388672</v>
+        <v>65.07356262207031</v>
       </c>
       <c r="F233">
-        <v>177.4265747070312</v>
+        <v>177.1726684570312</v>
       </c>
       <c r="G233">
         <v>117.6076354980469</v>
@@ -6448,8 +6435,8 @@
         <v>0.0130000002682209</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
-      <c r="A234" s="1">
+    <row r="234">
+      <c r="A234" s="2">
         <v>44287</v>
       </c>
       <c r="B234">
@@ -6459,49 +6446,49 @@
         <v>8.462693214416504</v>
       </c>
       <c r="D234">
-        <v>241.4587860107422</v>
+        <v>241.0050659179688</v>
       </c>
       <c r="E234">
-        <v>70.5894775390625</v>
+        <v>70.58945465087891</v>
       </c>
       <c r="F234">
-        <v>173.5801696777344</v>
+        <v>173.331787109375</v>
       </c>
       <c r="G234">
-        <v>116.6034622192383</v>
+        <v>116.6034393310547</v>
       </c>
       <c r="H234">
         <v>0.003000000026077032</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
-      <c r="A235" s="1">
+    <row r="235">
+      <c r="A235" s="2">
         <v>44317</v>
       </c>
       <c r="B235">
         <v>4204.10986328125</v>
       </c>
       <c r="C235">
-        <v>10.65536880493164</v>
+        <v>10.65537071228027</v>
       </c>
       <c r="D235">
-        <v>239.6170959472656</v>
+        <v>239.1668701171875</v>
       </c>
       <c r="E235">
-        <v>73.33704376220703</v>
+        <v>73.3370361328125</v>
       </c>
       <c r="F235">
-        <v>190.5351867675781</v>
+        <v>190.2625274658203</v>
       </c>
       <c r="G235">
-        <v>117.8531875610352</v>
+        <v>117.8532180786133</v>
       </c>
       <c r="H235">
         <v>0.00800000037997961</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
-      <c r="A236" s="1">
+    <row r="236">
+      <c r="A236" s="2">
         <v>44348</v>
       </c>
       <c r="B236">
@@ -6511,13 +6498,13 @@
         <v>10.89736938476562</v>
       </c>
       <c r="D236">
-        <v>259.9817810058594</v>
+        <v>259.4933776855469</v>
       </c>
       <c r="E236">
-        <v>72.49878692626953</v>
+        <v>72.498779296875</v>
       </c>
       <c r="F236">
-        <v>218.9428100585938</v>
+        <v>218.6295166015625</v>
       </c>
       <c r="G236">
         <v>117.9231109619141</v>
@@ -6526,50 +6513,50 @@
         <v>0.03999999910593033</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
-      <c r="A237" s="1">
+    <row r="237">
+      <c r="A237" s="2">
         <v>44378</v>
       </c>
       <c r="B237">
         <v>4395.259765625</v>
       </c>
       <c r="C237">
-        <v>10.23003196716309</v>
+        <v>10.2300329208374</v>
       </c>
       <c r="D237">
-        <v>273.4272155761719</v>
+        <v>272.9134521484375</v>
       </c>
       <c r="E237">
         <v>81.46004486083984</v>
       </c>
       <c r="F237">
-        <v>232.2785491943359</v>
+        <v>231.9461822509766</v>
       </c>
       <c r="G237">
-        <v>125.0847778320312</v>
+        <v>125.0848007202148</v>
       </c>
       <c r="H237">
         <v>0.03999999910593033</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
-      <c r="A238" s="1">
+    <row r="238">
+      <c r="A238" s="2">
         <v>44409</v>
       </c>
       <c r="B238">
         <v>4522.68017578125</v>
       </c>
       <c r="C238">
-        <v>9.555363655090332</v>
+        <v>9.555364608764648</v>
       </c>
       <c r="D238">
-        <v>290.2678527832031</v>
+        <v>289.7224426269531</v>
       </c>
       <c r="E238">
-        <v>83.3203125</v>
+        <v>83.32032775878906</v>
       </c>
       <c r="F238">
-        <v>247.1825408935547</v>
+        <v>246.8288421630859</v>
       </c>
       <c r="G238">
         <v>125.2255020141602</v>
@@ -6578,8 +6565,8 @@
         <v>0.03999999910593033</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
-      <c r="A239" s="1">
+    <row r="239">
+      <c r="A239" s="2">
         <v>44440</v>
       </c>
       <c r="B239">
@@ -6589,91 +6576,91 @@
         <v>10.38403415679932</v>
       </c>
       <c r="D239">
-        <v>271.0756530761719</v>
+        <v>270.5663452148438</v>
       </c>
       <c r="E239">
-        <v>81.45069122314453</v>
+        <v>81.45067596435547</v>
       </c>
       <c r="F239">
-        <v>221.1139373779297</v>
+        <v>220.7975616455078</v>
       </c>
       <c r="G239">
-        <v>122.9477157592773</v>
+        <v>122.9477233886719</v>
       </c>
       <c r="H239">
         <v>0.02800000086426735</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
-      <c r="A240" s="1">
+    <row r="240">
+      <c r="A240" s="2">
         <v>44470</v>
       </c>
       <c r="B240">
         <v>4605.3798828125</v>
       </c>
       <c r="C240">
-        <v>12.5253734588623</v>
+        <v>12.52537441253662</v>
       </c>
       <c r="D240">
-        <v>318.8639526367188</v>
+        <v>318.2647705078125</v>
       </c>
       <c r="E240">
-        <v>89.99843597412109</v>
+        <v>89.99842834472656</v>
       </c>
       <c r="F240">
-        <v>243.8043212890625</v>
+        <v>243.4554290771484</v>
       </c>
       <c r="G240">
-        <v>126.5327758789062</v>
+        <v>126.5327529907227</v>
       </c>
       <c r="H240">
         <v>0.04800000041723251</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
-      <c r="A241" s="1">
+    <row r="241">
+      <c r="A241" s="2">
         <v>44501</v>
       </c>
       <c r="B241">
         <v>4567</v>
       </c>
       <c r="C241">
-        <v>14.14357089996338</v>
+        <v>14.14357376098633</v>
       </c>
       <c r="D241">
-        <v>318.4550476074219</v>
+        <v>317.856689453125</v>
       </c>
       <c r="E241">
-        <v>85.12046051025391</v>
+        <v>85.12045288085938</v>
       </c>
       <c r="F241">
-        <v>238.1440124511719</v>
+        <v>237.8032836914062</v>
       </c>
       <c r="G241">
-        <v>127.9397583007812</v>
+        <v>127.9397659301758</v>
       </c>
       <c r="H241">
         <v>0.04800000041723251</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
-      <c r="A242" s="1">
+    <row r="242">
+      <c r="A242" s="2">
         <v>44531</v>
       </c>
       <c r="B242">
         <v>4766.18017578125</v>
       </c>
       <c r="C242">
-        <v>15.30807685852051</v>
+        <v>15.30808067321777</v>
       </c>
       <c r="D242">
-        <v>323.9747924804688</v>
+        <v>323.3659973144531</v>
       </c>
       <c r="E242">
-        <v>81.80908203125</v>
+        <v>81.80906677246094</v>
       </c>
       <c r="F242">
-        <v>265.1997680664062</v>
+        <v>264.8202819824219</v>
       </c>
       <c r="G242">
         <v>144.7529754638672</v>
@@ -6682,34 +6669,34 @@
         <v>0.03299999982118607</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
-      <c r="A243" s="1">
+    <row r="243">
+      <c r="A243" s="2">
         <v>44562</v>
       </c>
       <c r="B243">
         <v>4515.5498046875</v>
       </c>
       <c r="C243">
-        <v>15.03859519958496</v>
+        <v>15.03859710693359</v>
       </c>
       <c r="D243">
-        <v>299.5648803710938</v>
+        <v>299.0020141601562</v>
       </c>
       <c r="E243">
-        <v>76.41657257080078</v>
+        <v>76.41658782958984</v>
       </c>
       <c r="F243">
-        <v>235.5997772216797</v>
+        <v>235.2626342773438</v>
       </c>
       <c r="G243">
-        <v>142.7498016357422</v>
+        <v>142.7498321533203</v>
       </c>
       <c r="H243">
         <v>0.1729999929666519</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
-      <c r="A244" s="1">
+    <row r="244">
+      <c r="A244" s="2">
         <v>44593</v>
       </c>
       <c r="B244">
@@ -6719,13 +6706,13 @@
         <v>13.00875568389893</v>
       </c>
       <c r="D244">
-        <v>288.4175109863281</v>
+        <v>287.8756408691406</v>
       </c>
       <c r="E244">
-        <v>71.52991485595703</v>
+        <v>71.5299072265625</v>
       </c>
       <c r="F244">
-        <v>240.9796142578125</v>
+        <v>240.6348114013672</v>
       </c>
       <c r="G244">
         <v>138.6929016113281</v>
@@ -6734,34 +6721,34 @@
         <v>0.2879999876022339</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
-      <c r="A245" s="1">
+    <row r="245">
+      <c r="A245" s="2">
         <v>44621</v>
       </c>
       <c r="B245">
         <v>4530.41015625</v>
       </c>
       <c r="C245">
-        <v>12.52722358703613</v>
+        <v>12.52722644805908</v>
       </c>
       <c r="D245">
-        <v>297.6069946289062</v>
+        <v>297.0478210449219</v>
       </c>
       <c r="E245">
-        <v>77.89482879638672</v>
+        <v>77.89483642578125</v>
       </c>
       <c r="F245">
-        <v>276.0925903320312</v>
+        <v>275.6975402832031</v>
       </c>
       <c r="G245">
-        <v>135.9437255859375</v>
+        <v>135.9437866210938</v>
       </c>
       <c r="H245">
         <v>0.4930000007152557</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
-      <c r="A246" s="1">
+    <row r="246">
+      <c r="A246" s="2">
         <v>44652</v>
       </c>
       <c r="B246">
@@ -6771,13 +6758,13 @@
         <v>10.55977058410645</v>
       </c>
       <c r="D246">
-        <v>267.8858642578125</v>
+        <v>267.3825378417969</v>
       </c>
       <c r="E246">
-        <v>69.38046264648438</v>
+        <v>69.38048553466797</v>
       </c>
       <c r="F246">
-        <v>281.6459350585938</v>
+        <v>281.2428283691406</v>
       </c>
       <c r="G246">
         <v>143.6401824951172</v>
@@ -6786,24 +6773,24 @@
         <v>0.8080000281333923</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
-      <c r="A247" s="1">
+    <row r="247">
+      <c r="A247" s="2">
         <v>44682</v>
       </c>
       <c r="B247">
         <v>4132.14990234375</v>
       </c>
       <c r="C247">
-        <v>10.20181369781494</v>
+        <v>10.20181274414062</v>
       </c>
       <c r="D247">
-        <v>263.0432739257812</v>
+        <v>262.549072265625</v>
       </c>
       <c r="E247">
-        <v>67.98150634765625</v>
+        <v>67.98152160644531</v>
       </c>
       <c r="F247">
-        <v>303.2093811035156</v>
+        <v>302.7755432128906</v>
       </c>
       <c r="G247">
         <v>132.3046569824219</v>
@@ -6812,8 +6799,8 @@
         <v>1.029999971389771</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
-      <c r="A248" s="1">
+    <row r="248">
+      <c r="A248" s="2">
         <v>44713</v>
       </c>
       <c r="B248">
@@ -6823,101 +6810,101 @@
         <v>8.300159454345703</v>
       </c>
       <c r="D248">
-        <v>248.4915161132812</v>
+        <v>248.024658203125</v>
       </c>
       <c r="E248">
         <v>66.04378509521484</v>
       </c>
       <c r="F248">
-        <v>313.647216796875</v>
+        <v>313.1984558105469</v>
       </c>
       <c r="G248">
-        <v>128.6454010009766</v>
+        <v>128.6454162597656</v>
       </c>
       <c r="H248">
         <v>1.600000023841858</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
-      <c r="A249" s="1">
+    <row r="249">
+      <c r="A249" s="2">
         <v>44743</v>
       </c>
       <c r="B249">
         <v>4130.2900390625</v>
       </c>
       <c r="C249">
-        <v>10.95501708984375</v>
+        <v>10.9550142288208</v>
       </c>
       <c r="D249">
-        <v>271.625244140625</v>
+        <v>271.1148376464844</v>
       </c>
       <c r="E249">
-        <v>73.90639495849609</v>
+        <v>73.90638732910156</v>
       </c>
       <c r="F249">
-        <v>318.9290161132812</v>
+        <v>318.4725952148438</v>
       </c>
       <c r="G249">
-        <v>125.0862197875977</v>
+        <v>125.0862045288086</v>
       </c>
       <c r="H249">
         <v>2.29800009727478</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
-      <c r="A250" s="1">
+    <row r="250">
+      <c r="A250" s="2">
         <v>44774</v>
       </c>
       <c r="B250">
         <v>3955</v>
       </c>
       <c r="C250">
-        <v>11.47852516174316</v>
+        <v>11.47852611541748</v>
       </c>
       <c r="D250">
-        <v>253.5178375244141</v>
+        <v>253.0415344238281</v>
       </c>
       <c r="E250">
         <v>70.40286254882812</v>
       </c>
       <c r="F250">
-        <v>292.3492431640625</v>
+        <v>291.930908203125</v>
       </c>
       <c r="G250">
-        <v>124.2127456665039</v>
+        <v>124.2127380371094</v>
       </c>
       <c r="H250">
         <v>2.859999895095825</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
-      <c r="A251" s="1">
+    <row r="251">
+      <c r="A251" s="2">
         <v>44805</v>
       </c>
       <c r="B251">
         <v>3585.6201171875</v>
       </c>
       <c r="C251">
-        <v>8.435661315917969</v>
+        <v>8.435662269592285</v>
       </c>
       <c r="D251">
-        <v>225.8167724609375</v>
+        <v>225.3924407958984</v>
       </c>
       <c r="E251">
-        <v>57.98386001586914</v>
+        <v>57.98386764526367</v>
       </c>
       <c r="F251">
-        <v>313.817138671875</v>
+        <v>313.3680419921875</v>
       </c>
       <c r="G251">
-        <v>113.6860733032227</v>
+        <v>113.6860809326172</v>
       </c>
       <c r="H251">
         <v>3.180000066757202</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
-      <c r="A252" s="1">
+    <row r="252">
+      <c r="A252" s="2">
         <v>44835</v>
       </c>
       <c r="B252">
@@ -6927,23 +6914,23 @@
         <v>10.07007312774658</v>
       </c>
       <c r="D252">
-        <v>225.0701599121094</v>
+        <v>224.6473083496094</v>
       </c>
       <c r="E252">
-        <v>74.50582122802734</v>
+        <v>74.50580596923828</v>
       </c>
       <c r="F252">
-        <v>351.4150085449219</v>
+        <v>350.9120788574219</v>
       </c>
       <c r="G252">
-        <v>122.1287689208984</v>
+        <v>122.128791809082</v>
       </c>
       <c r="H252">
         <v>3.974999904632568</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
-      <c r="A253" s="1">
+    <row r="253">
+      <c r="A253" s="2">
         <v>44866</v>
       </c>
       <c r="B253">
@@ -6953,65 +6940,65 @@
         <v>10.57869529724121</v>
       </c>
       <c r="D253">
-        <v>248.0775756835938</v>
+        <v>247.6114196777344</v>
       </c>
       <c r="E253">
-        <v>79.23934936523438</v>
+        <v>79.23937225341797</v>
       </c>
       <c r="F253">
-        <v>361.1445007324219</v>
+        <v>360.6277770996094</v>
       </c>
       <c r="G253">
-        <v>135.2693939208984</v>
+        <v>135.2694091796875</v>
       </c>
       <c r="H253">
         <v>4.252999782562256</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
-      <c r="A254" s="1">
+    <row r="254">
+      <c r="A254" s="2">
         <v>44896</v>
       </c>
       <c r="B254">
         <v>3839.5</v>
       </c>
       <c r="C254">
-        <v>8.851095199584961</v>
+        <v>8.851094245910645</v>
       </c>
       <c r="D254">
-        <v>233.1816101074219</v>
+        <v>232.7434997558594</v>
       </c>
       <c r="E254">
-        <v>78.00825500488281</v>
+        <v>78.00826263427734</v>
       </c>
       <c r="F254">
-        <v>356.0447998046875</v>
+        <v>355.535400390625</v>
       </c>
       <c r="G254">
-        <v>137.4459228515625</v>
+        <v>137.4458923339844</v>
       </c>
       <c r="H254">
         <v>4.260000228881836</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
-      <c r="A255" s="1">
+    <row r="255">
+      <c r="A255" s="2">
         <v>44927</v>
       </c>
       <c r="B255">
         <v>4076.60009765625</v>
       </c>
       <c r="C255">
-        <v>10.28188228607178</v>
+        <v>10.28188037872314</v>
       </c>
       <c r="D255">
-        <v>240.950439453125</v>
+        <v>240.4977111816406</v>
       </c>
       <c r="E255">
         <v>84.73802185058594</v>
       </c>
       <c r="F255">
-        <v>334.9356079101562</v>
+        <v>334.4562683105469</v>
       </c>
       <c r="G255">
         <v>129.9310150146484</v>
@@ -7020,34 +7007,34 @@
         <v>4.570000171661377</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
-      <c r="A256" s="1">
+    <row r="256">
+      <c r="A256" s="2">
         <v>44958</v>
       </c>
       <c r="B256">
         <v>3970.14990234375</v>
       </c>
       <c r="C256">
-        <v>9.765058517456055</v>
+        <v>9.765056610107422</v>
       </c>
       <c r="D256">
-        <v>243.1233062744141</v>
+        <v>242.6664886474609</v>
       </c>
       <c r="E256">
-        <v>83.72263336181641</v>
+        <v>83.72261810302734</v>
       </c>
       <c r="F256">
-        <v>303.8671569824219</v>
+        <v>303.4323425292969</v>
       </c>
       <c r="G256">
-        <v>125.5324554443359</v>
+        <v>125.5324478149414</v>
       </c>
       <c r="H256">
         <v>4.710000038146973</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
-      <c r="A257" s="1">
+    <row r="257">
+      <c r="A257" s="2">
         <v>44986</v>
       </c>
       <c r="B257">
@@ -7057,101 +7044,101 @@
         <v>10.19384765625</v>
       </c>
       <c r="D257">
-        <v>281.0217590332031</v>
+        <v>280.4936828613281</v>
       </c>
       <c r="E257">
-        <v>89.0103759765625</v>
+        <v>89.01036071777344</v>
       </c>
       <c r="F257">
-        <v>335.3064880371094</v>
+        <v>334.8266906738281</v>
       </c>
       <c r="G257">
-        <v>135.6892852783203</v>
+        <v>135.6893157958984</v>
       </c>
       <c r="H257">
         <v>4.585000038146973</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
-      <c r="A258" s="1">
+    <row r="258">
+      <c r="A258" s="2">
         <v>45017</v>
       </c>
       <c r="B258">
         <v>4169.47998046875</v>
       </c>
       <c r="C258">
-        <v>9.73138427734375</v>
+        <v>9.731385231018066</v>
       </c>
       <c r="D258">
-        <v>299.5031127929688</v>
+        <v>298.9404296875</v>
       </c>
       <c r="E258">
-        <v>91.11459350585938</v>
+        <v>91.11460113525391</v>
       </c>
       <c r="F258">
-        <v>386.5074768066406</v>
+        <v>385.9544372558594</v>
       </c>
       <c r="G258">
-        <v>143.6003875732422</v>
+        <v>143.6004180908203</v>
       </c>
       <c r="H258">
         <v>4.922999858856201</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
-      <c r="A259" s="1">
+    <row r="259">
+      <c r="A259" s="2">
         <v>45047</v>
       </c>
       <c r="B259">
         <v>4179.830078125</v>
       </c>
       <c r="C259">
-        <v>9.829682350158691</v>
+        <v>9.829681396484375</v>
       </c>
       <c r="D259">
-        <v>320.7994384765625</v>
+        <v>320.1966857910156</v>
       </c>
       <c r="E259">
-        <v>101.9075241088867</v>
+        <v>101.9075317382812</v>
       </c>
       <c r="F259">
-        <v>420.4044189453125</v>
+        <v>419.8027954101562</v>
       </c>
       <c r="G259">
-        <v>130.8546447753906</v>
+        <v>130.8547058105469</v>
       </c>
       <c r="H259">
         <v>5.248000144958496</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
-      <c r="A260" s="1">
+    <row r="260">
+      <c r="A260" s="2">
         <v>45078</v>
       </c>
       <c r="B260">
         <v>4450.3798828125</v>
       </c>
       <c r="C260">
-        <v>12.39358997344971</v>
+        <v>12.39358806610107</v>
       </c>
       <c r="D260">
-        <v>332.6686096191406</v>
+        <v>332.0435180664062</v>
       </c>
       <c r="E260">
         <v>114.5569763183594</v>
       </c>
       <c r="F260">
-        <v>459.0910339355469</v>
+        <v>458.4341735839844</v>
       </c>
       <c r="G260">
-        <v>139.339599609375</v>
+        <v>139.3395690917969</v>
       </c>
       <c r="H260">
         <v>5.152999877929688</v>
       </c>
     </row>
-    <row r="261" spans="1:8">
-      <c r="A261" s="1">
+    <row r="261">
+      <c r="A261" s="2">
         <v>45108</v>
       </c>
       <c r="B261">
@@ -7161,13 +7148,13 @@
         <v>10.93862915039062</v>
       </c>
       <c r="D261">
-        <v>328.1554565429688</v>
+        <v>327.5388488769531</v>
       </c>
       <c r="E261">
-        <v>113.1635284423828</v>
+        <v>113.1635360717773</v>
       </c>
       <c r="F261">
-        <v>444.9653015136719</v>
+        <v>444.3285827636719</v>
       </c>
       <c r="G261">
         <v>144.4312286376953</v>
@@ -7176,50 +7163,50 @@
         <v>5.248000144958496</v>
       </c>
     </row>
-    <row r="262" spans="1:8">
-      <c r="A262" s="1">
+    <row r="262">
+      <c r="A262" s="2">
         <v>45139</v>
       </c>
       <c r="B262">
         <v>4507.66015625</v>
       </c>
       <c r="C262">
-        <v>10.04432773590088</v>
+        <v>10.0443286895752</v>
       </c>
       <c r="D262">
-        <v>320.8619384765625</v>
+        <v>320.2590026855469</v>
       </c>
       <c r="E262">
-        <v>116.2139129638672</v>
+        <v>116.2139053344727</v>
       </c>
       <c r="F262">
-        <v>543.6770629882812</v>
+        <v>542.8992309570312</v>
       </c>
       <c r="G262">
-        <v>142.6200714111328</v>
+        <v>142.6200866699219</v>
       </c>
       <c r="H262">
         <v>5.297999858856201</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
-      <c r="A263" s="1">
+    <row r="263">
+      <c r="A263" s="2">
         <v>45170</v>
       </c>
       <c r="B263">
         <v>4288.0498046875</v>
       </c>
       <c r="C263">
-        <v>10.28446483612061</v>
+        <v>10.28446292877197</v>
       </c>
       <c r="D263">
-        <v>309.1046752929688</v>
+        <v>308.5238647460938</v>
       </c>
       <c r="E263">
-        <v>102.2458343505859</v>
+        <v>102.245849609375</v>
       </c>
       <c r="F263">
-        <v>526.9310913085938</v>
+        <v>526.1771240234375</v>
       </c>
       <c r="G263">
         <v>134.7840270996094</v>
@@ -7228,50 +7215,50 @@
         <v>5.300000190734863</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
-      <c r="A264" s="1">
+    <row r="264">
+      <c r="A264" s="2">
         <v>45200</v>
       </c>
       <c r="B264">
         <v>4193.7998046875</v>
       </c>
       <c r="C264">
-        <v>8.199440002441406</v>
+        <v>8.19943904876709</v>
       </c>
       <c r="D264">
-        <v>330.9940795898438</v>
+        <v>330.3721618652344</v>
       </c>
       <c r="E264">
         <v>100.1785125732422</v>
       </c>
       <c r="F264">
-        <v>543.412109375</v>
+        <v>542.6345825195312</v>
       </c>
       <c r="G264">
-        <v>139.5124206542969</v>
+        <v>139.5124053955078</v>
       </c>
       <c r="H264">
         <v>5.320000171661377</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
-      <c r="A265" s="1">
+    <row r="265">
+      <c r="A265" s="2">
         <v>45231</v>
       </c>
       <c r="B265">
         <v>4567.7998046875</v>
       </c>
       <c r="C265">
-        <v>8.628334045410156</v>
+        <v>8.62833309173584</v>
       </c>
       <c r="D265">
-        <v>371.6882629394531</v>
+        <v>370.9898681640625</v>
       </c>
       <c r="E265">
-        <v>112.5894088745117</v>
+        <v>112.5894012451172</v>
       </c>
       <c r="F265">
-        <v>580.8887939453125</v>
+        <v>580.0576171875</v>
       </c>
       <c r="G265">
         <v>142.7577362060547</v>
@@ -7280,8 +7267,8 @@
         <v>5.23799991607666</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
-      <c r="A266" s="1">
+    <row r="266">
+      <c r="A266" s="2">
         <v>45261</v>
       </c>
       <c r="B266">
@@ -7291,39 +7278,39 @@
         <v>10.25140190124512</v>
       </c>
       <c r="D266">
-        <v>368.8729858398438</v>
+        <v>368.1797790527344</v>
       </c>
       <c r="E266">
-        <v>102.1452560424805</v>
+        <v>102.1452484130859</v>
       </c>
       <c r="F266">
-        <v>572.9083862304688</v>
+        <v>572.0885620117188</v>
       </c>
       <c r="G266">
-        <v>136.2670745849609</v>
+        <v>136.2670288085938</v>
       </c>
       <c r="H266">
         <v>5.179999828338623</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
-      <c r="A267" s="1">
+    <row r="267">
+      <c r="A267" s="2">
         <v>45292</v>
       </c>
       <c r="B267">
         <v>4845.64990234375</v>
       </c>
       <c r="C267">
-        <v>9.856146812438965</v>
+        <v>9.856147766113281</v>
       </c>
       <c r="D267">
-        <v>390.00244140625</v>
+        <v>389.2696228027344</v>
       </c>
       <c r="E267">
-        <v>108.6392440795898</v>
+        <v>108.6392364501953</v>
       </c>
       <c r="F267">
-        <v>634.521728515625</v>
+        <v>633.6135864257812</v>
       </c>
       <c r="G267">
         <v>147.0468139648438</v>
@@ -7332,34 +7319,34 @@
         <v>5.188000202178955</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
-      <c r="A268" s="1">
+    <row r="268">
+      <c r="A268" s="2">
         <v>45323</v>
       </c>
       <c r="B268">
         <v>5096.27001953125</v>
       </c>
       <c r="C268">
-        <v>10.74392986297607</v>
+        <v>10.74392795562744</v>
       </c>
       <c r="D268">
-        <v>406.5067138671875</v>
+        <v>405.7428894042969</v>
       </c>
       <c r="E268">
         <v>108.6198043823242</v>
       </c>
       <c r="F268">
-        <v>742.0338745117188</v>
+        <v>740.9721069335938</v>
       </c>
       <c r="G268">
-        <v>148.7312164306641</v>
+        <v>148.7311859130859</v>
       </c>
       <c r="H268">
         <v>5.223000049591064</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
-      <c r="A269" s="1">
+    <row r="269">
+      <c r="A269" s="2">
         <v>45352</v>
       </c>
       <c r="B269">
@@ -7369,49 +7356,49 @@
         <v>11.46940326690674</v>
       </c>
       <c r="D269">
-        <v>413.4645385742188</v>
+        <v>412.6876831054688</v>
       </c>
       <c r="E269">
         <v>122.168098449707</v>
       </c>
       <c r="F269">
-        <v>765.9387817382812</v>
+        <v>764.8427734375</v>
       </c>
       <c r="G269">
-        <v>151.8285827636719</v>
+        <v>151.8285675048828</v>
       </c>
       <c r="H269">
         <v>5.203000068664551</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
-      <c r="A270" s="1">
+    <row r="270">
+      <c r="A270" s="2">
         <v>45383</v>
       </c>
       <c r="B270">
         <v>5035.68994140625</v>
       </c>
       <c r="C270">
-        <v>10.4934663772583</v>
+        <v>10.49346828460693</v>
       </c>
       <c r="D270">
-        <v>382.6159362792969</v>
+        <v>381.8970031738281</v>
       </c>
       <c r="E270">
-        <v>110.990104675293</v>
+        <v>110.9900970458984</v>
       </c>
       <c r="F270">
-        <v>769.0302124023438</v>
+        <v>767.9298706054688</v>
       </c>
       <c r="G270">
-        <v>153.7036895751953</v>
+        <v>153.7036743164062</v>
       </c>
       <c r="H270">
         <v>5.244999885559082</v>
       </c>
     </row>
-    <row r="271" spans="1:8">
-      <c r="A271" s="1">
+    <row r="271">
+      <c r="A271" s="2">
         <v>45413</v>
       </c>
       <c r="B271">
@@ -7421,13 +7408,13 @@
         <v>10.60343647003174</v>
       </c>
       <c r="D271">
-        <v>408.7068481445312</v>
+        <v>407.9389038085938</v>
       </c>
       <c r="E271">
-        <v>114.3466339111328</v>
+        <v>114.3466415405273</v>
       </c>
       <c r="F271">
-        <v>809.0404663085938</v>
+        <v>807.8829345703125</v>
       </c>
       <c r="G271">
         <v>154.9656982421875</v>
@@ -7436,34 +7423,34 @@
         <v>5.244999885559082</v>
       </c>
     </row>
-    <row r="272" spans="1:8">
-      <c r="A272" s="1">
+    <row r="272">
+      <c r="A272" s="2">
         <v>45444</v>
       </c>
       <c r="B272">
         <v>5460.47998046875</v>
       </c>
       <c r="C272">
-        <v>10.96183681488037</v>
+        <v>10.96183776855469</v>
       </c>
       <c r="D272">
-        <v>440.0345153808594</v>
+        <v>439.2077026367188</v>
       </c>
       <c r="E272">
-        <v>137.7740783691406</v>
+        <v>137.7741088867188</v>
       </c>
       <c r="F272">
-        <v>892.9091796875</v>
+        <v>891.6314697265625</v>
       </c>
       <c r="G272">
-        <v>155.3236083984375</v>
+        <v>155.3235931396484</v>
       </c>
       <c r="H272">
         <v>5.212999820709229</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
-      <c r="A273" s="1">
+    <row r="273">
+      <c r="A273" s="2">
         <v>45474</v>
       </c>
       <c r="B273">
@@ -7473,65 +7460,65 @@
         <v>9.458300590515137</v>
       </c>
       <c r="D273">
-        <v>411.8770446777344</v>
+        <v>411.1031494140625</v>
       </c>
       <c r="E273">
         <v>136.4507293701172</v>
       </c>
       <c r="F273">
-        <v>793.1919555664062</v>
+        <v>792.056884765625</v>
       </c>
       <c r="G273">
-        <v>152.3162536621094</v>
+        <v>152.3162841796875</v>
       </c>
       <c r="H273">
         <v>5.135000228881836</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
-      <c r="A274" s="1">
+    <row r="274">
+      <c r="A274" s="2">
         <v>45505</v>
       </c>
       <c r="B274">
         <v>5648.39990234375</v>
       </c>
       <c r="C274">
-        <v>9.934099197387695</v>
+        <v>9.934097290039062</v>
       </c>
       <c r="D274">
-        <v>411.4259948730469</v>
+        <v>410.6529541015625</v>
       </c>
       <c r="E274">
         <v>138.2511596679688</v>
       </c>
       <c r="F274">
-        <v>948.1195068359375</v>
+        <v>946.7628173828125</v>
       </c>
       <c r="G274">
-        <v>162.5300598144531</v>
+        <v>162.5300445556641</v>
       </c>
       <c r="H274">
         <v>4.967999935150146</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
-      <c r="A275" s="1">
+    <row r="275">
+      <c r="A275" s="2">
         <v>45536</v>
       </c>
       <c r="B275">
         <v>5762.47998046875</v>
       </c>
       <c r="C275">
-        <v>9.374805450439453</v>
+        <v>9.37480640411377</v>
       </c>
       <c r="D275">
-        <v>424.4057006835938</v>
+        <v>423.6082763671875</v>
       </c>
       <c r="E275">
         <v>166.7350311279297</v>
       </c>
       <c r="F275">
-        <v>874.9578857421875</v>
+        <v>873.7057495117188</v>
       </c>
       <c r="G275">
         <v>164.1028900146484</v>
@@ -7540,24 +7527,24 @@
         <v>4.498000144958496</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
-      <c r="A276" s="1">
+    <row r="276">
+      <c r="A276" s="2">
         <v>45566</v>
       </c>
       <c r="B276">
         <v>5705.4501953125</v>
       </c>
       <c r="C276">
-        <v>9.135110855102539</v>
+        <v>9.135108947753906</v>
       </c>
       <c r="D276">
-        <v>400.7838134765625</v>
+        <v>400.0307006835938</v>
       </c>
       <c r="E276">
         <v>164.5993957519531</v>
       </c>
       <c r="F276">
-        <v>819.4544677734375</v>
+        <v>818.2818603515625</v>
       </c>
       <c r="G276">
         <v>157.4242706298828</v>
@@ -7566,24 +7553,24 @@
         <v>4.432000160217285</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
-      <c r="A277" s="1">
+    <row r="277">
+      <c r="A277" s="2">
         <v>45597</v>
       </c>
       <c r="B277">
         <v>6032.3798828125</v>
       </c>
       <c r="C277">
-        <v>10.01508235931396</v>
+        <v>10.01508331298828</v>
       </c>
       <c r="D277">
-        <v>418.4954223632812</v>
+        <v>417.7090759277344</v>
       </c>
       <c r="E277">
-        <v>181.2711639404297</v>
+        <v>181.2711791992188</v>
       </c>
       <c r="F277">
-        <v>786.7916259765625</v>
+        <v>785.665771484375</v>
       </c>
       <c r="G277">
         <v>170.8431854248047</v>
@@ -7592,50 +7579,50 @@
         <v>4.373000144958496</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
-      <c r="A278" s="1">
+    <row r="278">
+      <c r="A278" s="2">
         <v>45627</v>
       </c>
       <c r="B278">
         <v>5881.6298828125</v>
       </c>
       <c r="C278">
-        <v>8.908294677734375</v>
+        <v>8.908295631408691</v>
       </c>
       <c r="D278">
-        <v>416.5584106445312</v>
+        <v>415.7756958007812</v>
       </c>
       <c r="E278">
         <v>163.4225616455078</v>
       </c>
       <c r="F278">
-        <v>763.6929931640625</v>
+        <v>762.6002197265625</v>
       </c>
       <c r="G278">
-        <v>159.7783203125</v>
+        <v>159.7783050537109</v>
       </c>
       <c r="H278">
         <v>4.208000183105469</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
-      <c r="A279" s="1">
+    <row r="279">
+      <c r="A279" s="2">
         <v>45658</v>
       </c>
       <c r="B279">
         <v>6040.52978515625</v>
       </c>
       <c r="C279">
-        <v>9.07026481628418</v>
+        <v>9.070263862609863</v>
       </c>
       <c r="D279">
-        <v>410.1938781738281</v>
+        <v>409.4231262207031</v>
       </c>
       <c r="E279">
         <v>167.1864624023438</v>
       </c>
       <c r="F279">
-        <v>802.3524169921875</v>
+        <v>801.204345703125</v>
       </c>
       <c r="G279">
         <v>159.160888671875</v>
@@ -7644,24 +7631,24 @@
         <v>4.188000202178955</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
-      <c r="A280" s="1">
+    <row r="280">
+      <c r="A280" s="2">
         <v>45689</v>
       </c>
       <c r="B280">
         <v>5954.5</v>
       </c>
       <c r="C280">
-        <v>8.874183654785156</v>
+        <v>8.874184608459473</v>
       </c>
       <c r="D280">
-        <v>393.1224060058594</v>
+        <v>392.3837585449219</v>
       </c>
       <c r="E280">
-        <v>163.2540283203125</v>
+        <v>163.2540435791016</v>
       </c>
       <c r="F280">
-        <v>912.293212890625</v>
+        <v>910.9877319335938</v>
       </c>
       <c r="G280">
         <v>166.6879119873047</v>
@@ -7670,8 +7657,8 @@
         <v>4.192999839782715</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
-      <c r="A281" s="1">
+    <row r="281">
+      <c r="A281" s="2">
         <v>45717</v>
       </c>
       <c r="B281">
@@ -7681,91 +7668,91 @@
         <v>9.320216178894043</v>
       </c>
       <c r="D281">
-        <v>371.7328796386719</v>
+        <v>371.0344543457031</v>
       </c>
       <c r="E281">
         <v>137.4475860595703</v>
       </c>
       <c r="F281">
-        <v>818.430908203125</v>
+        <v>817.2598266601562</v>
       </c>
       <c r="G281">
-        <v>163.4086151123047</v>
+        <v>163.4086303710938</v>
       </c>
       <c r="H281">
         <v>4.192999839782715</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
-      <c r="A282" s="1">
+    <row r="282">
+      <c r="A282" s="2">
         <v>45748</v>
       </c>
       <c r="B282">
         <v>5569.06005859375</v>
       </c>
       <c r="C282">
-        <v>9.301630973815918</v>
+        <v>9.301631927490234</v>
       </c>
       <c r="D282">
-        <v>391.4092712402344</v>
+        <v>390.673828125</v>
       </c>
       <c r="E282">
         <v>138.8391723632812</v>
       </c>
       <c r="F282">
-        <v>890.8095703125</v>
+        <v>889.534912109375</v>
       </c>
       <c r="G282">
-        <v>156.853271484375</v>
+        <v>156.8532562255859</v>
       </c>
       <c r="H282">
         <v>4.190000057220459</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
-      <c r="A283" s="1">
+    <row r="283">
+      <c r="A283" s="2">
         <v>45778</v>
       </c>
       <c r="B283">
         <v>5911.68994140625</v>
       </c>
       <c r="C283">
-        <v>9.786189079284668</v>
+        <v>9.786190032958984</v>
       </c>
       <c r="D283">
-        <v>456.7119750976562</v>
+        <v>455.8537902832031</v>
       </c>
       <c r="E283">
-        <v>163.3175659179688</v>
+        <v>163.3175811767578</v>
       </c>
       <c r="F283">
-        <v>732.4884033203125</v>
+        <v>731.4402465820312</v>
       </c>
       <c r="G283">
-        <v>163.9158325195312</v>
+        <v>163.9158477783203</v>
       </c>
       <c r="H283">
         <v>4.23199987411499</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
-      <c r="A284" s="1">
+    <row r="284">
+      <c r="A284" s="2">
         <v>45809</v>
       </c>
       <c r="B284">
         <v>6204.9501953125</v>
       </c>
       <c r="C284">
-        <v>10.22930240631104</v>
+        <v>10.22930335998535</v>
       </c>
       <c r="D284">
-        <v>493.4683837890625</v>
+        <v>492.5411682128906</v>
       </c>
       <c r="E284">
-        <v>215.7078704833984</v>
+        <v>215.7078552246094</v>
       </c>
       <c r="F284">
-        <v>774.0543212890625</v>
+        <v>772.94677734375</v>
       </c>
       <c r="G284">
         <v>153.7175445556641</v>
@@ -7774,34 +7761,34 @@
         <v>4.190000057220459</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
-      <c r="A285" s="1">
+    <row r="285">
+      <c r="A285" s="2">
         <v>45839</v>
       </c>
       <c r="B285">
         <v>6339.39013671875</v>
       </c>
       <c r="C285">
-        <v>10.4367151260376</v>
+        <v>10.43671607971191</v>
       </c>
       <c r="D285">
-        <v>529.2723999023438</v>
+        <v>528.2779541015625</v>
       </c>
       <c r="E285">
         <v>250.9102172851562</v>
       </c>
       <c r="F285">
-        <v>734.8715209960938</v>
+        <v>733.8199462890625</v>
       </c>
       <c r="G285">
-        <v>146.1715698242188</v>
+        <v>146.1715850830078</v>
       </c>
       <c r="H285">
         <v>4.235000133514404</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
-      <c r="A286" s="1">
+    <row r="286">
+      <c r="A286" s="2">
         <v>45870</v>
       </c>
       <c r="B286">
@@ -7811,13 +7798,13 @@
         <v>11.24568748474121</v>
       </c>
       <c r="D286">
-        <v>503.501220703125</v>
+        <v>502.5551452636719</v>
       </c>
       <c r="E286">
         <v>223.5816955566406</v>
       </c>
       <c r="F286">
-        <v>729.0318603515625</v>
+        <v>727.9886474609375</v>
       </c>
       <c r="G286">
         <v>152.5538787841797</v>
@@ -7826,8 +7813,8 @@
         <v>4.043000221252441</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
-      <c r="A287" s="1">
+    <row r="287">
+      <c r="A287" s="2">
         <v>45901</v>
       </c>
       <c r="B287">
@@ -7837,13 +7824,13 @@
         <v>11.42722320556641</v>
       </c>
       <c r="D287">
-        <v>514.6903686523438</v>
+        <v>513.7232666015625</v>
       </c>
       <c r="E287">
         <v>278.0706481933594</v>
       </c>
       <c r="F287">
-        <v>759.3045654296875</v>
+        <v>758.2180786132812</v>
       </c>
       <c r="G287">
         <v>149.2607269287109</v>
@@ -7852,8 +7839,8 @@
         <v>3.845000028610229</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
-      <c r="A288" s="1">
+    <row r="288">
+      <c r="A288" s="2">
         <v>45931</v>
       </c>
       <c r="B288">
@@ -7863,13 +7850,13 @@
         <v>12.54510307312012</v>
       </c>
       <c r="D288">
-        <v>514.5512084960938</v>
+        <v>513.5844116210938</v>
       </c>
       <c r="E288">
-        <v>260.1011657714844</v>
+        <v>260.1011352539062</v>
       </c>
       <c r="F288">
-        <v>858.6808471679688</v>
+        <v>857.4521484375</v>
       </c>
       <c r="G288">
         <v>147.0959167480469</v>
@@ -7878,8 +7865,8 @@
         <v>3.717999935150146</v>
       </c>
     </row>
-    <row r="289" spans="1:8">
-      <c r="A289" s="1">
+    <row r="289">
+      <c r="A289" s="2">
         <v>45962</v>
       </c>
       <c r="B289">
@@ -7889,13 +7876,13 @@
         <v>12.83516502380371</v>
       </c>
       <c r="D289">
-        <v>489.8286743164062</v>
+        <v>488.9082946777344</v>
       </c>
       <c r="E289">
-        <v>200.0206909179688</v>
+        <v>200.0206756591797</v>
       </c>
       <c r="F289">
-        <v>1071.832885742188</v>
+        <v>1070.299194335938</v>
       </c>
       <c r="G289">
         <v>144.9340362548828</v>
@@ -7904,8 +7891,8 @@
         <v>3.697000026702881</v>
       </c>
     </row>
-    <row r="290" spans="1:8">
-      <c r="A290" s="1">
+    <row r="290">
+      <c r="A290" s="2">
         <v>45992</v>
       </c>
       <c r="B290">
@@ -7915,23 +7902,23 @@
         <v>12.68052387237549</v>
       </c>
       <c r="D290">
-        <v>481.4758605957031</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="E290">
         <v>193.0479431152344</v>
       </c>
       <c r="F290">
-        <v>1071.045654296875</v>
+        <v>1069.513061523438</v>
       </c>
       <c r="G290">
-        <v>140.1896362304688</v>
+        <v>140.1896209716797</v>
       </c>
       <c r="H290">
         <v>3.546999931335449</v>
       </c>
     </row>
-    <row r="291" spans="1:8">
-      <c r="A291" s="1">
+    <row r="291">
+      <c r="A291" s="2">
         <v>46023</v>
       </c>
       <c r="B291">
@@ -7941,13 +7928,13 @@
         <v>13.41506671905518</v>
       </c>
       <c r="D291">
-        <v>428.38232421875</v>
+        <v>427.577392578125</v>
       </c>
       <c r="E291">
         <v>163.4385833740234</v>
       </c>
       <c r="F291">
-        <v>1033.642456054688</v>
+        <v>1032.163330078125</v>
       </c>
       <c r="G291">
         <v>149.5195465087891</v>
@@ -7956,8 +7943,8 @@
         <v>3.572000026702881</v>
       </c>
     </row>
-    <row r="292" spans="1:8">
-      <c r="A292" s="1">
+    <row r="292">
+      <c r="A292" s="2">
         <v>46054</v>
       </c>
       <c r="B292">
@@ -7967,13 +7954,13 @@
         <v>13.7655200958252</v>
       </c>
       <c r="D292">
-        <v>391.8912048339844</v>
+        <v>391.1548461914062</v>
       </c>
       <c r="E292">
         <v>144.3916015625</v>
       </c>
       <c r="F292">
-        <v>1050.18212890625</v>
+        <v>1048.679443359375</v>
       </c>
       <c r="G292">
         <v>164.7207336425781</v>
@@ -7982,8 +7969,8 @@
         <v>3.578000068664551</v>
       </c>
     </row>
-    <row r="293" spans="1:8">
-      <c r="A293" s="1">
+    <row r="293">
+      <c r="A293" s="2">
         <v>46082</v>
       </c>
       <c r="B293">
@@ -7993,13 +7980,13 @@
         <v>11.27424430847168</v>
       </c>
       <c r="D293">
-        <v>369.3699951171875</v>
+        <v>368.6759643554688</v>
       </c>
       <c r="E293">
         <v>146.0897521972656</v>
       </c>
       <c r="F293">
-        <v>918.189453125</v>
+        <v>916.8756103515625</v>
       </c>
       <c r="G293">
         <v>142.2982330322266</v>
@@ -8008,8 +7995,8 @@
         <v>3.599999904632568</v>
       </c>
     </row>
-    <row r="294" spans="1:8">
-      <c r="A294" s="1">
+    <row r="294">
+      <c r="A294" s="2">
         <v>46113</v>
       </c>
       <c r="B294">
@@ -8019,13 +8006,13 @@
         <v>11.80180835723877</v>
       </c>
       <c r="D294">
-        <v>406.8987121582031</v>
+        <v>406.1341552734375</v>
       </c>
       <c r="E294">
         <v>160.8304748535156</v>
       </c>
       <c r="F294">
-        <v>932.993896484375</v>
+        <v>931.6588745117188</v>
       </c>
       <c r="G294">
         <v>146.0001068115234</v>
@@ -8034,8 +8021,8 @@
         <v>3.585000038146973</v>
       </c>
     </row>
-    <row r="295" spans="1:8">
-      <c r="A295" s="1">
+    <row r="295">
+      <c r="A295" s="2">
         <v>46143</v>
       </c>
       <c r="B295">
@@ -8045,13 +8032,13 @@
         <v>17.25314331054688</v>
       </c>
       <c r="D295">
-        <v>450.239990234375</v>
+        <v>449.3940124511719</v>
       </c>
       <c r="E295">
         <v>224.9972381591797</v>
       </c>
       <c r="F295">
-        <v>1105</v>
+        <v>1103.418823242188</v>
       </c>
       <c r="G295">
         <v>142.4962615966797</v>
@@ -8060,8 +8047,8 @@
         <v>3.588000059127808</v>
       </c>
     </row>
-    <row r="296" spans="1:8">
-      <c r="A296" s="1">
+    <row r="296">
+      <c r="A296" s="2">
         <v>46174</v>
       </c>
       <c r="B296">
@@ -8071,13 +8058,13 @@
         <v>13.75107097625732</v>
       </c>
       <c r="D296">
-        <v>373.0199890136719</v>
+        <v>372.319091796875</v>
       </c>
       <c r="E296">
         <v>146.0419311523438</v>
       </c>
       <c r="F296">
-        <v>1199.430053710938</v>
+        <v>1197.713745117188</v>
       </c>
       <c r="G296">
         <v>145.5534362792969</v>
@@ -8086,8 +8073,8 @@
         <v>3.732000112533569</v>
       </c>
     </row>
-    <row r="297" spans="1:8">
-      <c r="A297" s="1">
+    <row r="297">
+      <c r="A297" s="2">
         <v>46204</v>
       </c>
       <c r="B297">
@@ -8097,13 +8084,13 @@
         <v>14.52271461486816</v>
       </c>
       <c r="D297">
-        <v>464.7200012207031</v>
+        <v>463.8468017578125</v>
       </c>
       <c r="E297">
         <v>129.8699951171875</v>
       </c>
       <c r="F297">
-        <v>1148.839965820312</v>
+        <v>1147.196044921875</v>
       </c>
       <c r="G297">
         <v>144.4900054931641</v>
@@ -8112,30 +8099,56 @@
         <v>3.681999921798706</v>
       </c>
     </row>
-    <row r="298" spans="1:8">
-      <c r="A298" s="1">
+    <row r="298">
+      <c r="A298" s="2">
         <v>46235</v>
       </c>
       <c r="B298">
-        <v>7798.990234375</v>
+        <v>7686.14013671875</v>
       </c>
       <c r="C298">
-        <v>13.89000034332275</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="D298">
-        <v>496.8800048828125</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="E298">
-        <v>156.2200012207031</v>
+        <v>149.1199951171875</v>
       </c>
       <c r="F298">
-        <v>1209</v>
+        <v>1156.72998046875</v>
       </c>
       <c r="G298">
-        <v>144.2599945068359</v>
+        <v>145.1199951171875</v>
       </c>
       <c r="H298">
-        <v>3.704999923706055</v>
+        <v>3.732000112533569</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B299">
+        <v>7704.1298828125</v>
+      </c>
+      <c r="C299">
+        <v>12.60000038146973</v>
+      </c>
+      <c r="D299">
+        <v>497.9299926757812</v>
+      </c>
+      <c r="E299">
+        <v>139.5399932861328</v>
+      </c>
+      <c r="F299">
+        <v>1181.890014648438</v>
+      </c>
+      <c r="G299">
+        <v>145.6799926757812</v>
+      </c>
+      <c r="H299">
+        <v>4.067999839782715</v>
       </c>
     </row>
   </sheetData>
